--- a/output/acs-activity-calendar-2027.xlsx
+++ b/output/acs-activity-calendar-2027.xlsx
@@ -828,7 +828,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="147">
+  <borders count="153">
     <border>
       <left/>
       <right/>
@@ -2494,6 +2494,66 @@
       </bottom>
     </border>
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="00FFFFFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00FFFFFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FFFFFF"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="00C62026"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="hair">
+        <color rgb="00C8C6BD"/>
+      </right>
+      <bottom style="hair">
+        <color rgb="00C8C6BD"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FFFFFF"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FFFFFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00FFFFFF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FFFFFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00FFFFFF"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00FFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2514,7 +2574,7 @@
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1230">
+  <cellXfs count="1283">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6234,6 +6294,171 @@
     </xf>
     <xf numFmtId="0" fontId="66" fillId="46" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="148" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="148" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="103" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="47" borderId="103" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="46" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="46" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="47" borderId="103" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="48" borderId="103" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="49" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="60" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="52" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="52" borderId="146" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="53" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="53" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="54" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="54" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="55" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="55" borderId="146" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="56" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="56" borderId="146" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="57" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="61" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="49" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="49" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="57" borderId="146" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="53" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="57" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="54" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="59" borderId="146" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="58" borderId="146" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="58" borderId="146" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="49" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="52" borderId="149" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="111" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="112" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="151" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="53" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="54" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="55" borderId="149" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="56" borderId="149" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="49" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="49" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="57" borderId="149" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="54" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="59" borderId="149" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="109" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -6917,404 +7142,401 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="998" t="inlineStr">
+      <c r="A1" s="1230" t="inlineStr">
         <is>
           <t>ACS ACTIVITY CALENDAR 2027</t>
         </is>
       </c>
-      <c r="B1" s="999" t="n"/>
-      <c r="C1" s="999" t="n"/>
-      <c r="D1" s="999" t="n"/>
-      <c r="E1" s="999" t="n"/>
-      <c r="F1" s="999" t="n"/>
-      <c r="G1" s="999" t="n"/>
-      <c r="H1" s="999" t="n"/>
-      <c r="I1" s="999" t="n"/>
-      <c r="J1" s="999" t="n"/>
-      <c r="K1" s="999" t="n"/>
-      <c r="L1" s="999" t="n"/>
-      <c r="M1" s="999" t="n"/>
-      <c r="N1" s="999" t="n"/>
-      <c r="O1" s="999" t="n"/>
-      <c r="P1" s="999" t="n"/>
-      <c r="Q1" s="999" t="n"/>
-      <c r="R1" s="999" t="n"/>
-      <c r="S1" s="999" t="n"/>
-      <c r="T1" s="999" t="n"/>
-      <c r="U1" s="999" t="n"/>
-      <c r="V1" s="999" t="n"/>
-      <c r="W1" s="999" t="n"/>
-      <c r="X1" s="999" t="n"/>
-      <c r="Y1" s="999" t="n"/>
-      <c r="Z1" s="999" t="n"/>
-      <c r="AA1" s="999" t="n"/>
-      <c r="AB1" s="999" t="n"/>
-      <c r="AC1" s="999" t="n"/>
-      <c r="AD1" s="999" t="n"/>
-      <c r="AE1" s="999" t="n"/>
-      <c r="AF1" s="999" t="n"/>
-      <c r="AG1" s="999" t="n"/>
-      <c r="AH1" s="999" t="n"/>
-      <c r="AI1" s="999" t="n"/>
-      <c r="AJ1" s="999" t="n"/>
-      <c r="AK1" s="999" t="n"/>
-      <c r="AL1" s="999" t="n"/>
-      <c r="AM1" s="999" t="n"/>
-      <c r="AN1" s="999" t="n"/>
+      <c r="B1" s="1231" t="n"/>
+      <c r="C1" s="1231" t="n"/>
+      <c r="D1" s="1231" t="n"/>
+      <c r="E1" s="1231" t="n"/>
+      <c r="F1" s="1231" t="n"/>
+      <c r="G1" s="1231" t="n"/>
+      <c r="H1" s="1231" t="n"/>
+      <c r="I1" s="1231" t="n"/>
+      <c r="J1" s="1231" t="n"/>
+      <c r="K1" s="1231" t="n"/>
+      <c r="L1" s="1231" t="n"/>
+      <c r="M1" s="1231" t="n"/>
+      <c r="N1" s="1231" t="n"/>
+      <c r="O1" s="1231" t="n"/>
+      <c r="P1" s="1231" t="n"/>
+      <c r="Q1" s="1231" t="n"/>
+      <c r="R1" s="1231" t="n"/>
+      <c r="S1" s="1231" t="n"/>
+      <c r="T1" s="1231" t="n"/>
+      <c r="U1" s="1231" t="n"/>
+      <c r="V1" s="1231" t="n"/>
+      <c r="W1" s="1231" t="n"/>
+      <c r="X1" s="1231" t="n"/>
+      <c r="Y1" s="1231" t="n"/>
+      <c r="Z1" s="1231" t="n"/>
+      <c r="AA1" s="1231" t="n"/>
+      <c r="AB1" s="1231" t="n"/>
+      <c r="AC1" s="1231" t="n"/>
+      <c r="AD1" s="1231" t="n"/>
+      <c r="AE1" s="1231" t="n"/>
+      <c r="AF1" s="1231" t="n"/>
+      <c r="AG1" s="1231" t="n"/>
+      <c r="AH1" s="1231" t="n"/>
+      <c r="AI1" s="1231" t="n"/>
+      <c r="AJ1" s="1231" t="n"/>
+      <c r="AK1" s="1231" t="n"/>
+      <c r="AL1" s="1231" t="n"/>
+      <c r="AM1" s="1231" t="n"/>
+      <c r="AN1" s="1231" t="n"/>
     </row>
     <row r="2" ht="8" customHeight="1" thickBot="1">
-      <c r="C2" s="350" t="n"/>
-      <c r="D2" s="350" t="n"/>
-      <c r="E2" s="350" t="n"/>
-      <c r="F2" s="350" t="n"/>
-      <c r="G2" s="350" t="n"/>
-      <c r="H2" s="350" t="n"/>
-      <c r="I2" s="350" t="n"/>
-      <c r="J2" s="350" t="n"/>
-      <c r="K2" s="350" t="n"/>
-      <c r="L2" s="350" t="n"/>
-      <c r="M2" s="350" t="n"/>
-      <c r="N2" s="350" t="n"/>
-      <c r="O2" s="350" t="n"/>
-      <c r="P2" s="350" t="n"/>
-      <c r="Q2" s="350" t="n"/>
-      <c r="R2" s="350" t="n"/>
-      <c r="S2" s="350" t="n"/>
-      <c r="T2" s="350" t="n"/>
-      <c r="U2" s="350" t="n"/>
-      <c r="V2" s="350" t="n"/>
-      <c r="W2" s="350" t="n"/>
-      <c r="X2" s="350" t="n"/>
-      <c r="Y2" s="350" t="n"/>
-      <c r="Z2" s="350" t="n"/>
-      <c r="AA2" s="350" t="n"/>
-      <c r="AB2" s="350" t="n"/>
-      <c r="AC2" s="350" t="n"/>
-      <c r="AD2" s="350" t="n"/>
-      <c r="AE2" s="350" t="n"/>
-      <c r="AF2" s="350" t="n"/>
-      <c r="AG2" s="350" t="n"/>
-      <c r="AH2" s="350" t="n"/>
-      <c r="AI2" s="350" t="n"/>
-      <c r="AJ2" s="350" t="n"/>
-      <c r="AK2" s="350" t="n"/>
-      <c r="AL2" s="350" t="n"/>
-      <c r="AM2" s="350" t="n"/>
-      <c r="AN2" s="350" t="n"/>
+      <c r="A2" s="1225" t="n"/>
+      <c r="B2" s="1225" t="n"/>
+      <c r="C2" s="1265" t="n"/>
+      <c r="D2" s="1265" t="n"/>
+      <c r="E2" s="1265" t="n"/>
+      <c r="F2" s="1265" t="n"/>
+      <c r="G2" s="1265" t="n"/>
+      <c r="H2" s="1265" t="n"/>
+      <c r="I2" s="1265" t="n"/>
+      <c r="J2" s="1265" t="n"/>
+      <c r="K2" s="1265" t="n"/>
+      <c r="L2" s="1265" t="n"/>
+      <c r="M2" s="1265" t="n"/>
+      <c r="N2" s="1265" t="n"/>
+      <c r="O2" s="1265" t="n"/>
+      <c r="P2" s="1265" t="n"/>
+      <c r="Q2" s="1265" t="n"/>
+      <c r="R2" s="1265" t="n"/>
+      <c r="S2" s="1265" t="n"/>
+      <c r="T2" s="1265" t="n"/>
+      <c r="U2" s="1265" t="n"/>
+      <c r="V2" s="1265" t="n"/>
+      <c r="W2" s="1265" t="n"/>
+      <c r="X2" s="1265" t="n"/>
+      <c r="Y2" s="1265" t="n"/>
+      <c r="Z2" s="1265" t="n"/>
+      <c r="AA2" s="1265" t="n"/>
+      <c r="AB2" s="1265" t="n"/>
+      <c r="AC2" s="1265" t="n"/>
+      <c r="AD2" s="1265" t="n"/>
+      <c r="AE2" s="1265" t="n"/>
+      <c r="AF2" s="1265" t="n"/>
+      <c r="AG2" s="1265" t="n"/>
+      <c r="AH2" s="1265" t="n"/>
+      <c r="AI2" s="1265" t="n"/>
+      <c r="AJ2" s="1265" t="n"/>
+      <c r="AK2" s="1265" t="n"/>
+      <c r="AL2" s="1265" t="n"/>
+      <c r="AM2" s="1265" t="n"/>
+      <c r="AN2" s="1265" t="n"/>
     </row>
     <row r="3" ht="13" customHeight="1" thickBot="1">
-      <c r="A3" s="318" t="n"/>
-      <c r="B3" s="1000" t="inlineStr">
+      <c r="A3" s="1233" t="n"/>
+      <c r="B3" s="1234" t="inlineStr">
         <is>
           <t>Su</t>
         </is>
       </c>
-      <c r="C3" s="711" t="inlineStr">
+      <c r="C3" s="1235" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="D3" s="711" t="inlineStr">
+      <c r="D3" s="1235" t="inlineStr">
         <is>
           <t>Tu</t>
         </is>
       </c>
-      <c r="E3" s="711" t="inlineStr">
+      <c r="E3" s="1235" t="inlineStr">
         <is>
           <t>We</t>
         </is>
       </c>
-      <c r="F3" s="711" t="inlineStr">
+      <c r="F3" s="1235" t="inlineStr">
         <is>
           <t>Th</t>
         </is>
       </c>
-      <c r="G3" s="711" t="inlineStr">
+      <c r="G3" s="1235" t="inlineStr">
         <is>
           <t>Fr</t>
         </is>
       </c>
-      <c r="H3" s="1001" t="inlineStr">
+      <c r="H3" s="1234" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="I3" s="1001" t="inlineStr">
+      <c r="I3" s="1234" t="inlineStr">
         <is>
           <t>Su</t>
         </is>
       </c>
-      <c r="J3" s="711" t="inlineStr">
+      <c r="J3" s="1235" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="K3" s="711" t="inlineStr">
+      <c r="K3" s="1235" t="inlineStr">
         <is>
           <t>Tu</t>
         </is>
       </c>
-      <c r="L3" s="711" t="inlineStr">
+      <c r="L3" s="1235" t="inlineStr">
         <is>
           <t>We</t>
         </is>
       </c>
-      <c r="M3" s="711" t="inlineStr">
+      <c r="M3" s="1235" t="inlineStr">
         <is>
           <t>Th</t>
         </is>
       </c>
-      <c r="N3" s="711" t="inlineStr">
+      <c r="N3" s="1235" t="inlineStr">
         <is>
           <t>Fr</t>
         </is>
       </c>
-      <c r="O3" s="1001" t="inlineStr">
+      <c r="O3" s="1234" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="P3" s="1001" t="inlineStr">
+      <c r="P3" s="1234" t="inlineStr">
         <is>
           <t>Su</t>
         </is>
       </c>
-      <c r="Q3" s="711" t="inlineStr">
+      <c r="Q3" s="1235" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="R3" s="711" t="inlineStr">
+      <c r="R3" s="1235" t="inlineStr">
         <is>
           <t>Tu</t>
         </is>
       </c>
-      <c r="S3" s="711" t="inlineStr">
+      <c r="S3" s="1235" t="inlineStr">
         <is>
           <t>We</t>
         </is>
       </c>
-      <c r="T3" s="711" t="inlineStr">
+      <c r="T3" s="1235" t="inlineStr">
         <is>
           <t>Th</t>
         </is>
       </c>
-      <c r="U3" s="711" t="inlineStr">
+      <c r="U3" s="1235" t="inlineStr">
         <is>
           <t>Fr</t>
         </is>
       </c>
-      <c r="V3" s="1001" t="inlineStr">
+      <c r="V3" s="1234" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="W3" s="1001" t="inlineStr">
+      <c r="W3" s="1234" t="inlineStr">
         <is>
           <t>Su</t>
         </is>
       </c>
-      <c r="X3" s="711" t="inlineStr">
+      <c r="X3" s="1235" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="Y3" s="711" t="inlineStr">
+      <c r="Y3" s="1235" t="inlineStr">
         <is>
           <t>Tu</t>
         </is>
       </c>
-      <c r="Z3" s="711" t="inlineStr">
+      <c r="Z3" s="1235" t="inlineStr">
         <is>
           <t>We</t>
         </is>
       </c>
-      <c r="AA3" s="711" t="inlineStr">
+      <c r="AA3" s="1235" t="inlineStr">
         <is>
           <t>Th</t>
         </is>
       </c>
-      <c r="AB3" s="711" t="inlineStr">
+      <c r="AB3" s="1235" t="inlineStr">
         <is>
           <t>Fr</t>
         </is>
       </c>
-      <c r="AC3" s="1001" t="inlineStr">
+      <c r="AC3" s="1234" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="AD3" s="1001" t="inlineStr">
+      <c r="AD3" s="1234" t="inlineStr">
         <is>
           <t>Su</t>
         </is>
       </c>
-      <c r="AE3" s="711" t="inlineStr">
+      <c r="AE3" s="1235" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="AF3" s="711" t="inlineStr">
+      <c r="AF3" s="1235" t="inlineStr">
         <is>
           <t>Tu</t>
         </is>
       </c>
-      <c r="AG3" s="711" t="inlineStr">
+      <c r="AG3" s="1235" t="inlineStr">
         <is>
           <t>We</t>
         </is>
       </c>
-      <c r="AH3" s="711" t="inlineStr">
+      <c r="AH3" s="1235" t="inlineStr">
         <is>
           <t>Th</t>
         </is>
       </c>
-      <c r="AI3" s="711" t="inlineStr">
+      <c r="AI3" s="1235" t="inlineStr">
         <is>
           <t>Fr</t>
         </is>
       </c>
-      <c r="AJ3" s="1001" t="inlineStr">
+      <c r="AJ3" s="1234" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="AK3" s="1001" t="inlineStr">
+      <c r="AK3" s="1234" t="inlineStr">
         <is>
           <t>Su</t>
         </is>
       </c>
-      <c r="AL3" s="713" t="inlineStr">
+      <c r="AL3" s="1235" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="AM3" s="714" t="inlineStr">
+      <c r="AM3" s="1235" t="inlineStr">
         <is>
           <t>Tu</t>
         </is>
       </c>
-      <c r="AN3" s="715" t="inlineStr">
+      <c r="AN3" s="1235" t="inlineStr">
         <is>
           <t>We</t>
         </is>
       </c>
     </row>
     <row r="4" ht="14" customHeight="1" thickBot="1">
-      <c r="A4" s="1226" t="inlineStr">
+      <c r="A4" s="1236" t="inlineStr">
         <is>
           <t>January</t>
         </is>
       </c>
-      <c r="B4" s="1002" t="n"/>
-      <c r="C4" s="1146" t="n"/>
-      <c r="D4" s="1146" t="n"/>
-      <c r="E4" s="1146" t="n"/>
-      <c r="F4" s="1147" t="n"/>
-      <c r="G4" s="720" t="n">
+      <c r="B4" s="1266" t="n"/>
+      <c r="F4" s="1149" t="n"/>
+      <c r="G4" s="1238" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="721" t="n">
+      <c r="H4" s="1239" t="n">
         <v>2</v>
       </c>
-      <c r="I4" s="721" t="n">
+      <c r="I4" s="1239" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="720" t="n">
+      <c r="J4" s="1238" t="n">
         <v>4</v>
       </c>
-      <c r="K4" s="720" t="n">
+      <c r="K4" s="1238" t="n">
         <v>5</v>
       </c>
-      <c r="L4" s="720" t="n">
+      <c r="L4" s="1238" t="n">
         <v>6</v>
       </c>
-      <c r="M4" s="720" t="n">
+      <c r="M4" s="1238" t="n">
         <v>7</v>
       </c>
-      <c r="N4" s="720" t="n">
+      <c r="N4" s="1238" t="n">
         <v>8</v>
       </c>
-      <c r="O4" s="721" t="n">
+      <c r="O4" s="1239" t="n">
         <v>9</v>
       </c>
-      <c r="P4" s="721" t="n">
+      <c r="P4" s="1239" t="n">
         <v>10</v>
       </c>
-      <c r="Q4" s="720" t="n">
+      <c r="Q4" s="1238" t="n">
         <v>11</v>
       </c>
-      <c r="R4" s="720" t="n">
+      <c r="R4" s="1238" t="n">
         <v>12</v>
       </c>
-      <c r="S4" s="720" t="n">
+      <c r="S4" s="1238" t="n">
         <v>13</v>
       </c>
-      <c r="T4" s="720" t="n">
+      <c r="T4" s="1238" t="n">
         <v>14</v>
       </c>
-      <c r="U4" s="720" t="n">
+      <c r="U4" s="1238" t="n">
         <v>15</v>
       </c>
-      <c r="V4" s="721" t="n">
+      <c r="V4" s="1239" t="n">
         <v>16</v>
       </c>
-      <c r="W4" s="721" t="n">
+      <c r="W4" s="1239" t="n">
         <v>17</v>
       </c>
-      <c r="X4" s="720" t="n">
+      <c r="X4" s="1238" t="n">
         <v>18</v>
       </c>
-      <c r="Y4" s="720" t="n">
+      <c r="Y4" s="1238" t="n">
         <v>19</v>
       </c>
-      <c r="Z4" s="720" t="n">
+      <c r="Z4" s="1238" t="n">
         <v>20</v>
       </c>
-      <c r="AA4" s="720" t="n">
+      <c r="AA4" s="1238" t="n">
         <v>21</v>
       </c>
-      <c r="AB4" s="720" t="n">
+      <c r="AB4" s="1238" t="n">
         <v>22</v>
       </c>
-      <c r="AC4" s="721" t="n">
+      <c r="AC4" s="1239" t="n">
         <v>23</v>
       </c>
-      <c r="AD4" s="721" t="n">
+      <c r="AD4" s="1239" t="n">
         <v>24</v>
       </c>
-      <c r="AE4" s="720" t="n">
+      <c r="AE4" s="1238" t="n">
         <v>25</v>
       </c>
-      <c r="AF4" s="720" t="n">
+      <c r="AF4" s="1238" t="n">
         <v>26</v>
       </c>
-      <c r="AG4" s="720" t="n">
+      <c r="AG4" s="1238" t="n">
         <v>27</v>
       </c>
-      <c r="AH4" s="720" t="n">
+      <c r="AH4" s="1238" t="n">
         <v>28</v>
       </c>
-      <c r="AI4" s="720" t="n">
+      <c r="AI4" s="1238" t="n">
         <v>29</v>
       </c>
-      <c r="AJ4" s="721" t="n">
+      <c r="AJ4" s="1239" t="n">
         <v>30</v>
       </c>
-      <c r="AK4" s="721" t="n">
+      <c r="AK4" s="1239" t="n">
         <v>31</v>
       </c>
-      <c r="AL4" s="1004" t="n"/>
-      <c r="AM4" s="1146" t="n"/>
-      <c r="AN4" s="1147" t="n"/>
+      <c r="AL4" s="1267" t="n"/>
+      <c r="AN4" s="1149" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="1206" t="inlineStr">
+      <c r="A5" s="1241" t="inlineStr">
         <is>
           <t>ACS</t>
         </is>
       </c>
-      <c r="B5" s="1148" t="n"/>
       <c r="F5" s="1149" t="n"/>
       <c r="G5" s="1006" t="n"/>
       <c r="H5" s="1007" t="n"/>
@@ -7347,12 +7569,10 @@
       <c r="AI5" s="1009" t="n"/>
       <c r="AJ5" s="1010" t="n"/>
       <c r="AK5" s="1010" t="n"/>
-      <c r="AL5" s="1148" t="n"/>
       <c r="AN5" s="1149" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1" thickBot="1">
-      <c r="A6" s="729" t="n"/>
-      <c r="B6" s="1148" t="n"/>
+      <c r="A6" s="1268" t="n"/>
       <c r="F6" s="1149" t="n"/>
       <c r="G6" s="1008" t="n"/>
       <c r="H6" s="1012" t="n"/>
@@ -7385,16 +7605,14 @@
       <c r="AI6" s="1009" t="n"/>
       <c r="AJ6" s="1010" t="n"/>
       <c r="AK6" s="1010" t="n"/>
-      <c r="AL6" s="1148" t="n"/>
       <c r="AN6" s="1149" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1" thickBot="1">
-      <c r="A7" s="1208" t="inlineStr">
+      <c r="A7" s="1242" t="inlineStr">
         <is>
           <t>OCS (NZ)</t>
         </is>
       </c>
-      <c r="B7" s="1148" t="n"/>
       <c r="F7" s="1149" t="n"/>
       <c r="G7" s="1008" t="n"/>
       <c r="H7" s="1015" t="n"/>
@@ -7404,39 +7622,37 @@
       <c r="L7" s="1009" t="n"/>
       <c r="M7" s="1009" t="n"/>
       <c r="N7" s="1009" t="n"/>
-      <c r="O7" s="1017" t="inlineStr">
+      <c r="O7" s="1269" t="inlineStr">
         <is>
           <t>TFCC</t>
         </is>
       </c>
-      <c r="P7" s="732" t="n"/>
-      <c r="Q7" s="732" t="n"/>
-      <c r="R7" s="732" t="n"/>
-      <c r="S7" s="732" t="n"/>
-      <c r="T7" s="732" t="n"/>
-      <c r="U7" s="732" t="n"/>
-      <c r="V7" s="732" t="n"/>
-      <c r="W7" s="732" t="n"/>
-      <c r="X7" s="732" t="n"/>
-      <c r="Y7" s="732" t="n"/>
-      <c r="Z7" s="732" t="n"/>
-      <c r="AA7" s="732" t="n"/>
-      <c r="AB7" s="732" t="n"/>
-      <c r="AC7" s="732" t="n"/>
-      <c r="AD7" s="732" t="n"/>
-      <c r="AE7" s="732" t="n"/>
-      <c r="AF7" s="732" t="n"/>
-      <c r="AG7" s="732" t="n"/>
-      <c r="AH7" s="732" t="n"/>
-      <c r="AI7" s="732" t="n"/>
-      <c r="AJ7" s="732" t="n"/>
-      <c r="AK7" s="733" t="n"/>
-      <c r="AL7" s="1148" t="n"/>
+      <c r="P7" s="1270" t="n"/>
+      <c r="Q7" s="1270" t="n"/>
+      <c r="R7" s="1270" t="n"/>
+      <c r="S7" s="1270" t="n"/>
+      <c r="T7" s="1270" t="n"/>
+      <c r="U7" s="1270" t="n"/>
+      <c r="V7" s="1270" t="n"/>
+      <c r="W7" s="1270" t="n"/>
+      <c r="X7" s="1270" t="n"/>
+      <c r="Y7" s="1270" t="n"/>
+      <c r="Z7" s="1270" t="n"/>
+      <c r="AA7" s="1270" t="n"/>
+      <c r="AB7" s="1270" t="n"/>
+      <c r="AC7" s="1270" t="n"/>
+      <c r="AD7" s="1270" t="n"/>
+      <c r="AE7" s="1270" t="n"/>
+      <c r="AF7" s="1270" t="n"/>
+      <c r="AG7" s="1270" t="n"/>
+      <c r="AH7" s="1270" t="n"/>
+      <c r="AI7" s="1270" t="n"/>
+      <c r="AJ7" s="1270" t="n"/>
+      <c r="AK7" s="1271" t="n"/>
       <c r="AN7" s="1149" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="724" t="n"/>
-      <c r="B8" s="1148" t="n"/>
+      <c r="A8" s="1272" t="n"/>
       <c r="F8" s="1149" t="n"/>
       <c r="G8" s="1008" t="n"/>
       <c r="H8" s="1012" t="n"/>
@@ -7455,30 +7671,28 @@
       <c r="U8" s="1009" t="n"/>
       <c r="V8" s="1015" t="n"/>
       <c r="W8" s="1015" t="n"/>
-      <c r="X8" s="1017" t="inlineStr">
+      <c r="X8" s="1269" t="inlineStr">
         <is>
           <t>IIT</t>
         </is>
       </c>
-      <c r="Y8" s="732" t="n"/>
-      <c r="Z8" s="732" t="n"/>
-      <c r="AA8" s="732" t="n"/>
-      <c r="AB8" s="732" t="n"/>
-      <c r="AC8" s="732" t="n"/>
-      <c r="AD8" s="732" t="n"/>
-      <c r="AE8" s="732" t="n"/>
-      <c r="AF8" s="732" t="n"/>
-      <c r="AG8" s="732" t="n"/>
-      <c r="AH8" s="732" t="n"/>
-      <c r="AI8" s="732" t="n"/>
-      <c r="AJ8" s="732" t="n"/>
-      <c r="AK8" s="733" t="n"/>
-      <c r="AL8" s="1148" t="n"/>
+      <c r="Y8" s="1270" t="n"/>
+      <c r="Z8" s="1270" t="n"/>
+      <c r="AA8" s="1270" t="n"/>
+      <c r="AB8" s="1270" t="n"/>
+      <c r="AC8" s="1270" t="n"/>
+      <c r="AD8" s="1270" t="n"/>
+      <c r="AE8" s="1270" t="n"/>
+      <c r="AF8" s="1270" t="n"/>
+      <c r="AG8" s="1270" t="n"/>
+      <c r="AH8" s="1270" t="n"/>
+      <c r="AI8" s="1270" t="n"/>
+      <c r="AJ8" s="1270" t="n"/>
+      <c r="AK8" s="1271" t="n"/>
       <c r="AN8" s="1149" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="724" t="n"/>
-      <c r="B9" s="1148" t="n"/>
+      <c r="A9" s="1272" t="n"/>
       <c r="F9" s="1149" t="n"/>
       <c r="G9" s="1008" t="n"/>
       <c r="H9" s="1012" t="n"/>
@@ -7511,12 +7725,10 @@
       <c r="AI9" s="1009" t="n"/>
       <c r="AJ9" s="1010" t="n"/>
       <c r="AK9" s="1010" t="n"/>
-      <c r="AL9" s="1148" t="n"/>
       <c r="AN9" s="1149" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1" thickBot="1">
-      <c r="A10" s="735" t="n"/>
-      <c r="B10" s="1148" t="n"/>
+      <c r="A10" s="1268" t="n"/>
       <c r="F10" s="1149" t="n"/>
       <c r="G10" s="1008" t="n"/>
       <c r="H10" s="1012" t="n"/>
@@ -7549,29 +7761,27 @@
       <c r="AI10" s="1009" t="n"/>
       <c r="AJ10" s="1010" t="n"/>
       <c r="AK10" s="1010" t="n"/>
-      <c r="AL10" s="1148" t="n"/>
       <c r="AN10" s="1149" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1" thickBot="1">
-      <c r="A11" s="1020" t="inlineStr">
+      <c r="A11" s="1244" t="inlineStr">
         <is>
           <t>ALC LD Wing</t>
         </is>
       </c>
-      <c r="B11" s="1148" t="n"/>
       <c r="F11" s="1149" t="n"/>
       <c r="G11" s="1008" t="n"/>
       <c r="H11" s="1012" t="n"/>
       <c r="I11" s="1012" t="n"/>
       <c r="J11" s="1013" t="n"/>
       <c r="K11" s="1013" t="n"/>
-      <c r="L11" s="1021" t="inlineStr">
+      <c r="L11" s="1273" t="inlineStr">
         <is>
           <t>TtT TFCC</t>
         </is>
       </c>
-      <c r="M11" s="739" t="n"/>
-      <c r="N11" s="740" t="n"/>
+      <c r="M11" s="1155" t="n"/>
+      <c r="N11" s="1156" t="n"/>
       <c r="O11" s="1012" t="n"/>
       <c r="P11" s="1012" t="n"/>
       <c r="Q11" s="1022" t="n"/>
@@ -7581,15 +7791,15 @@
       <c r="U11" s="1013" t="n"/>
       <c r="V11" s="1012" t="n"/>
       <c r="W11" s="1012" t="n"/>
-      <c r="X11" s="1021" t="inlineStr">
+      <c r="X11" s="1273" t="inlineStr">
         <is>
           <t>LEAD TEAMS BMC</t>
         </is>
       </c>
-      <c r="Y11" s="739" t="n"/>
-      <c r="Z11" s="739" t="n"/>
-      <c r="AA11" s="739" t="n"/>
-      <c r="AB11" s="740" t="n"/>
+      <c r="Y11" s="1155" t="n"/>
+      <c r="Z11" s="1155" t="n"/>
+      <c r="AA11" s="1155" t="n"/>
+      <c r="AB11" s="1156" t="n"/>
       <c r="AC11" s="1012" t="n"/>
       <c r="AD11" s="1012" t="n"/>
       <c r="AE11" s="1008" t="n"/>
@@ -7599,16 +7809,14 @@
       <c r="AI11" s="1009" t="n"/>
       <c r="AJ11" s="1010" t="n"/>
       <c r="AK11" s="1010" t="n"/>
-      <c r="AL11" s="1148" t="n"/>
       <c r="AN11" s="1149" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" thickBot="1">
-      <c r="A12" s="1027" t="inlineStr">
+      <c r="A12" s="1246" t="inlineStr">
         <is>
           <t>ALC ELDA Wing</t>
         </is>
       </c>
-      <c r="B12" s="1148" t="n"/>
       <c r="F12" s="1149" t="n"/>
       <c r="G12" s="1008" t="n"/>
       <c r="H12" s="1012" t="n"/>
@@ -7620,16 +7828,16 @@
       <c r="N12" s="1008" t="n"/>
       <c r="O12" s="1012" t="n"/>
       <c r="P12" s="1012" t="n"/>
-      <c r="Q12" s="1028" t="inlineStr">
+      <c r="Q12" s="1274" t="inlineStr">
         <is>
           <t>LEAD TEAMS BMC</t>
         </is>
       </c>
-      <c r="R12" s="744" t="n"/>
-      <c r="S12" s="744" t="n"/>
-      <c r="T12" s="744" t="n"/>
-      <c r="U12" s="744" t="n"/>
-      <c r="V12" s="745" t="n"/>
+      <c r="R12" s="1155" t="n"/>
+      <c r="S12" s="1155" t="n"/>
+      <c r="T12" s="1155" t="n"/>
+      <c r="U12" s="1155" t="n"/>
+      <c r="V12" s="1156" t="n"/>
       <c r="W12" s="1012" t="n"/>
       <c r="X12" s="1013" t="n"/>
       <c r="Y12" s="1008" t="n"/>
@@ -7638,27 +7846,25 @@
       <c r="AB12" s="1008" t="n"/>
       <c r="AC12" s="1012" t="n"/>
       <c r="AD12" s="1012" t="n"/>
-      <c r="AE12" s="1028" t="inlineStr">
+      <c r="AE12" s="1274" t="inlineStr">
         <is>
           <t>LEAD TEAMS LMC</t>
         </is>
       </c>
-      <c r="AF12" s="744" t="n"/>
-      <c r="AG12" s="744" t="n"/>
-      <c r="AH12" s="744" t="n"/>
-      <c r="AI12" s="744" t="n"/>
-      <c r="AJ12" s="745" t="n"/>
+      <c r="AF12" s="1155" t="n"/>
+      <c r="AG12" s="1155" t="n"/>
+      <c r="AH12" s="1155" t="n"/>
+      <c r="AI12" s="1155" t="n"/>
+      <c r="AJ12" s="1156" t="n"/>
       <c r="AK12" s="1010" t="n"/>
-      <c r="AL12" s="1148" t="n"/>
       <c r="AN12" s="1149" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="1030" t="inlineStr">
+      <c r="A13" s="1248" t="inlineStr">
         <is>
           <t>2 RTW</t>
         </is>
       </c>
-      <c r="B13" s="1148" t="n"/>
       <c r="F13" s="1149" t="n"/>
       <c r="G13" s="1008" t="n"/>
       <c r="H13" s="1012" t="n"/>
@@ -7684,27 +7890,25 @@
       <c r="AB13" s="1008" t="n"/>
       <c r="AC13" s="1012" t="n"/>
       <c r="AD13" s="1012" t="n"/>
-      <c r="AE13" s="1031" t="inlineStr">
+      <c r="AE13" s="1275" t="inlineStr">
         <is>
           <t>RF JNCO 27/02</t>
         </is>
       </c>
-      <c r="AF13" s="732" t="n"/>
-      <c r="AG13" s="732" t="n"/>
-      <c r="AH13" s="732" t="n"/>
-      <c r="AI13" s="732" t="n"/>
-      <c r="AJ13" s="732" t="n"/>
-      <c r="AK13" s="733" t="n"/>
-      <c r="AL13" s="1148" t="n"/>
+      <c r="AF13" s="1270" t="n"/>
+      <c r="AG13" s="1270" t="n"/>
+      <c r="AH13" s="1270" t="n"/>
+      <c r="AI13" s="1270" t="n"/>
+      <c r="AJ13" s="1270" t="n"/>
+      <c r="AK13" s="1271" t="n"/>
       <c r="AN13" s="1149" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="1033" t="inlineStr">
+      <c r="A14" s="1250" t="inlineStr">
         <is>
           <t>3 RTW</t>
         </is>
       </c>
-      <c r="B14" s="1148" t="n"/>
       <c r="F14" s="1149" t="n"/>
       <c r="G14" s="1034" t="n"/>
       <c r="H14" s="1012" t="n"/>
@@ -7716,41 +7920,39 @@
       <c r="N14" s="1034" t="n"/>
       <c r="O14" s="1012" t="n"/>
       <c r="P14" s="1012" t="n"/>
-      <c r="Q14" s="1035" t="inlineStr">
+      <c r="Q14" s="1276" t="inlineStr">
         <is>
           <t>RF JNCO 27/01</t>
         </is>
       </c>
-      <c r="R14" s="732" t="n"/>
-      <c r="S14" s="732" t="n"/>
-      <c r="T14" s="732" t="n"/>
-      <c r="U14" s="732" t="n"/>
-      <c r="V14" s="732" t="n"/>
-      <c r="W14" s="732" t="n"/>
-      <c r="X14" s="732" t="n"/>
-      <c r="Y14" s="732" t="n"/>
-      <c r="Z14" s="732" t="n"/>
-      <c r="AA14" s="732" t="n"/>
-      <c r="AB14" s="732" t="n"/>
-      <c r="AC14" s="732" t="n"/>
-      <c r="AD14" s="732" t="n"/>
-      <c r="AE14" s="732" t="n"/>
-      <c r="AF14" s="732" t="n"/>
-      <c r="AG14" s="732" t="n"/>
-      <c r="AH14" s="732" t="n"/>
-      <c r="AI14" s="732" t="n"/>
-      <c r="AJ14" s="732" t="n"/>
-      <c r="AK14" s="733" t="n"/>
-      <c r="AL14" s="1148" t="n"/>
+      <c r="R14" s="1270" t="n"/>
+      <c r="S14" s="1270" t="n"/>
+      <c r="T14" s="1270" t="n"/>
+      <c r="U14" s="1270" t="n"/>
+      <c r="V14" s="1270" t="n"/>
+      <c r="W14" s="1270" t="n"/>
+      <c r="X14" s="1270" t="n"/>
+      <c r="Y14" s="1270" t="n"/>
+      <c r="Z14" s="1270" t="n"/>
+      <c r="AA14" s="1270" t="n"/>
+      <c r="AB14" s="1270" t="n"/>
+      <c r="AC14" s="1270" t="n"/>
+      <c r="AD14" s="1270" t="n"/>
+      <c r="AE14" s="1270" t="n"/>
+      <c r="AF14" s="1270" t="n"/>
+      <c r="AG14" s="1270" t="n"/>
+      <c r="AH14" s="1270" t="n"/>
+      <c r="AI14" s="1270" t="n"/>
+      <c r="AJ14" s="1270" t="n"/>
+      <c r="AK14" s="1271" t="n"/>
       <c r="AN14" s="1149" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="1037" t="inlineStr">
+      <c r="A15" s="1252" t="inlineStr">
         <is>
           <t>SNCO Wing</t>
         </is>
       </c>
-      <c r="B15" s="1148" t="n"/>
       <c r="F15" s="1149" t="n"/>
       <c r="G15" s="1008" t="n"/>
       <c r="H15" s="1012" t="n"/>
@@ -7783,16 +7985,15 @@
       <c r="AI15" s="1009" t="n"/>
       <c r="AJ15" s="1010" t="n"/>
       <c r="AK15" s="1010" t="n"/>
-      <c r="AL15" s="1148" t="n"/>
       <c r="AN15" s="1149" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1" thickBot="1">
-      <c r="A16" s="1039" t="inlineStr">
+      <c r="A16" s="1253" t="inlineStr">
         <is>
           <t>WO Wing</t>
         </is>
       </c>
-      <c r="B16" s="1154" t="n"/>
+      <c r="B16" s="1155" t="n"/>
       <c r="C16" s="1155" t="n"/>
       <c r="D16" s="1155" t="n"/>
       <c r="E16" s="1155" t="n"/>
@@ -7828,7 +8029,7 @@
       <c r="AI16" s="1009" t="n"/>
       <c r="AJ16" s="1010" t="n"/>
       <c r="AK16" s="1010" t="n"/>
-      <c r="AL16" s="1154" t="n"/>
+      <c r="AL16" s="1155" t="n"/>
       <c r="AM16" s="1155" t="n"/>
       <c r="AN16" s="1156" t="n"/>
     </row>
@@ -7875,114 +8076,106 @@
       <c r="AN17" s="1225" t="n"/>
     </row>
     <row r="18" ht="14" customHeight="1">
-      <c r="A18" s="1227" t="inlineStr">
+      <c r="A18" s="1236" t="inlineStr">
         <is>
           <t>February</t>
         </is>
       </c>
-      <c r="B18" s="1041" t="n"/>
-      <c r="C18" s="1146" t="n"/>
-      <c r="D18" s="1146" t="n"/>
-      <c r="E18" s="1146" t="n"/>
-      <c r="F18" s="1146" t="n"/>
-      <c r="G18" s="1146" t="n"/>
-      <c r="H18" s="1146" t="n"/>
-      <c r="I18" s="1147" t="n"/>
-      <c r="J18" s="720" t="n">
+      <c r="B18" s="1277" t="n"/>
+      <c r="I18" s="1149" t="n"/>
+      <c r="J18" s="1238" t="n">
         <v>1</v>
       </c>
-      <c r="K18" s="720" t="n">
+      <c r="K18" s="1238" t="n">
         <v>2</v>
       </c>
-      <c r="L18" s="720" t="n">
+      <c r="L18" s="1238" t="n">
         <v>3</v>
       </c>
-      <c r="M18" s="720" t="n">
+      <c r="M18" s="1238" t="n">
         <v>4</v>
       </c>
-      <c r="N18" s="720" t="n">
+      <c r="N18" s="1238" t="n">
         <v>5</v>
       </c>
-      <c r="O18" s="721" t="n">
+      <c r="O18" s="1239" t="n">
         <v>6</v>
       </c>
-      <c r="P18" s="721" t="n">
+      <c r="P18" s="1239" t="n">
         <v>7</v>
       </c>
-      <c r="Q18" s="720" t="n">
+      <c r="Q18" s="1238" t="n">
         <v>8</v>
       </c>
-      <c r="R18" s="720" t="n">
+      <c r="R18" s="1238" t="n">
         <v>9</v>
       </c>
-      <c r="S18" s="720" t="n">
+      <c r="S18" s="1238" t="n">
         <v>10</v>
       </c>
-      <c r="T18" s="720" t="n">
+      <c r="T18" s="1238" t="n">
         <v>11</v>
       </c>
-      <c r="U18" s="720" t="n">
+      <c r="U18" s="1238" t="n">
         <v>12</v>
       </c>
-      <c r="V18" s="721" t="n">
+      <c r="V18" s="1239" t="n">
         <v>13</v>
       </c>
-      <c r="W18" s="721" t="n">
+      <c r="W18" s="1239" t="n">
         <v>14</v>
       </c>
-      <c r="X18" s="720" t="n">
+      <c r="X18" s="1238" t="n">
         <v>15</v>
       </c>
-      <c r="Y18" s="720" t="n">
+      <c r="Y18" s="1238" t="n">
         <v>16</v>
       </c>
-      <c r="Z18" s="720" t="n">
+      <c r="Z18" s="1238" t="n">
         <v>17</v>
       </c>
-      <c r="AA18" s="720" t="n">
+      <c r="AA18" s="1238" t="n">
         <v>18</v>
       </c>
-      <c r="AB18" s="720" t="n">
+      <c r="AB18" s="1238" t="n">
         <v>19</v>
       </c>
-      <c r="AC18" s="721" t="n">
+      <c r="AC18" s="1239" t="n">
         <v>20</v>
       </c>
-      <c r="AD18" s="721" t="n">
+      <c r="AD18" s="1239" t="n">
         <v>21</v>
       </c>
-      <c r="AE18" s="720" t="n">
+      <c r="AE18" s="1238" t="n">
         <v>22</v>
       </c>
-      <c r="AF18" s="720" t="n">
+      <c r="AF18" s="1238" t="n">
         <v>23</v>
       </c>
-      <c r="AG18" s="720" t="n">
+      <c r="AG18" s="1238" t="n">
         <v>24</v>
       </c>
-      <c r="AH18" s="720" t="n">
+      <c r="AH18" s="1238" t="n">
         <v>25</v>
       </c>
-      <c r="AI18" s="720" t="n">
+      <c r="AI18" s="1238" t="n">
         <v>26</v>
       </c>
-      <c r="AJ18" s="721" t="n">
+      <c r="AJ18" s="1239" t="n">
         <v>27</v>
       </c>
-      <c r="AK18" s="721" t="n">
+      <c r="AK18" s="1239" t="n">
         <v>28</v>
       </c>
-      <c r="AL18" s="1042" t="n"/>
-      <c r="AM18" s="1146" t="n"/>
-      <c r="AN18" s="1147" t="n"/>
+      <c r="AL18" s="1278" t="n"/>
+      <c r="AN18" s="1149" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1" thickBot="1">
-      <c r="A19" s="1206" t="inlineStr">
+      <c r="A19" s="1241" t="inlineStr">
         <is>
           <t>ACS</t>
         </is>
       </c>
-      <c r="B19" s="1148" t="n"/>
       <c r="I19" s="1149" t="n"/>
       <c r="J19" s="1024" t="n"/>
       <c r="K19" s="1024" t="n"/>
@@ -8012,12 +8205,10 @@
       <c r="AI19" s="1024" t="n"/>
       <c r="AJ19" s="1045" t="n"/>
       <c r="AK19" s="1045" t="n"/>
-      <c r="AL19" s="1148" t="n"/>
       <c r="AN19" s="1149" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="729" t="n"/>
-      <c r="B20" s="1148" t="n"/>
+      <c r="A20" s="1268" t="n"/>
       <c r="I20" s="1149" t="n"/>
       <c r="J20" s="1024" t="n"/>
       <c r="K20" s="1024" t="n"/>
@@ -8047,33 +8238,31 @@
       <c r="AI20" s="1024" t="n"/>
       <c r="AJ20" s="1045" t="n"/>
       <c r="AK20" s="1045" t="n"/>
-      <c r="AL20" s="1148" t="n"/>
       <c r="AN20" s="1149" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="1211" t="inlineStr">
+      <c r="A21" s="1242" t="inlineStr">
         <is>
           <t>OCS (NZ)</t>
         </is>
       </c>
-      <c r="B21" s="1148" t="n"/>
       <c r="I21" s="1149" t="n"/>
-      <c r="J21" s="1048" t="inlineStr">
+      <c r="J21" s="1269" t="inlineStr">
         <is>
           <t>TFCC</t>
         </is>
       </c>
-      <c r="K21" s="732" t="n"/>
-      <c r="L21" s="732" t="n"/>
-      <c r="M21" s="732" t="n"/>
-      <c r="N21" s="732" t="n"/>
-      <c r="O21" s="732" t="n"/>
-      <c r="P21" s="732" t="n"/>
-      <c r="Q21" s="732" t="n"/>
-      <c r="R21" s="732" t="n"/>
-      <c r="S21" s="732" t="n"/>
-      <c r="T21" s="732" t="n"/>
-      <c r="U21" s="765" t="n"/>
+      <c r="K21" s="1270" t="n"/>
+      <c r="L21" s="1270" t="n"/>
+      <c r="M21" s="1270" t="n"/>
+      <c r="N21" s="1270" t="n"/>
+      <c r="O21" s="1270" t="n"/>
+      <c r="P21" s="1270" t="n"/>
+      <c r="Q21" s="1270" t="n"/>
+      <c r="R21" s="1270" t="n"/>
+      <c r="S21" s="1270" t="n"/>
+      <c r="T21" s="1270" t="n"/>
+      <c r="U21" s="1271" t="n"/>
       <c r="V21" s="1015" t="n"/>
       <c r="W21" s="1015" t="n"/>
       <c r="X21" s="1024" t="n"/>
@@ -8090,75 +8279,71 @@
       <c r="AI21" s="1024" t="n"/>
       <c r="AJ21" s="1045" t="n"/>
       <c r="AK21" s="1045" t="n"/>
-      <c r="AL21" s="1148" t="n"/>
       <c r="AN21" s="1149" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="726" t="n"/>
-      <c r="B22" s="1148" t="n"/>
+      <c r="A22" s="1272" t="n"/>
       <c r="I22" s="1149" t="n"/>
-      <c r="J22" s="1049" t="inlineStr">
+      <c r="J22" s="1269" t="inlineStr">
         <is>
           <t>IIT</t>
         </is>
       </c>
-      <c r="K22" s="732" t="n"/>
-      <c r="L22" s="732" t="n"/>
-      <c r="M22" s="732" t="n"/>
-      <c r="N22" s="732" t="n"/>
-      <c r="O22" s="732" t="n"/>
-      <c r="P22" s="732" t="n"/>
-      <c r="Q22" s="732" t="n"/>
-      <c r="R22" s="732" t="n"/>
-      <c r="S22" s="732" t="n"/>
-      <c r="T22" s="732" t="n"/>
-      <c r="U22" s="732" t="n"/>
-      <c r="V22" s="732" t="n"/>
-      <c r="W22" s="732" t="n"/>
-      <c r="X22" s="732" t="n"/>
-      <c r="Y22" s="732" t="n"/>
-      <c r="Z22" s="732" t="n"/>
-      <c r="AA22" s="732" t="n"/>
-      <c r="AB22" s="732" t="n"/>
-      <c r="AC22" s="732" t="n"/>
-      <c r="AD22" s="732" t="n"/>
-      <c r="AE22" s="732" t="n"/>
-      <c r="AF22" s="732" t="n"/>
-      <c r="AG22" s="732" t="n"/>
-      <c r="AH22" s="732" t="n"/>
-      <c r="AI22" s="732" t="n"/>
-      <c r="AJ22" s="732" t="n"/>
-      <c r="AK22" s="733" t="n"/>
-      <c r="AL22" s="1148" t="n"/>
+      <c r="K22" s="1270" t="n"/>
+      <c r="L22" s="1270" t="n"/>
+      <c r="M22" s="1270" t="n"/>
+      <c r="N22" s="1270" t="n"/>
+      <c r="O22" s="1270" t="n"/>
+      <c r="P22" s="1270" t="n"/>
+      <c r="Q22" s="1270" t="n"/>
+      <c r="R22" s="1270" t="n"/>
+      <c r="S22" s="1270" t="n"/>
+      <c r="T22" s="1270" t="n"/>
+      <c r="U22" s="1270" t="n"/>
+      <c r="V22" s="1270" t="n"/>
+      <c r="W22" s="1270" t="n"/>
+      <c r="X22" s="1270" t="n"/>
+      <c r="Y22" s="1270" t="n"/>
+      <c r="Z22" s="1270" t="n"/>
+      <c r="AA22" s="1270" t="n"/>
+      <c r="AB22" s="1270" t="n"/>
+      <c r="AC22" s="1270" t="n"/>
+      <c r="AD22" s="1270" t="n"/>
+      <c r="AE22" s="1270" t="n"/>
+      <c r="AF22" s="1270" t="n"/>
+      <c r="AG22" s="1270" t="n"/>
+      <c r="AH22" s="1270" t="n"/>
+      <c r="AI22" s="1270" t="n"/>
+      <c r="AJ22" s="1270" t="n"/>
+      <c r="AK22" s="1271" t="n"/>
       <c r="AN22" s="1149" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1" thickBot="1">
-      <c r="A23" s="726" t="n"/>
-      <c r="B23" s="1148" t="n"/>
+      <c r="A23" s="1272" t="n"/>
       <c r="I23" s="1149" t="n"/>
       <c r="J23" s="1024" t="n"/>
       <c r="K23" s="1024" t="n"/>
       <c r="L23" s="1024" t="n"/>
-      <c r="M23" s="1050" t="inlineStr">
+      <c r="M23" s="1269" t="inlineStr">
         <is>
           <t>RANGE PACKAGE</t>
         </is>
       </c>
-      <c r="N23" s="732" t="n"/>
-      <c r="O23" s="732" t="n"/>
-      <c r="P23" s="732" t="n"/>
-      <c r="Q23" s="732" t="n"/>
-      <c r="R23" s="732" t="n"/>
-      <c r="S23" s="732" t="n"/>
-      <c r="T23" s="732" t="n"/>
-      <c r="U23" s="732" t="n"/>
-      <c r="V23" s="732" t="n"/>
-      <c r="W23" s="732" t="n"/>
-      <c r="X23" s="732" t="n"/>
-      <c r="Y23" s="732" t="n"/>
-      <c r="Z23" s="732" t="n"/>
-      <c r="AA23" s="732" t="n"/>
-      <c r="AB23" s="765" t="n"/>
+      <c r="N23" s="1270" t="n"/>
+      <c r="O23" s="1270" t="n"/>
+      <c r="P23" s="1270" t="n"/>
+      <c r="Q23" s="1270" t="n"/>
+      <c r="R23" s="1270" t="n"/>
+      <c r="S23" s="1270" t="n"/>
+      <c r="T23" s="1270" t="n"/>
+      <c r="U23" s="1270" t="n"/>
+      <c r="V23" s="1270" t="n"/>
+      <c r="W23" s="1270" t="n"/>
+      <c r="X23" s="1270" t="n"/>
+      <c r="Y23" s="1270" t="n"/>
+      <c r="Z23" s="1270" t="n"/>
+      <c r="AA23" s="1270" t="n"/>
+      <c r="AB23" s="1271" t="n"/>
       <c r="AC23" s="1015" t="n"/>
       <c r="AD23" s="1015" t="n"/>
       <c r="AE23" s="1024" t="n"/>
@@ -8168,22 +8353,20 @@
       <c r="AI23" s="1024" t="n"/>
       <c r="AJ23" s="1045" t="n"/>
       <c r="AK23" s="1045" t="n"/>
-      <c r="AL23" s="1148" t="n"/>
       <c r="AN23" s="1149" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="729" t="n"/>
-      <c r="B24" s="1148" t="n"/>
+      <c r="A24" s="1268" t="n"/>
       <c r="I24" s="1149" t="n"/>
-      <c r="J24" s="1051" t="inlineStr">
+      <c r="J24" s="1273" t="inlineStr">
         <is>
           <t>LEAD TEAMS LMC</t>
         </is>
       </c>
-      <c r="K24" s="739" t="n"/>
-      <c r="L24" s="739" t="n"/>
-      <c r="M24" s="739" t="n"/>
-      <c r="N24" s="740" t="n"/>
+      <c r="K24" s="1155" t="n"/>
+      <c r="L24" s="1155" t="n"/>
+      <c r="M24" s="1155" t="n"/>
+      <c r="N24" s="1156" t="n"/>
       <c r="O24" s="1015" t="n"/>
       <c r="P24" s="1015" t="n"/>
       <c r="Q24" s="1043" t="n"/>
@@ -8193,15 +8376,15 @@
       <c r="U24" s="1024" t="n"/>
       <c r="V24" s="1012" t="n"/>
       <c r="W24" s="1012" t="n"/>
-      <c r="X24" s="1021" t="inlineStr">
+      <c r="X24" s="1273" t="inlineStr">
         <is>
           <t>LEAD LEADERS BMC</t>
         </is>
       </c>
-      <c r="Y24" s="739" t="n"/>
-      <c r="Z24" s="739" t="n"/>
-      <c r="AA24" s="739" t="n"/>
-      <c r="AB24" s="740" t="n"/>
+      <c r="Y24" s="1155" t="n"/>
+      <c r="Z24" s="1155" t="n"/>
+      <c r="AA24" s="1155" t="n"/>
+      <c r="AB24" s="1156" t="n"/>
       <c r="AC24" s="1012" t="n"/>
       <c r="AD24" s="1012" t="n"/>
       <c r="AE24" s="1024" t="n"/>
@@ -8211,16 +8394,14 @@
       <c r="AI24" s="1024" t="n"/>
       <c r="AJ24" s="1045" t="n"/>
       <c r="AK24" s="1045" t="n"/>
-      <c r="AL24" s="1148" t="n"/>
       <c r="AN24" s="1149" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1" thickBot="1">
-      <c r="A25" s="1020" t="inlineStr">
+      <c r="A25" s="1244" t="inlineStr">
         <is>
           <t>ALC LD Wing</t>
         </is>
       </c>
-      <c r="B25" s="1148" t="n"/>
       <c r="I25" s="1149" t="n"/>
       <c r="J25" s="1024" t="n"/>
       <c r="K25" s="1024" t="n"/>
@@ -8229,16 +8410,16 @@
       <c r="N25" s="1008" t="n"/>
       <c r="O25" s="1012" t="n"/>
       <c r="P25" s="1012" t="n"/>
-      <c r="Q25" s="1028" t="inlineStr">
+      <c r="Q25" s="1274" t="inlineStr">
         <is>
           <t>LEAD LEADERS BMC</t>
         </is>
       </c>
-      <c r="R25" s="744" t="n"/>
-      <c r="S25" s="744" t="n"/>
-      <c r="T25" s="744" t="n"/>
-      <c r="U25" s="744" t="n"/>
-      <c r="V25" s="745" t="n"/>
+      <c r="R25" s="1155" t="n"/>
+      <c r="S25" s="1155" t="n"/>
+      <c r="T25" s="1155" t="n"/>
+      <c r="U25" s="1155" t="n"/>
+      <c r="V25" s="1156" t="n"/>
       <c r="W25" s="1012" t="n"/>
       <c r="X25" s="1024" t="n"/>
       <c r="Y25" s="1024" t="n"/>
@@ -8247,27 +8428,25 @@
       <c r="AB25" s="1024" t="n"/>
       <c r="AC25" s="1012" t="n"/>
       <c r="AD25" s="1012" t="n"/>
-      <c r="AE25" s="1028" t="inlineStr">
+      <c r="AE25" s="1274" t="inlineStr">
         <is>
           <t>LEAD LEADERS OFFICER</t>
         </is>
       </c>
-      <c r="AF25" s="744" t="n"/>
-      <c r="AG25" s="744" t="n"/>
-      <c r="AH25" s="744" t="n"/>
-      <c r="AI25" s="744" t="n"/>
-      <c r="AJ25" s="745" t="n"/>
+      <c r="AF25" s="1155" t="n"/>
+      <c r="AG25" s="1155" t="n"/>
+      <c r="AH25" s="1155" t="n"/>
+      <c r="AI25" s="1155" t="n"/>
+      <c r="AJ25" s="1156" t="n"/>
       <c r="AK25" s="1045" t="n"/>
-      <c r="AL25" s="1148" t="n"/>
       <c r="AN25" s="1149" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="1027" t="inlineStr">
+      <c r="A26" s="1246" t="inlineStr">
         <is>
           <t>ALC ELDA Wing</t>
         </is>
       </c>
-      <c r="B26" s="1148" t="n"/>
       <c r="I26" s="1149" t="n"/>
       <c r="J26" s="1024" t="n"/>
       <c r="K26" s="1024" t="n"/>
@@ -8297,102 +8476,96 @@
       <c r="AI26" s="1024" t="n"/>
       <c r="AJ26" s="1045" t="n"/>
       <c r="AK26" s="1045" t="n"/>
-      <c r="AL26" s="1148" t="n"/>
       <c r="AN26" s="1149" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="1030" t="inlineStr">
+      <c r="A27" s="1248" t="inlineStr">
         <is>
           <t>2 RTW</t>
         </is>
       </c>
-      <c r="B27" s="1148" t="n"/>
       <c r="I27" s="1149" t="n"/>
-      <c r="J27" s="1054" t="inlineStr">
+      <c r="J27" s="1275" t="inlineStr">
         <is>
           <t>RF JNCO 27/02</t>
         </is>
       </c>
-      <c r="K27" s="732" t="n"/>
-      <c r="L27" s="732" t="n"/>
-      <c r="M27" s="732" t="n"/>
-      <c r="N27" s="732" t="n"/>
-      <c r="O27" s="732" t="n"/>
-      <c r="P27" s="732" t="n"/>
-      <c r="Q27" s="732" t="n"/>
-      <c r="R27" s="732" t="n"/>
-      <c r="S27" s="732" t="n"/>
-      <c r="T27" s="732" t="n"/>
-      <c r="U27" s="732" t="n"/>
-      <c r="V27" s="732" t="n"/>
-      <c r="W27" s="732" t="n"/>
-      <c r="X27" s="732" t="n"/>
-      <c r="Y27" s="732" t="n"/>
-      <c r="Z27" s="732" t="n"/>
-      <c r="AA27" s="732" t="n"/>
-      <c r="AB27" s="732" t="n"/>
-      <c r="AC27" s="732" t="n"/>
-      <c r="AD27" s="732" t="n"/>
-      <c r="AE27" s="732" t="n"/>
-      <c r="AF27" s="732" t="n"/>
-      <c r="AG27" s="732" t="n"/>
-      <c r="AH27" s="732" t="n"/>
-      <c r="AI27" s="732" t="n"/>
-      <c r="AJ27" s="732" t="n"/>
-      <c r="AK27" s="733" t="n"/>
-      <c r="AL27" s="1148" t="n"/>
+      <c r="K27" s="1270" t="n"/>
+      <c r="L27" s="1270" t="n"/>
+      <c r="M27" s="1270" t="n"/>
+      <c r="N27" s="1270" t="n"/>
+      <c r="O27" s="1270" t="n"/>
+      <c r="P27" s="1270" t="n"/>
+      <c r="Q27" s="1270" t="n"/>
+      <c r="R27" s="1270" t="n"/>
+      <c r="S27" s="1270" t="n"/>
+      <c r="T27" s="1270" t="n"/>
+      <c r="U27" s="1270" t="n"/>
+      <c r="V27" s="1270" t="n"/>
+      <c r="W27" s="1270" t="n"/>
+      <c r="X27" s="1270" t="n"/>
+      <c r="Y27" s="1270" t="n"/>
+      <c r="Z27" s="1270" t="n"/>
+      <c r="AA27" s="1270" t="n"/>
+      <c r="AB27" s="1270" t="n"/>
+      <c r="AC27" s="1270" t="n"/>
+      <c r="AD27" s="1270" t="n"/>
+      <c r="AE27" s="1270" t="n"/>
+      <c r="AF27" s="1270" t="n"/>
+      <c r="AG27" s="1270" t="n"/>
+      <c r="AH27" s="1270" t="n"/>
+      <c r="AI27" s="1270" t="n"/>
+      <c r="AJ27" s="1270" t="n"/>
+      <c r="AK27" s="1271" t="n"/>
       <c r="AN27" s="1149" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="1033" t="inlineStr">
+      <c r="A28" s="1250" t="inlineStr">
         <is>
           <t>3 RTW</t>
         </is>
       </c>
-      <c r="B28" s="1148" t="n"/>
       <c r="I28" s="1149" t="n"/>
-      <c r="J28" s="1056" t="inlineStr">
+      <c r="J28" s="1276" t="inlineStr">
         <is>
           <t>RF JNCO 27/01</t>
         </is>
       </c>
-      <c r="K28" s="732" t="n"/>
-      <c r="L28" s="732" t="n"/>
-      <c r="M28" s="732" t="n"/>
-      <c r="N28" s="732" t="n"/>
-      <c r="O28" s="732" t="n"/>
-      <c r="P28" s="732" t="n"/>
-      <c r="Q28" s="732" t="n"/>
-      <c r="R28" s="732" t="n"/>
-      <c r="S28" s="732" t="n"/>
-      <c r="T28" s="732" t="n"/>
-      <c r="U28" s="732" t="n"/>
-      <c r="V28" s="732" t="n"/>
-      <c r="W28" s="732" t="n"/>
-      <c r="X28" s="732" t="n"/>
-      <c r="Y28" s="732" t="n"/>
-      <c r="Z28" s="732" t="n"/>
-      <c r="AA28" s="732" t="n"/>
-      <c r="AB28" s="732" t="n"/>
-      <c r="AC28" s="732" t="n"/>
-      <c r="AD28" s="732" t="n"/>
-      <c r="AE28" s="732" t="n"/>
-      <c r="AF28" s="732" t="n"/>
-      <c r="AG28" s="732" t="n"/>
-      <c r="AH28" s="732" t="n"/>
-      <c r="AI28" s="732" t="n"/>
-      <c r="AJ28" s="732" t="n"/>
-      <c r="AK28" s="733" t="n"/>
-      <c r="AL28" s="1148" t="n"/>
+      <c r="K28" s="1270" t="n"/>
+      <c r="L28" s="1270" t="n"/>
+      <c r="M28" s="1270" t="n"/>
+      <c r="N28" s="1270" t="n"/>
+      <c r="O28" s="1270" t="n"/>
+      <c r="P28" s="1270" t="n"/>
+      <c r="Q28" s="1270" t="n"/>
+      <c r="R28" s="1270" t="n"/>
+      <c r="S28" s="1270" t="n"/>
+      <c r="T28" s="1270" t="n"/>
+      <c r="U28" s="1270" t="n"/>
+      <c r="V28" s="1270" t="n"/>
+      <c r="W28" s="1270" t="n"/>
+      <c r="X28" s="1270" t="n"/>
+      <c r="Y28" s="1270" t="n"/>
+      <c r="Z28" s="1270" t="n"/>
+      <c r="AA28" s="1270" t="n"/>
+      <c r="AB28" s="1270" t="n"/>
+      <c r="AC28" s="1270" t="n"/>
+      <c r="AD28" s="1270" t="n"/>
+      <c r="AE28" s="1270" t="n"/>
+      <c r="AF28" s="1270" t="n"/>
+      <c r="AG28" s="1270" t="n"/>
+      <c r="AH28" s="1270" t="n"/>
+      <c r="AI28" s="1270" t="n"/>
+      <c r="AJ28" s="1270" t="n"/>
+      <c r="AK28" s="1271" t="n"/>
       <c r="AN28" s="1149" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1" thickBot="1">
-      <c r="A29" s="1037" t="inlineStr">
+      <c r="A29" s="1252" t="inlineStr">
         <is>
           <t>SNCO Wing</t>
         </is>
       </c>
-      <c r="B29" s="1148" t="n"/>
       <c r="I29" s="1149" t="n"/>
       <c r="J29" s="1024" t="n"/>
       <c r="K29" s="1024" t="n"/>
@@ -8401,41 +8574,40 @@
       <c r="N29" s="1008" t="n"/>
       <c r="O29" s="1012" t="n"/>
       <c r="P29" s="1012" t="n"/>
-      <c r="Q29" s="1058" t="inlineStr">
+      <c r="Q29" s="1279" t="inlineStr">
         <is>
           <t>RF SNCO 27/01</t>
         </is>
       </c>
-      <c r="R29" s="732" t="n"/>
-      <c r="S29" s="732" t="n"/>
-      <c r="T29" s="732" t="n"/>
-      <c r="U29" s="732" t="n"/>
-      <c r="V29" s="732" t="n"/>
-      <c r="W29" s="732" t="n"/>
-      <c r="X29" s="732" t="n"/>
-      <c r="Y29" s="732" t="n"/>
-      <c r="Z29" s="732" t="n"/>
-      <c r="AA29" s="732" t="n"/>
-      <c r="AB29" s="732" t="n"/>
-      <c r="AC29" s="732" t="n"/>
-      <c r="AD29" s="732" t="n"/>
-      <c r="AE29" s="732" t="n"/>
-      <c r="AF29" s="732" t="n"/>
-      <c r="AG29" s="732" t="n"/>
-      <c r="AH29" s="732" t="n"/>
-      <c r="AI29" s="732" t="n"/>
-      <c r="AJ29" s="732" t="n"/>
-      <c r="AK29" s="733" t="n"/>
-      <c r="AL29" s="1148" t="n"/>
+      <c r="R29" s="1270" t="n"/>
+      <c r="S29" s="1270" t="n"/>
+      <c r="T29" s="1270" t="n"/>
+      <c r="U29" s="1270" t="n"/>
+      <c r="V29" s="1270" t="n"/>
+      <c r="W29" s="1270" t="n"/>
+      <c r="X29" s="1270" t="n"/>
+      <c r="Y29" s="1270" t="n"/>
+      <c r="Z29" s="1270" t="n"/>
+      <c r="AA29" s="1270" t="n"/>
+      <c r="AB29" s="1270" t="n"/>
+      <c r="AC29" s="1270" t="n"/>
+      <c r="AD29" s="1270" t="n"/>
+      <c r="AE29" s="1270" t="n"/>
+      <c r="AF29" s="1270" t="n"/>
+      <c r="AG29" s="1270" t="n"/>
+      <c r="AH29" s="1270" t="n"/>
+      <c r="AI29" s="1270" t="n"/>
+      <c r="AJ29" s="1270" t="n"/>
+      <c r="AK29" s="1271" t="n"/>
       <c r="AN29" s="1149" t="n"/>
     </row>
     <row r="30" ht="15" customHeight="1" thickBot="1">
-      <c r="A30" s="1039" t="inlineStr">
+      <c r="A30" s="1253" t="inlineStr">
         <is>
           <t>WO Wing</t>
         </is>
       </c>
-      <c r="B30" s="1154" t="n"/>
+      <c r="B30" s="1155" t="n"/>
       <c r="C30" s="1155" t="n"/>
       <c r="D30" s="1155" t="n"/>
       <c r="E30" s="1155" t="n"/>
@@ -8471,7 +8643,7 @@
       <c r="AI30" s="1024" t="n"/>
       <c r="AJ30" s="1045" t="n"/>
       <c r="AK30" s="1045" t="n"/>
-      <c r="AL30" s="1154" t="n"/>
+      <c r="AL30" s="1155" t="n"/>
       <c r="AM30" s="1155" t="n"/>
       <c r="AN30" s="1156" t="n"/>
     </row>
@@ -8518,120 +8690,113 @@
       <c r="AN31" s="1225" t="n"/>
     </row>
     <row r="32" ht="14" customHeight="1" thickBot="1">
-      <c r="A32" s="1227" t="inlineStr">
+      <c r="A32" s="1236" t="inlineStr">
         <is>
           <t>March</t>
         </is>
       </c>
-      <c r="B32" s="1042" t="n"/>
-      <c r="C32" s="1146" t="n"/>
-      <c r="D32" s="1146" t="n"/>
-      <c r="E32" s="1146" t="n"/>
-      <c r="F32" s="1146" t="n"/>
-      <c r="G32" s="1146" t="n"/>
-      <c r="H32" s="1146" t="n"/>
-      <c r="I32" s="1147" t="n"/>
-      <c r="J32" s="720" t="n">
+      <c r="B32" s="1278" t="n"/>
+      <c r="I32" s="1149" t="n"/>
+      <c r="J32" s="1238" t="n">
         <v>1</v>
       </c>
-      <c r="K32" s="720" t="n">
+      <c r="K32" s="1238" t="n">
         <v>2</v>
       </c>
-      <c r="L32" s="720" t="n">
+      <c r="L32" s="1238" t="n">
         <v>3</v>
       </c>
-      <c r="M32" s="720" t="n">
+      <c r="M32" s="1238" t="n">
         <v>4</v>
       </c>
-      <c r="N32" s="720" t="n">
+      <c r="N32" s="1238" t="n">
         <v>5</v>
       </c>
-      <c r="O32" s="721" t="n">
+      <c r="O32" s="1239" t="n">
         <v>6</v>
       </c>
-      <c r="P32" s="721" t="n">
+      <c r="P32" s="1239" t="n">
         <v>7</v>
       </c>
-      <c r="Q32" s="720" t="n">
+      <c r="Q32" s="1238" t="n">
         <v>8</v>
       </c>
-      <c r="R32" s="720" t="n">
+      <c r="R32" s="1238" t="n">
         <v>9</v>
       </c>
-      <c r="S32" s="720" t="n">
+      <c r="S32" s="1238" t="n">
         <v>10</v>
       </c>
-      <c r="T32" s="720" t="n">
+      <c r="T32" s="1238" t="n">
         <v>11</v>
       </c>
-      <c r="U32" s="720" t="n">
+      <c r="U32" s="1238" t="n">
         <v>12</v>
       </c>
-      <c r="V32" s="721" t="n">
+      <c r="V32" s="1239" t="n">
         <v>13</v>
       </c>
-      <c r="W32" s="721" t="n">
+      <c r="W32" s="1239" t="n">
         <v>14</v>
       </c>
-      <c r="X32" s="720" t="n">
+      <c r="X32" s="1238" t="n">
         <v>15</v>
       </c>
-      <c r="Y32" s="720" t="n">
+      <c r="Y32" s="1238" t="n">
         <v>16</v>
       </c>
-      <c r="Z32" s="720" t="n">
+      <c r="Z32" s="1238" t="n">
         <v>17</v>
       </c>
-      <c r="AA32" s="720" t="n">
+      <c r="AA32" s="1238" t="n">
         <v>18</v>
       </c>
-      <c r="AB32" s="720" t="n">
+      <c r="AB32" s="1238" t="n">
         <v>19</v>
       </c>
-      <c r="AC32" s="721" t="n">
+      <c r="AC32" s="1239" t="n">
         <v>20</v>
       </c>
-      <c r="AD32" s="721" t="n">
+      <c r="AD32" s="1239" t="n">
         <v>21</v>
       </c>
-      <c r="AE32" s="720" t="n">
+      <c r="AE32" s="1238" t="n">
         <v>22</v>
       </c>
-      <c r="AF32" s="720" t="n">
+      <c r="AF32" s="1238" t="n">
         <v>23</v>
       </c>
-      <c r="AG32" s="720" t="n">
+      <c r="AG32" s="1238" t="n">
         <v>24</v>
       </c>
-      <c r="AH32" s="720" t="n">
+      <c r="AH32" s="1238" t="n">
         <v>25</v>
       </c>
-      <c r="AI32" s="720" t="n">
+      <c r="AI32" s="1238" t="n">
         <v>26</v>
       </c>
-      <c r="AJ32" s="721" t="n">
+      <c r="AJ32" s="1239" t="n">
         <v>27</v>
       </c>
-      <c r="AK32" s="721" t="n">
+      <c r="AK32" s="1239" t="n">
         <v>28</v>
       </c>
-      <c r="AL32" s="720" t="n">
+      <c r="AL32" s="1238" t="n">
         <v>29</v>
       </c>
-      <c r="AM32" s="720" t="n">
+      <c r="AM32" s="1238" t="n">
         <v>30</v>
       </c>
-      <c r="AN32" s="720" t="n">
+      <c r="AN32" s="1238" t="n">
         <v>31</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="1206" t="inlineStr">
+      <c r="A33" s="1241" t="inlineStr">
         <is>
           <t>ACS</t>
         </is>
       </c>
-      <c r="B33" s="1148" t="n"/>
       <c r="I33" s="1149" t="n"/>
       <c r="J33" s="1008" t="n"/>
       <c r="K33" s="1008" t="n"/>
@@ -8640,21 +8805,21 @@
       <c r="N33" s="1008" t="n"/>
       <c r="O33" s="1012" t="n"/>
       <c r="P33" s="1012" t="n"/>
-      <c r="Q33" s="1021" t="inlineStr">
+      <c r="Q33" s="1273" t="inlineStr">
         <is>
           <t>TTT WAI</t>
         </is>
       </c>
-      <c r="R33" s="739" t="n"/>
-      <c r="S33" s="740" t="n"/>
+      <c r="R33" s="1155" t="n"/>
+      <c r="S33" s="1156" t="n"/>
       <c r="T33" s="1008" t="n"/>
-      <c r="U33" s="1021" t="inlineStr">
+      <c r="U33" s="1273" t="inlineStr">
         <is>
           <t>LEAD TEAMS</t>
         </is>
       </c>
-      <c r="V33" s="739" t="n"/>
-      <c r="W33" s="740" t="n"/>
+      <c r="V33" s="1155" t="n"/>
+      <c r="W33" s="1156" t="n"/>
       <c r="X33" s="1008" t="n"/>
       <c r="Y33" s="1009" t="n"/>
       <c r="Z33" s="1009" t="n"/>
@@ -8674,8 +8839,7 @@
       <c r="AN33" s="1008" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="729" t="n"/>
-      <c r="B34" s="1148" t="n"/>
+      <c r="A34" s="1268" t="n"/>
       <c r="I34" s="1149" t="n"/>
       <c r="J34" s="1008" t="n"/>
       <c r="K34" s="1008" t="n"/>
@@ -8692,18 +8856,18 @@
       <c r="V34" s="1012" t="n"/>
       <c r="W34" s="1012" t="n"/>
       <c r="X34" s="1008" t="n"/>
-      <c r="Y34" s="1028" t="inlineStr">
+      <c r="Y34" s="1274" t="inlineStr">
         <is>
           <t>LEAD SYS OFFICER</t>
         </is>
       </c>
-      <c r="Z34" s="744" t="n"/>
-      <c r="AA34" s="744" t="n"/>
-      <c r="AB34" s="744" t="n"/>
-      <c r="AC34" s="744" t="n"/>
-      <c r="AD34" s="744" t="n"/>
-      <c r="AE34" s="744" t="n"/>
-      <c r="AF34" s="745" t="n"/>
+      <c r="Z34" s="1155" t="n"/>
+      <c r="AA34" s="1155" t="n"/>
+      <c r="AB34" s="1155" t="n"/>
+      <c r="AC34" s="1155" t="n"/>
+      <c r="AD34" s="1155" t="n"/>
+      <c r="AE34" s="1155" t="n"/>
+      <c r="AF34" s="1156" t="n"/>
       <c r="AG34" s="1022" t="n"/>
       <c r="AH34" s="1022" t="n"/>
       <c r="AI34" s="1012" t="n"/>
@@ -8714,29 +8878,28 @@
       <c r="AN34" s="1008" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1" thickBot="1">
-      <c r="A35" s="1214" t="inlineStr">
+      <c r="A35" s="1242" t="inlineStr">
         <is>
           <t>OCS (NZ)</t>
         </is>
       </c>
-      <c r="B35" s="1148" t="n"/>
       <c r="I35" s="1149" t="n"/>
       <c r="J35" s="1008" t="n"/>
       <c r="K35" s="1008" t="n"/>
       <c r="L35" s="1008" t="n"/>
-      <c r="M35" s="1063" t="inlineStr">
+      <c r="M35" s="1269" t="inlineStr">
         <is>
           <t>EX MAADI</t>
         </is>
       </c>
-      <c r="N35" s="732" t="n"/>
-      <c r="O35" s="732" t="n"/>
-      <c r="P35" s="732" t="n"/>
-      <c r="Q35" s="732" t="n"/>
-      <c r="R35" s="732" t="n"/>
-      <c r="S35" s="732" t="n"/>
-      <c r="T35" s="732" t="n"/>
-      <c r="U35" s="765" t="n"/>
+      <c r="N35" s="1270" t="n"/>
+      <c r="O35" s="1270" t="n"/>
+      <c r="P35" s="1270" t="n"/>
+      <c r="Q35" s="1270" t="n"/>
+      <c r="R35" s="1270" t="n"/>
+      <c r="S35" s="1270" t="n"/>
+      <c r="T35" s="1270" t="n"/>
+      <c r="U35" s="1271" t="n"/>
       <c r="V35" s="1015" t="n"/>
       <c r="W35" s="1015" t="n"/>
       <c r="X35" s="1009" t="n"/>
@@ -8758,25 +8921,24 @@
       <c r="AN35" s="1009" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="726" t="n"/>
-      <c r="B36" s="1148" t="n"/>
+      <c r="A36" s="1272" t="n"/>
       <c r="I36" s="1149" t="n"/>
-      <c r="J36" s="1048" t="inlineStr">
+      <c r="J36" s="1269" t="inlineStr">
         <is>
           <t>IIT</t>
         </is>
       </c>
-      <c r="K36" s="732" t="n"/>
-      <c r="L36" s="732" t="n"/>
-      <c r="M36" s="732" t="n"/>
-      <c r="N36" s="732" t="n"/>
-      <c r="O36" s="732" t="n"/>
-      <c r="P36" s="732" t="n"/>
-      <c r="Q36" s="732" t="n"/>
-      <c r="R36" s="732" t="n"/>
-      <c r="S36" s="732" t="n"/>
-      <c r="T36" s="732" t="n"/>
-      <c r="U36" s="765" t="n"/>
+      <c r="K36" s="1270" t="n"/>
+      <c r="L36" s="1270" t="n"/>
+      <c r="M36" s="1270" t="n"/>
+      <c r="N36" s="1270" t="n"/>
+      <c r="O36" s="1270" t="n"/>
+      <c r="P36" s="1270" t="n"/>
+      <c r="Q36" s="1270" t="n"/>
+      <c r="R36" s="1270" t="n"/>
+      <c r="S36" s="1270" t="n"/>
+      <c r="T36" s="1270" t="n"/>
+      <c r="U36" s="1271" t="n"/>
       <c r="V36" s="1015" t="n"/>
       <c r="W36" s="1015" t="n"/>
       <c r="X36" s="1009" t="n"/>
@@ -8798,8 +8960,7 @@
       <c r="AN36" s="1009" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1" thickBot="1">
-      <c r="A37" s="729" t="n"/>
-      <c r="B37" s="1148" t="n"/>
+      <c r="A37" s="1268" t="n"/>
       <c r="I37" s="1149" t="n"/>
       <c r="J37" s="1008" t="n"/>
       <c r="K37" s="1008" t="n"/>
@@ -8834,12 +8995,11 @@
       <c r="AN37" s="1008" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="1020" t="inlineStr">
+      <c r="A38" s="1244" t="inlineStr">
         <is>
           <t>ALC LD Wing</t>
         </is>
       </c>
-      <c r="B38" s="1148" t="n"/>
       <c r="I38" s="1149" t="n"/>
       <c r="J38" s="1008" t="n"/>
       <c r="K38" s="1013" t="n"/>
@@ -8874,12 +9034,11 @@
       <c r="AN38" s="1008" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="1027" t="inlineStr">
+      <c r="A39" s="1246" t="inlineStr">
         <is>
           <t>ALC ELDA Wing</t>
         </is>
       </c>
-      <c r="B39" s="1148" t="n"/>
       <c r="I39" s="1149" t="n"/>
       <c r="J39" s="1008" t="n"/>
       <c r="K39" s="1064" t="n"/>
@@ -8914,92 +9073,90 @@
       <c r="AN39" s="1008" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="1030" t="inlineStr">
+      <c r="A40" s="1248" t="inlineStr">
         <is>
           <t>2 RTW</t>
         </is>
       </c>
-      <c r="B40" s="1148" t="n"/>
       <c r="I40" s="1149" t="n"/>
-      <c r="J40" s="1066" t="inlineStr">
+      <c r="J40" s="1275" t="inlineStr">
         <is>
           <t>RF JNCO 27/02</t>
         </is>
       </c>
-      <c r="K40" s="732" t="n"/>
-      <c r="L40" s="732" t="n"/>
-      <c r="M40" s="732" t="n"/>
-      <c r="N40" s="732" t="n"/>
-      <c r="O40" s="732" t="n"/>
-      <c r="P40" s="732" t="n"/>
-      <c r="Q40" s="732" t="n"/>
-      <c r="R40" s="732" t="n"/>
-      <c r="S40" s="732" t="n"/>
-      <c r="T40" s="732" t="n"/>
-      <c r="U40" s="732" t="n"/>
-      <c r="V40" s="732" t="n"/>
-      <c r="W40" s="765" t="n"/>
-      <c r="X40" s="1067" t="inlineStr">
+      <c r="K40" s="1270" t="n"/>
+      <c r="L40" s="1270" t="n"/>
+      <c r="M40" s="1270" t="n"/>
+      <c r="N40" s="1270" t="n"/>
+      <c r="O40" s="1270" t="n"/>
+      <c r="P40" s="1270" t="n"/>
+      <c r="Q40" s="1270" t="n"/>
+      <c r="R40" s="1270" t="n"/>
+      <c r="S40" s="1270" t="n"/>
+      <c r="T40" s="1270" t="n"/>
+      <c r="U40" s="1270" t="n"/>
+      <c r="V40" s="1270" t="n"/>
+      <c r="W40" s="1271" t="n"/>
+      <c r="X40" s="1275" t="inlineStr">
         <is>
           <t>EX YOUNG LION</t>
         </is>
       </c>
-      <c r="Y40" s="732" t="n"/>
-      <c r="Z40" s="732" t="n"/>
-      <c r="AA40" s="732" t="n"/>
-      <c r="AB40" s="732" t="n"/>
-      <c r="AC40" s="732" t="n"/>
-      <c r="AD40" s="732" t="n"/>
-      <c r="AE40" s="732" t="n"/>
-      <c r="AF40" s="732" t="n"/>
-      <c r="AG40" s="732" t="n"/>
-      <c r="AH40" s="732" t="n"/>
-      <c r="AI40" s="765" t="n"/>
-      <c r="AJ40" s="1067" t="inlineStr">
+      <c r="Y40" s="1270" t="n"/>
+      <c r="Z40" s="1270" t="n"/>
+      <c r="AA40" s="1270" t="n"/>
+      <c r="AB40" s="1270" t="n"/>
+      <c r="AC40" s="1270" t="n"/>
+      <c r="AD40" s="1270" t="n"/>
+      <c r="AE40" s="1270" t="n"/>
+      <c r="AF40" s="1270" t="n"/>
+      <c r="AG40" s="1270" t="n"/>
+      <c r="AH40" s="1270" t="n"/>
+      <c r="AI40" s="1271" t="n"/>
+      <c r="AJ40" s="1275" t="inlineStr">
         <is>
           <t>RF JNCO 27/02</t>
         </is>
       </c>
-      <c r="AK40" s="732" t="n"/>
-      <c r="AL40" s="732" t="n"/>
-      <c r="AM40" s="732" t="n"/>
-      <c r="AN40" s="765" t="n"/>
+      <c r="AK40" s="1270" t="n"/>
+      <c r="AL40" s="1270" t="n"/>
+      <c r="AM40" s="1270" t="n"/>
+      <c r="AN40" s="1271" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1" thickBot="1">
-      <c r="A41" s="1033" t="inlineStr">
+      <c r="A41" s="1250" t="inlineStr">
         <is>
           <t>3 RTW</t>
         </is>
       </c>
-      <c r="B41" s="1148" t="n"/>
       <c r="I41" s="1149" t="n"/>
-      <c r="J41" s="1068" t="inlineStr">
+      <c r="J41" s="1276" t="inlineStr">
         <is>
           <t>EX YOUNG LION</t>
         </is>
       </c>
-      <c r="K41" s="732" t="n"/>
-      <c r="L41" s="732" t="n"/>
-      <c r="M41" s="732" t="n"/>
-      <c r="N41" s="732" t="n"/>
-      <c r="O41" s="732" t="n"/>
-      <c r="P41" s="732" t="n"/>
-      <c r="Q41" s="732" t="n"/>
-      <c r="R41" s="732" t="n"/>
-      <c r="S41" s="732" t="n"/>
-      <c r="T41" s="732" t="n"/>
-      <c r="U41" s="765" t="n"/>
-      <c r="V41" s="1069" t="inlineStr">
+      <c r="K41" s="1270" t="n"/>
+      <c r="L41" s="1270" t="n"/>
+      <c r="M41" s="1270" t="n"/>
+      <c r="N41" s="1270" t="n"/>
+      <c r="O41" s="1270" t="n"/>
+      <c r="P41" s="1270" t="n"/>
+      <c r="Q41" s="1270" t="n"/>
+      <c r="R41" s="1270" t="n"/>
+      <c r="S41" s="1270" t="n"/>
+      <c r="T41" s="1270" t="n"/>
+      <c r="U41" s="1271" t="n"/>
+      <c r="V41" s="1276" t="inlineStr">
         <is>
           <t>RF JNCO 27/01</t>
         </is>
       </c>
-      <c r="W41" s="732" t="n"/>
-      <c r="X41" s="732" t="n"/>
-      <c r="Y41" s="732" t="n"/>
-      <c r="Z41" s="732" t="n"/>
-      <c r="AA41" s="732" t="n"/>
-      <c r="AB41" s="765" t="n"/>
+      <c r="W41" s="1270" t="n"/>
+      <c r="X41" s="1270" t="n"/>
+      <c r="Y41" s="1270" t="n"/>
+      <c r="Z41" s="1270" t="n"/>
+      <c r="AA41" s="1270" t="n"/>
+      <c r="AB41" s="1271" t="n"/>
       <c r="AC41" s="1044" t="n"/>
       <c r="AD41" s="1044" t="n"/>
       <c r="AE41" s="1022" t="n"/>
@@ -9014,60 +9171,59 @@
       <c r="AN41" s="1008" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1" thickBot="1">
-      <c r="A42" s="1037" t="inlineStr">
+      <c r="A42" s="1252" t="inlineStr">
         <is>
           <t>SNCO Wing</t>
         </is>
       </c>
-      <c r="B42" s="1148" t="n"/>
       <c r="I42" s="1149" t="n"/>
-      <c r="J42" s="1159" t="inlineStr">
+      <c r="J42" s="1279" t="inlineStr">
         <is>
           <t>RF SNCO 27/01</t>
         </is>
       </c>
-      <c r="K42" s="732" t="n"/>
-      <c r="L42" s="732" t="n"/>
-      <c r="M42" s="732" t="n"/>
-      <c r="N42" s="732" t="n"/>
-      <c r="O42" s="732" t="n"/>
-      <c r="P42" s="732" t="n"/>
-      <c r="Q42" s="732" t="n"/>
-      <c r="R42" s="732" t="n"/>
-      <c r="S42" s="732" t="n"/>
-      <c r="T42" s="732" t="n"/>
-      <c r="U42" s="732" t="n"/>
-      <c r="V42" s="732" t="n"/>
-      <c r="W42" s="1160" t="n"/>
-      <c r="X42" s="1071" t="inlineStr">
+      <c r="K42" s="1270" t="n"/>
+      <c r="L42" s="1270" t="n"/>
+      <c r="M42" s="1270" t="n"/>
+      <c r="N42" s="1270" t="n"/>
+      <c r="O42" s="1270" t="n"/>
+      <c r="P42" s="1270" t="n"/>
+      <c r="Q42" s="1270" t="n"/>
+      <c r="R42" s="1270" t="n"/>
+      <c r="S42" s="1270" t="n"/>
+      <c r="T42" s="1270" t="n"/>
+      <c r="U42" s="1270" t="n"/>
+      <c r="V42" s="1270" t="n"/>
+      <c r="W42" s="1271" t="n"/>
+      <c r="X42" s="1279" t="inlineStr">
         <is>
           <t>EX KALAMATI</t>
         </is>
       </c>
-      <c r="Y42" s="732" t="n"/>
-      <c r="Z42" s="732" t="n"/>
-      <c r="AA42" s="732" t="n"/>
-      <c r="AB42" s="732" t="n"/>
-      <c r="AC42" s="732" t="n"/>
-      <c r="AD42" s="732" t="n"/>
-      <c r="AE42" s="732" t="n"/>
-      <c r="AF42" s="732" t="n"/>
-      <c r="AG42" s="732" t="n"/>
-      <c r="AH42" s="732" t="n"/>
-      <c r="AI42" s="732" t="n"/>
-      <c r="AJ42" s="732" t="n"/>
-      <c r="AK42" s="732" t="n"/>
-      <c r="AL42" s="732" t="n"/>
-      <c r="AM42" s="732" t="n"/>
-      <c r="AN42" s="765" t="n"/>
+      <c r="Y42" s="1270" t="n"/>
+      <c r="Z42" s="1270" t="n"/>
+      <c r="AA42" s="1270" t="n"/>
+      <c r="AB42" s="1270" t="n"/>
+      <c r="AC42" s="1270" t="n"/>
+      <c r="AD42" s="1270" t="n"/>
+      <c r="AE42" s="1270" t="n"/>
+      <c r="AF42" s="1270" t="n"/>
+      <c r="AG42" s="1270" t="n"/>
+      <c r="AH42" s="1270" t="n"/>
+      <c r="AI42" s="1270" t="n"/>
+      <c r="AJ42" s="1270" t="n"/>
+      <c r="AK42" s="1270" t="n"/>
+      <c r="AL42" s="1270" t="n"/>
+      <c r="AM42" s="1270" t="n"/>
+      <c r="AN42" s="1271" t="n"/>
     </row>
     <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="1039" t="inlineStr">
+      <c r="A43" s="1253" t="inlineStr">
         <is>
           <t>WO Wing</t>
         </is>
       </c>
-      <c r="B43" s="1154" t="n"/>
+      <c r="B43" s="1155" t="n"/>
       <c r="C43" s="1155" t="n"/>
       <c r="D43" s="1155" t="n"/>
       <c r="E43" s="1155" t="n"/>
@@ -9150,118 +9306,112 @@
       <c r="AN44" s="1225" t="n"/>
     </row>
     <row r="45" ht="14" customHeight="1">
-      <c r="A45" s="1226" t="inlineStr">
+      <c r="A45" s="1236" t="inlineStr">
         <is>
           <t>April</t>
         </is>
       </c>
-      <c r="B45" s="1042" t="n"/>
-      <c r="C45" s="1146" t="n"/>
-      <c r="D45" s="1146" t="n"/>
-      <c r="E45" s="1147" t="n"/>
-      <c r="F45" s="720" t="n">
+      <c r="B45" s="1278" t="n"/>
+      <c r="E45" s="1149" t="n"/>
+      <c r="F45" s="1238" t="n">
         <v>1</v>
       </c>
-      <c r="G45" s="720" t="n">
+      <c r="G45" s="1238" t="n">
         <v>2</v>
       </c>
-      <c r="H45" s="721" t="n">
+      <c r="H45" s="1239" t="n">
         <v>3</v>
       </c>
-      <c r="I45" s="721" t="n">
+      <c r="I45" s="1239" t="n">
         <v>4</v>
       </c>
-      <c r="J45" s="720" t="n">
+      <c r="J45" s="1238" t="n">
         <v>5</v>
       </c>
-      <c r="K45" s="720" t="n">
+      <c r="K45" s="1238" t="n">
         <v>6</v>
       </c>
-      <c r="L45" s="720" t="n">
+      <c r="L45" s="1238" t="n">
         <v>7</v>
       </c>
-      <c r="M45" s="720" t="n">
+      <c r="M45" s="1238" t="n">
         <v>8</v>
       </c>
-      <c r="N45" s="720" t="n">
+      <c r="N45" s="1238" t="n">
         <v>9</v>
       </c>
-      <c r="O45" s="721" t="n">
+      <c r="O45" s="1239" t="n">
         <v>10</v>
       </c>
-      <c r="P45" s="721" t="n">
+      <c r="P45" s="1239" t="n">
         <v>11</v>
       </c>
-      <c r="Q45" s="720" t="n">
+      <c r="Q45" s="1238" t="n">
         <v>12</v>
       </c>
-      <c r="R45" s="720" t="n">
+      <c r="R45" s="1238" t="n">
         <v>13</v>
       </c>
-      <c r="S45" s="720" t="n">
+      <c r="S45" s="1238" t="n">
         <v>14</v>
       </c>
-      <c r="T45" s="720" t="n">
+      <c r="T45" s="1238" t="n">
         <v>15</v>
       </c>
-      <c r="U45" s="720" t="n">
+      <c r="U45" s="1238" t="n">
         <v>16</v>
       </c>
-      <c r="V45" s="721" t="n">
+      <c r="V45" s="1239" t="n">
         <v>17</v>
       </c>
-      <c r="W45" s="721" t="n">
+      <c r="W45" s="1239" t="n">
         <v>18</v>
       </c>
-      <c r="X45" s="720" t="n">
+      <c r="X45" s="1238" t="n">
         <v>19</v>
       </c>
-      <c r="Y45" s="720" t="n">
+      <c r="Y45" s="1238" t="n">
         <v>20</v>
       </c>
-      <c r="Z45" s="720" t="n">
+      <c r="Z45" s="1238" t="n">
         <v>21</v>
       </c>
-      <c r="AA45" s="720" t="n">
+      <c r="AA45" s="1238" t="n">
         <v>22</v>
       </c>
-      <c r="AB45" s="720" t="n">
+      <c r="AB45" s="1238" t="n">
         <v>23</v>
       </c>
-      <c r="AC45" s="721" t="n">
+      <c r="AC45" s="1239" t="n">
         <v>24</v>
       </c>
-      <c r="AD45" s="721" t="n">
+      <c r="AD45" s="1239" t="n">
         <v>25</v>
       </c>
-      <c r="AE45" s="720" t="n">
+      <c r="AE45" s="1238" t="n">
         <v>26</v>
       </c>
-      <c r="AF45" s="720" t="n">
+      <c r="AF45" s="1238" t="n">
         <v>27</v>
       </c>
-      <c r="AG45" s="720" t="n">
+      <c r="AG45" s="1238" t="n">
         <v>28</v>
       </c>
-      <c r="AH45" s="720" t="n">
+      <c r="AH45" s="1238" t="n">
         <v>29</v>
       </c>
-      <c r="AI45" s="720" t="n">
+      <c r="AI45" s="1238" t="n">
         <v>30</v>
       </c>
-      <c r="AJ45" s="1002" t="n"/>
-      <c r="AK45" s="1146" t="n"/>
-      <c r="AL45" s="1146" t="n"/>
-      <c r="AM45" s="1146" t="n"/>
-      <c r="AN45" s="1147" t="n"/>
+      <c r="AJ45" s="1266" t="n"/>
+      <c r="AN45" s="1149" t="n"/>
     </row>
     <row r="46" ht="15" customHeight="1">
-      <c r="A46" s="1215" t="inlineStr">
+      <c r="A46" s="1241" t="inlineStr">
         <is>
           <t>ACS</t>
         </is>
       </c>
-      <c r="B46" s="1148" t="n"/>
       <c r="E46" s="1149" t="n"/>
       <c r="F46" s="1073" t="n"/>
       <c r="G46" s="1073" t="n"/>
@@ -9293,12 +9443,10 @@
       <c r="AG46" s="1008" t="n"/>
       <c r="AH46" s="1013" t="n"/>
       <c r="AI46" s="1013" t="n"/>
-      <c r="AJ46" s="1148" t="n"/>
       <c r="AN46" s="1149" t="n"/>
     </row>
     <row r="47" ht="15" customHeight="1" thickBot="1">
-      <c r="A47" s="726" t="n"/>
-      <c r="B47" s="1148" t="n"/>
+      <c r="A47" s="1268" t="n"/>
       <c r="E47" s="1149" t="n"/>
       <c r="F47" s="1073" t="n"/>
       <c r="G47" s="1073" t="n"/>
@@ -9330,16 +9478,14 @@
       <c r="AG47" s="1008" t="n"/>
       <c r="AH47" s="1013" t="n"/>
       <c r="AI47" s="1013" t="n"/>
-      <c r="AJ47" s="1148" t="n"/>
       <c r="AN47" s="1149" t="n"/>
     </row>
     <row r="48" ht="15" customHeight="1" thickBot="1">
-      <c r="A48" s="1211" t="inlineStr">
+      <c r="A48" s="1242" t="inlineStr">
         <is>
           <t>OCS (NZ)</t>
         </is>
       </c>
-      <c r="B48" s="1148" t="n"/>
       <c r="E48" s="1149" t="n"/>
       <c r="F48" s="1009" t="n"/>
       <c r="G48" s="1009" t="n"/>
@@ -9350,20 +9496,20 @@
       <c r="L48" s="1009" t="n"/>
       <c r="M48" s="1009" t="n"/>
       <c r="N48" s="1009" t="n"/>
-      <c r="O48" s="1063" t="inlineStr">
+      <c r="O48" s="1269" t="inlineStr">
         <is>
           <t>EX LBV</t>
         </is>
       </c>
-      <c r="P48" s="732" t="n"/>
-      <c r="Q48" s="732" t="n"/>
-      <c r="R48" s="732" t="n"/>
-      <c r="S48" s="732" t="n"/>
-      <c r="T48" s="732" t="n"/>
-      <c r="U48" s="732" t="n"/>
-      <c r="V48" s="732" t="n"/>
-      <c r="W48" s="732" t="n"/>
-      <c r="X48" s="765" t="n"/>
+      <c r="P48" s="1270" t="n"/>
+      <c r="Q48" s="1270" t="n"/>
+      <c r="R48" s="1270" t="n"/>
+      <c r="S48" s="1270" t="n"/>
+      <c r="T48" s="1270" t="n"/>
+      <c r="U48" s="1270" t="n"/>
+      <c r="V48" s="1270" t="n"/>
+      <c r="W48" s="1270" t="n"/>
+      <c r="X48" s="1271" t="n"/>
       <c r="Y48" s="1009" t="n"/>
       <c r="Z48" s="1009" t="n"/>
       <c r="AA48" s="1009" t="n"/>
@@ -9372,19 +9518,17 @@
       <c r="AD48" s="1015" t="n"/>
       <c r="AE48" s="1015" t="n"/>
       <c r="AF48" s="1009" t="n"/>
-      <c r="AG48" s="1017" t="inlineStr">
+      <c r="AG48" s="1269" t="inlineStr">
         <is>
           <t>EX TEBAGA GAP</t>
         </is>
       </c>
-      <c r="AH48" s="732" t="n"/>
-      <c r="AI48" s="733" t="n"/>
-      <c r="AJ48" s="1148" t="n"/>
+      <c r="AH48" s="1270" t="n"/>
+      <c r="AI48" s="1271" t="n"/>
       <c r="AN48" s="1149" t="n"/>
     </row>
     <row r="49" ht="15" customHeight="1" thickBot="1">
-      <c r="A49" s="726" t="n"/>
-      <c r="B49" s="1148" t="n"/>
+      <c r="A49" s="1272" t="n"/>
       <c r="E49" s="1149" t="n"/>
       <c r="F49" s="1080" t="n"/>
       <c r="G49" s="1080" t="n"/>
@@ -9416,12 +9560,10 @@
       <c r="AG49" s="1008" t="n"/>
       <c r="AH49" s="1013" t="n"/>
       <c r="AI49" s="1013" t="n"/>
-      <c r="AJ49" s="1148" t="n"/>
       <c r="AN49" s="1149" t="n"/>
     </row>
     <row r="50" ht="15" customHeight="1">
-      <c r="A50" s="729" t="n"/>
-      <c r="B50" s="1148" t="n"/>
+      <c r="A50" s="1268" t="n"/>
       <c r="E50" s="1149" t="n"/>
       <c r="F50" s="1073" t="n"/>
       <c r="G50" s="1073" t="n"/>
@@ -9453,16 +9595,14 @@
       <c r="AG50" s="1008" t="n"/>
       <c r="AH50" s="1013" t="n"/>
       <c r="AI50" s="1013" t="n"/>
-      <c r="AJ50" s="1148" t="n"/>
       <c r="AN50" s="1149" t="n"/>
     </row>
     <row r="51" ht="15" customHeight="1">
-      <c r="A51" s="1020" t="inlineStr">
+      <c r="A51" s="1244" t="inlineStr">
         <is>
           <t>ALC LD Wing</t>
         </is>
       </c>
-      <c r="B51" s="1148" t="n"/>
       <c r="E51" s="1149" t="n"/>
       <c r="F51" s="1073" t="n"/>
       <c r="G51" s="1073" t="n"/>
@@ -9494,16 +9634,14 @@
       <c r="AG51" s="1008" t="n"/>
       <c r="AH51" s="1013" t="n"/>
       <c r="AI51" s="1013" t="n"/>
-      <c r="AJ51" s="1148" t="n"/>
       <c r="AN51" s="1149" t="n"/>
     </row>
     <row r="52" ht="15" customHeight="1">
-      <c r="A52" s="1027" t="inlineStr">
+      <c r="A52" s="1246" t="inlineStr">
         <is>
           <t>ALC ELDA Wing</t>
         </is>
       </c>
-      <c r="B52" s="1148" t="n"/>
       <c r="E52" s="1149" t="n"/>
       <c r="F52" s="1073" t="n"/>
       <c r="G52" s="1073" t="n"/>
@@ -9530,32 +9668,30 @@
       <c r="AB52" s="1008" t="n"/>
       <c r="AC52" s="1012" t="n"/>
       <c r="AD52" s="1012" t="n"/>
-      <c r="AE52" s="1081" t="inlineStr">
+      <c r="AE52" s="1274" t="inlineStr">
         <is>
           <t>LEAD LEADERS BMC</t>
         </is>
       </c>
-      <c r="AF52" s="795" t="n"/>
-      <c r="AG52" s="795" t="n"/>
-      <c r="AH52" s="795" t="n"/>
-      <c r="AI52" s="796" t="n"/>
-      <c r="AJ52" s="1148" t="n"/>
+      <c r="AF52" s="1155" t="n"/>
+      <c r="AG52" s="1155" t="n"/>
+      <c r="AH52" s="1155" t="n"/>
+      <c r="AI52" s="1156" t="n"/>
       <c r="AN52" s="1149" t="n"/>
     </row>
     <row r="53" ht="15" customHeight="1" thickBot="1">
-      <c r="A53" s="1030" t="inlineStr">
+      <c r="A53" s="1248" t="inlineStr">
         <is>
           <t>2 RTW</t>
         </is>
       </c>
-      <c r="B53" s="1148" t="n"/>
       <c r="E53" s="1149" t="n"/>
-      <c r="F53" s="1082" t="inlineStr">
+      <c r="F53" s="1275" t="inlineStr">
         <is>
           <t>RF JNCO 27/02</t>
         </is>
       </c>
-      <c r="G53" s="765" t="n"/>
+      <c r="G53" s="1271" t="n"/>
       <c r="H53" s="1076" t="n"/>
       <c r="I53" s="1076" t="n"/>
       <c r="J53" s="1073" t="n"/>
@@ -9584,16 +9720,14 @@
       <c r="AG53" s="1008" t="n"/>
       <c r="AH53" s="1013" t="n"/>
       <c r="AI53" s="1013" t="n"/>
-      <c r="AJ53" s="1148" t="n"/>
       <c r="AN53" s="1149" t="n"/>
     </row>
     <row r="54" ht="15" customHeight="1" thickBot="1">
-      <c r="A54" s="1033" t="inlineStr">
+      <c r="A54" s="1250" t="inlineStr">
         <is>
           <t>3 RTW</t>
         </is>
       </c>
-      <c r="B54" s="1148" t="n"/>
       <c r="E54" s="1149" t="n"/>
       <c r="F54" s="1073" t="n"/>
       <c r="G54" s="1073" t="n"/>
@@ -9625,34 +9759,32 @@
       <c r="AG54" s="1008" t="n"/>
       <c r="AH54" s="1013" t="n"/>
       <c r="AI54" s="1013" t="n"/>
-      <c r="AJ54" s="1148" t="n"/>
       <c r="AN54" s="1149" t="n"/>
     </row>
     <row r="55" ht="15" customHeight="1">
-      <c r="A55" s="1037" t="inlineStr">
+      <c r="A55" s="1252" t="inlineStr">
         <is>
           <t>SNCO Wing</t>
         </is>
       </c>
-      <c r="B55" s="1148" t="n"/>
       <c r="E55" s="1149" t="n"/>
-      <c r="F55" s="1083" t="inlineStr">
+      <c r="F55" s="1279" t="inlineStr">
         <is>
           <t>EX KALAMATI</t>
         </is>
       </c>
-      <c r="G55" s="765" t="n"/>
-      <c r="H55" s="1071" t="inlineStr">
+      <c r="G55" s="1271" t="n"/>
+      <c r="H55" s="1279" t="inlineStr">
         <is>
           <t>RF SNCO 27/01</t>
         </is>
       </c>
-      <c r="I55" s="732" t="n"/>
-      <c r="J55" s="732" t="n"/>
-      <c r="K55" s="732" t="n"/>
-      <c r="L55" s="732" t="n"/>
-      <c r="M55" s="732" t="n"/>
-      <c r="N55" s="765" t="n"/>
+      <c r="I55" s="1270" t="n"/>
+      <c r="J55" s="1270" t="n"/>
+      <c r="K55" s="1270" t="n"/>
+      <c r="L55" s="1270" t="n"/>
+      <c r="M55" s="1270" t="n"/>
+      <c r="N55" s="1271" t="n"/>
       <c r="O55" s="1084" t="n"/>
       <c r="P55" s="1084" t="n"/>
       <c r="Q55" s="1085" t="n"/>
@@ -9669,25 +9801,24 @@
       <c r="AB55" s="1008" t="n"/>
       <c r="AC55" s="1012" t="n"/>
       <c r="AD55" s="1012" t="n"/>
-      <c r="AE55" s="1058" t="inlineStr">
+      <c r="AE55" s="1279" t="inlineStr">
         <is>
           <t>RF SNCO 27/02</t>
         </is>
       </c>
-      <c r="AF55" s="732" t="n"/>
-      <c r="AG55" s="732" t="n"/>
-      <c r="AH55" s="732" t="n"/>
-      <c r="AI55" s="733" t="n"/>
-      <c r="AJ55" s="1148" t="n"/>
+      <c r="AF55" s="1270" t="n"/>
+      <c r="AG55" s="1270" t="n"/>
+      <c r="AH55" s="1270" t="n"/>
+      <c r="AI55" s="1271" t="n"/>
       <c r="AN55" s="1149" t="n"/>
     </row>
     <row r="56" ht="15" customHeight="1" thickBot="1">
-      <c r="A56" s="1039" t="inlineStr">
+      <c r="A56" s="1253" t="inlineStr">
         <is>
           <t>WO Wing</t>
         </is>
       </c>
-      <c r="B56" s="1154" t="n"/>
+      <c r="B56" s="1155" t="n"/>
       <c r="C56" s="1155" t="n"/>
       <c r="D56" s="1155" t="n"/>
       <c r="E56" s="1156" t="n"/>
@@ -9721,7 +9852,7 @@
       <c r="AG56" s="1008" t="n"/>
       <c r="AH56" s="1013" t="n"/>
       <c r="AI56" s="1013" t="n"/>
-      <c r="AJ56" s="1154" t="n"/>
+      <c r="AJ56" s="1155" t="n"/>
       <c r="AK56" s="1155" t="n"/>
       <c r="AL56" s="1155" t="n"/>
       <c r="AM56" s="1155" t="n"/>
@@ -9770,120 +9901,115 @@
       <c r="AN57" s="1225" t="n"/>
     </row>
     <row r="58" ht="14" customHeight="1">
-      <c r="A58" s="1226" t="inlineStr">
+      <c r="A58" s="1236" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="B58" s="1042" t="n"/>
-      <c r="C58" s="1146" t="n"/>
-      <c r="D58" s="1146" t="n"/>
-      <c r="E58" s="1146" t="n"/>
-      <c r="F58" s="1146" t="n"/>
-      <c r="G58" s="1147" t="n"/>
-      <c r="H58" s="721" t="n">
+      <c r="B58" s="1278" t="n"/>
+      <c r="G58" s="1149" t="n"/>
+      <c r="H58" s="1239" t="n">
         <v>1</v>
       </c>
-      <c r="I58" s="721" t="n">
+      <c r="I58" s="1239" t="n">
         <v>2</v>
       </c>
-      <c r="J58" s="720" t="n">
+      <c r="J58" s="1238" t="n">
         <v>3</v>
       </c>
-      <c r="K58" s="720" t="n">
+      <c r="K58" s="1238" t="n">
         <v>4</v>
       </c>
-      <c r="L58" s="720" t="n">
+      <c r="L58" s="1238" t="n">
         <v>5</v>
       </c>
-      <c r="M58" s="720" t="n">
+      <c r="M58" s="1238" t="n">
         <v>6</v>
       </c>
-      <c r="N58" s="720" t="n">
+      <c r="N58" s="1238" t="n">
         <v>7</v>
       </c>
-      <c r="O58" s="721" t="n">
+      <c r="O58" s="1239" t="n">
         <v>8</v>
       </c>
-      <c r="P58" s="721" t="n">
+      <c r="P58" s="1239" t="n">
         <v>9</v>
       </c>
-      <c r="Q58" s="720" t="n">
+      <c r="Q58" s="1238" t="n">
         <v>10</v>
       </c>
-      <c r="R58" s="720" t="n">
+      <c r="R58" s="1238" t="n">
         <v>11</v>
       </c>
-      <c r="S58" s="720" t="n">
+      <c r="S58" s="1238" t="n">
         <v>12</v>
       </c>
-      <c r="T58" s="720" t="n">
+      <c r="T58" s="1238" t="n">
         <v>13</v>
       </c>
-      <c r="U58" s="720" t="n">
+      <c r="U58" s="1238" t="n">
         <v>14</v>
       </c>
-      <c r="V58" s="721" t="n">
+      <c r="V58" s="1239" t="n">
         <v>15</v>
       </c>
-      <c r="W58" s="721" t="n">
+      <c r="W58" s="1239" t="n">
         <v>16</v>
       </c>
-      <c r="X58" s="720" t="n">
+      <c r="X58" s="1238" t="n">
         <v>17</v>
       </c>
-      <c r="Y58" s="720" t="n">
+      <c r="Y58" s="1238" t="n">
         <v>18</v>
       </c>
-      <c r="Z58" s="720" t="n">
+      <c r="Z58" s="1238" t="n">
         <v>19</v>
       </c>
-      <c r="AA58" s="720" t="n">
+      <c r="AA58" s="1238" t="n">
         <v>20</v>
       </c>
-      <c r="AB58" s="720" t="n">
+      <c r="AB58" s="1238" t="n">
         <v>21</v>
       </c>
-      <c r="AC58" s="721" t="n">
+      <c r="AC58" s="1239" t="n">
         <v>22</v>
       </c>
-      <c r="AD58" s="721" t="n">
+      <c r="AD58" s="1239" t="n">
         <v>23</v>
       </c>
-      <c r="AE58" s="720" t="n">
+      <c r="AE58" s="1238" t="n">
         <v>24</v>
       </c>
-      <c r="AF58" s="720" t="n">
+      <c r="AF58" s="1238" t="n">
         <v>25</v>
       </c>
-      <c r="AG58" s="720" t="n">
+      <c r="AG58" s="1238" t="n">
         <v>26</v>
       </c>
-      <c r="AH58" s="720" t="n">
+      <c r="AH58" s="1238" t="n">
         <v>27</v>
       </c>
-      <c r="AI58" s="720" t="n">
+      <c r="AI58" s="1238" t="n">
         <v>28</v>
       </c>
-      <c r="AJ58" s="721" t="n">
+      <c r="AJ58" s="1239" t="n">
         <v>29</v>
       </c>
-      <c r="AK58" s="721" t="n">
+      <c r="AK58" s="1239" t="n">
         <v>30</v>
       </c>
-      <c r="AL58" s="720" t="n">
+      <c r="AL58" s="1238" t="n">
         <v>31</v>
       </c>
-      <c r="AM58" s="1042" t="n"/>
-      <c r="AN58" s="1147" t="n"/>
+      <c r="AM58" s="1278" t="n"/>
+      <c r="AN58" s="1149" t="n"/>
     </row>
     <row r="59" ht="15" customHeight="1" thickBot="1">
-      <c r="A59" s="1206" t="inlineStr">
+      <c r="A59" s="1241" t="inlineStr">
         <is>
           <t>ACS</t>
         </is>
       </c>
-      <c r="B59" s="1148" t="n"/>
       <c r="G59" s="1149" t="n"/>
       <c r="H59" s="1012" t="n"/>
       <c r="I59" s="1012" t="n"/>
@@ -9916,12 +10042,10 @@
       <c r="AJ59" s="1012" t="n"/>
       <c r="AK59" s="1045" t="n"/>
       <c r="AL59" s="1087" t="n"/>
-      <c r="AM59" s="1148" t="n"/>
       <c r="AN59" s="1149" t="n"/>
     </row>
     <row r="60" ht="15" customHeight="1" thickBot="1">
-      <c r="A60" s="729" t="n"/>
-      <c r="B60" s="1148" t="n"/>
+      <c r="A60" s="1268" t="n"/>
       <c r="G60" s="1149" t="n"/>
       <c r="H60" s="1012" t="n"/>
       <c r="I60" s="1012" t="n"/>
@@ -9954,28 +10078,26 @@
       <c r="AJ60" s="1012" t="n"/>
       <c r="AK60" s="1045" t="n"/>
       <c r="AL60" s="1087" t="n"/>
-      <c r="AM60" s="1148" t="n"/>
       <c r="AN60" s="1149" t="n"/>
     </row>
     <row r="61" ht="15" customHeight="1" thickBot="1">
-      <c r="A61" s="1211" t="inlineStr">
+      <c r="A61" s="1242" t="inlineStr">
         <is>
           <t>OCS (NZ)</t>
         </is>
       </c>
-      <c r="B61" s="1148" t="n"/>
       <c r="G61" s="1149" t="n"/>
-      <c r="H61" s="1048" t="inlineStr">
+      <c r="H61" s="1269" t="inlineStr">
         <is>
           <t>EX TEBAGA GAP</t>
         </is>
       </c>
-      <c r="I61" s="732" t="n"/>
-      <c r="J61" s="732" t="n"/>
-      <c r="K61" s="732" t="n"/>
-      <c r="L61" s="732" t="n"/>
-      <c r="M61" s="732" t="n"/>
-      <c r="N61" s="765" t="n"/>
+      <c r="I61" s="1270" t="n"/>
+      <c r="J61" s="1270" t="n"/>
+      <c r="K61" s="1270" t="n"/>
+      <c r="L61" s="1270" t="n"/>
+      <c r="M61" s="1270" t="n"/>
+      <c r="N61" s="1271" t="n"/>
       <c r="O61" s="1015" t="n"/>
       <c r="P61" s="1015" t="n"/>
       <c r="Q61" s="1009" t="n"/>
@@ -10000,12 +10122,10 @@
       <c r="AJ61" s="1015" t="n"/>
       <c r="AK61" s="1045" t="n"/>
       <c r="AL61" s="1087" t="n"/>
-      <c r="AM61" s="1148" t="n"/>
       <c r="AN61" s="1149" t="n"/>
     </row>
     <row r="62" ht="15" customHeight="1">
-      <c r="A62" s="726" t="n"/>
-      <c r="B62" s="1148" t="n"/>
+      <c r="A62" s="1272" t="n"/>
       <c r="G62" s="1149" t="n"/>
       <c r="H62" s="1012" t="n"/>
       <c r="I62" s="1012" t="n"/>
@@ -10038,12 +10158,10 @@
       <c r="AJ62" s="1012" t="n"/>
       <c r="AK62" s="1045" t="n"/>
       <c r="AL62" s="1087" t="n"/>
-      <c r="AM62" s="1148" t="n"/>
       <c r="AN62" s="1149" t="n"/>
     </row>
     <row r="63" ht="15" customHeight="1">
-      <c r="A63" s="729" t="n"/>
-      <c r="B63" s="1148" t="n"/>
+      <c r="A63" s="1268" t="n"/>
       <c r="G63" s="1149" t="n"/>
       <c r="H63" s="1012" t="n"/>
       <c r="I63" s="1012" t="n"/>
@@ -10076,28 +10194,26 @@
       <c r="AJ63" s="1012" t="n"/>
       <c r="AK63" s="1045" t="n"/>
       <c r="AL63" s="1087" t="n"/>
-      <c r="AM63" s="1148" t="n"/>
       <c r="AN63" s="1149" t="n"/>
     </row>
     <row r="64" ht="15" customHeight="1">
-      <c r="A64" s="1020" t="inlineStr">
+      <c r="A64" s="1244" t="inlineStr">
         <is>
           <t>ALC LD Wing</t>
         </is>
       </c>
-      <c r="B64" s="1148" t="n"/>
       <c r="G64" s="1149" t="n"/>
       <c r="H64" s="1012" t="n"/>
       <c r="I64" s="1090" t="n"/>
-      <c r="J64" s="1021" t="inlineStr">
+      <c r="J64" s="1273" t="inlineStr">
         <is>
           <t>LEAD LEADERS 27_03 BMC</t>
         </is>
       </c>
-      <c r="K64" s="739" t="n"/>
-      <c r="L64" s="739" t="n"/>
-      <c r="M64" s="739" t="n"/>
-      <c r="N64" s="740" t="n"/>
+      <c r="K64" s="1155" t="n"/>
+      <c r="L64" s="1155" t="n"/>
+      <c r="M64" s="1155" t="n"/>
+      <c r="N64" s="1156" t="n"/>
       <c r="O64" s="1012" t="n"/>
       <c r="P64" s="1012" t="n"/>
       <c r="Q64" s="1008" t="n"/>
@@ -10107,15 +10223,15 @@
       <c r="U64" s="1008" t="n"/>
       <c r="V64" s="1012" t="n"/>
       <c r="W64" s="1091" t="n"/>
-      <c r="X64" s="1021" t="inlineStr">
+      <c r="X64" s="1273" t="inlineStr">
         <is>
           <t>LEAD TEAMS BMC</t>
         </is>
       </c>
-      <c r="Y64" s="739" t="n"/>
-      <c r="Z64" s="739" t="n"/>
-      <c r="AA64" s="739" t="n"/>
-      <c r="AB64" s="740" t="n"/>
+      <c r="Y64" s="1155" t="n"/>
+      <c r="Z64" s="1155" t="n"/>
+      <c r="AA64" s="1155" t="n"/>
+      <c r="AB64" s="1156" t="n"/>
       <c r="AC64" s="1078" t="n"/>
       <c r="AD64" s="1078" t="n"/>
       <c r="AE64" s="1080" t="n"/>
@@ -10125,17 +10241,15 @@
       <c r="AI64" s="1024" t="n"/>
       <c r="AJ64" s="1012" t="n"/>
       <c r="AK64" s="1045" t="n"/>
-      <c r="AL64" s="1167" t="n"/>
-      <c r="AM64" s="1148" t="n"/>
+      <c r="AL64" s="1257" t="n"/>
       <c r="AN64" s="1149" t="n"/>
     </row>
     <row r="65" ht="15" customHeight="1" thickBot="1">
-      <c r="A65" s="1027" t="inlineStr">
+      <c r="A65" s="1246" t="inlineStr">
         <is>
           <t>ALC ELDA Wing</t>
         </is>
       </c>
-      <c r="B65" s="1148" t="n"/>
       <c r="G65" s="1149" t="n"/>
       <c r="H65" s="1012" t="n"/>
       <c r="I65" s="1012" t="n"/>
@@ -10146,16 +10260,16 @@
       <c r="N65" s="1008" t="n"/>
       <c r="O65" s="1012" t="n"/>
       <c r="P65" s="1012" t="n"/>
-      <c r="Q65" s="1028" t="inlineStr">
+      <c r="Q65" s="1274" t="inlineStr">
         <is>
           <t>LEAD TEAMS BMC</t>
         </is>
       </c>
-      <c r="R65" s="744" t="n"/>
-      <c r="S65" s="744" t="n"/>
-      <c r="T65" s="744" t="n"/>
-      <c r="U65" s="744" t="n"/>
-      <c r="V65" s="745" t="n"/>
+      <c r="R65" s="1155" t="n"/>
+      <c r="S65" s="1155" t="n"/>
+      <c r="T65" s="1155" t="n"/>
+      <c r="U65" s="1155" t="n"/>
+      <c r="V65" s="1156" t="n"/>
       <c r="W65" s="1012" t="n"/>
       <c r="X65" s="1013" t="n"/>
       <c r="Y65" s="1013" t="n"/>
@@ -10164,28 +10278,26 @@
       <c r="AB65" s="1080" t="n"/>
       <c r="AC65" s="1078" t="n"/>
       <c r="AD65" s="1012" t="n"/>
-      <c r="AE65" s="1028" t="inlineStr">
+      <c r="AE65" s="1274" t="inlineStr">
         <is>
           <t>LEAD TEAMS LTN</t>
         </is>
       </c>
-      <c r="AF65" s="744" t="n"/>
-      <c r="AG65" s="744" t="n"/>
-      <c r="AH65" s="744" t="n"/>
-      <c r="AI65" s="744" t="n"/>
-      <c r="AJ65" s="745" t="n"/>
+      <c r="AF65" s="1155" t="n"/>
+      <c r="AG65" s="1155" t="n"/>
+      <c r="AH65" s="1155" t="n"/>
+      <c r="AI65" s="1155" t="n"/>
+      <c r="AJ65" s="1156" t="n"/>
       <c r="AK65" s="1045" t="n"/>
       <c r="AL65" s="1087" t="n"/>
-      <c r="AM65" s="1148" t="n"/>
       <c r="AN65" s="1149" t="n"/>
     </row>
     <row r="66" ht="15" customHeight="1" thickBot="1">
-      <c r="A66" s="1030" t="inlineStr">
+      <c r="A66" s="1248" t="inlineStr">
         <is>
           <t>2 RTW</t>
         </is>
       </c>
-      <c r="B66" s="1148" t="n"/>
       <c r="G66" s="1149" t="n"/>
       <c r="H66" s="1012" t="n"/>
       <c r="I66" s="1012" t="n"/>
@@ -10210,28 +10322,26 @@
       <c r="AB66" s="1080" t="n"/>
       <c r="AC66" s="1078" t="n"/>
       <c r="AD66" s="1012" t="n"/>
-      <c r="AE66" s="1031" t="inlineStr">
+      <c r="AE66" s="1275" t="inlineStr">
         <is>
           <t>RF JNCO 27/04</t>
         </is>
       </c>
-      <c r="AF66" s="732" t="n"/>
-      <c r="AG66" s="732" t="n"/>
-      <c r="AH66" s="732" t="n"/>
-      <c r="AI66" s="732" t="n"/>
-      <c r="AJ66" s="732" t="n"/>
-      <c r="AK66" s="732" t="n"/>
-      <c r="AL66" s="733" t="n"/>
-      <c r="AM66" s="1148" t="n"/>
+      <c r="AF66" s="1270" t="n"/>
+      <c r="AG66" s="1270" t="n"/>
+      <c r="AH66" s="1270" t="n"/>
+      <c r="AI66" s="1270" t="n"/>
+      <c r="AJ66" s="1270" t="n"/>
+      <c r="AK66" s="1270" t="n"/>
+      <c r="AL66" s="1271" t="n"/>
       <c r="AN66" s="1149" t="n"/>
     </row>
     <row r="67" ht="15" customHeight="1">
-      <c r="A67" s="1033" t="inlineStr">
+      <c r="A67" s="1250" t="inlineStr">
         <is>
           <t>3 RTW</t>
         </is>
       </c>
-      <c r="B67" s="1148" t="n"/>
       <c r="G67" s="1149" t="n"/>
       <c r="H67" s="1012" t="n"/>
       <c r="I67" s="1012" t="n"/>
@@ -10242,92 +10352,89 @@
       <c r="N67" s="1008" t="n"/>
       <c r="O67" s="1012" t="n"/>
       <c r="P67" s="1012" t="n"/>
-      <c r="Q67" s="1035" t="inlineStr">
+      <c r="Q67" s="1276" t="inlineStr">
         <is>
           <t>RF JNCO 27/03</t>
         </is>
       </c>
-      <c r="R67" s="732" t="n"/>
-      <c r="S67" s="732" t="n"/>
-      <c r="T67" s="732" t="n"/>
-      <c r="U67" s="732" t="n"/>
-      <c r="V67" s="732" t="n"/>
-      <c r="W67" s="732" t="n"/>
-      <c r="X67" s="732" t="n"/>
-      <c r="Y67" s="732" t="n"/>
-      <c r="Z67" s="732" t="n"/>
-      <c r="AA67" s="732" t="n"/>
-      <c r="AB67" s="732" t="n"/>
-      <c r="AC67" s="732" t="n"/>
-      <c r="AD67" s="732" t="n"/>
-      <c r="AE67" s="732" t="n"/>
-      <c r="AF67" s="732" t="n"/>
-      <c r="AG67" s="732" t="n"/>
-      <c r="AH67" s="732" t="n"/>
-      <c r="AI67" s="732" t="n"/>
-      <c r="AJ67" s="732" t="n"/>
-      <c r="AK67" s="732" t="n"/>
-      <c r="AL67" s="733" t="n"/>
-      <c r="AM67" s="1148" t="n"/>
+      <c r="R67" s="1270" t="n"/>
+      <c r="S67" s="1270" t="n"/>
+      <c r="T67" s="1270" t="n"/>
+      <c r="U67" s="1270" t="n"/>
+      <c r="V67" s="1270" t="n"/>
+      <c r="W67" s="1270" t="n"/>
+      <c r="X67" s="1270" t="n"/>
+      <c r="Y67" s="1270" t="n"/>
+      <c r="Z67" s="1270" t="n"/>
+      <c r="AA67" s="1270" t="n"/>
+      <c r="AB67" s="1270" t="n"/>
+      <c r="AC67" s="1270" t="n"/>
+      <c r="AD67" s="1270" t="n"/>
+      <c r="AE67" s="1270" t="n"/>
+      <c r="AF67" s="1270" t="n"/>
+      <c r="AG67" s="1270" t="n"/>
+      <c r="AH67" s="1270" t="n"/>
+      <c r="AI67" s="1270" t="n"/>
+      <c r="AJ67" s="1270" t="n"/>
+      <c r="AK67" s="1270" t="n"/>
+      <c r="AL67" s="1271" t="n"/>
       <c r="AN67" s="1149" t="n"/>
     </row>
     <row r="68" ht="15" customHeight="1" thickBot="1">
-      <c r="A68" s="1037" t="inlineStr">
+      <c r="A68" s="1252" t="inlineStr">
         <is>
           <t>SNCO Wing</t>
         </is>
       </c>
-      <c r="B68" s="1148" t="n"/>
       <c r="G68" s="1149" t="n"/>
-      <c r="H68" s="1083" t="inlineStr">
+      <c r="H68" s="1279" t="inlineStr">
         <is>
           <t>RF SNCO 27/02</t>
         </is>
       </c>
-      <c r="I68" s="732" t="n"/>
-      <c r="J68" s="732" t="n"/>
-      <c r="K68" s="732" t="n"/>
-      <c r="L68" s="732" t="n"/>
-      <c r="M68" s="732" t="n"/>
-      <c r="N68" s="732" t="n"/>
-      <c r="O68" s="732" t="n"/>
-      <c r="P68" s="732" t="n"/>
-      <c r="Q68" s="732" t="n"/>
-      <c r="R68" s="732" t="n"/>
-      <c r="S68" s="732" t="n"/>
-      <c r="T68" s="732" t="n"/>
-      <c r="U68" s="732" t="n"/>
-      <c r="V68" s="732" t="n"/>
-      <c r="W68" s="732" t="n"/>
-      <c r="X68" s="732" t="n"/>
-      <c r="Y68" s="732" t="n"/>
-      <c r="Z68" s="732" t="n"/>
-      <c r="AA68" s="732" t="n"/>
-      <c r="AB68" s="732" t="n"/>
-      <c r="AC68" s="732" t="n"/>
-      <c r="AD68" s="732" t="n"/>
-      <c r="AE68" s="732" t="n"/>
-      <c r="AF68" s="732" t="n"/>
-      <c r="AG68" s="732" t="n"/>
-      <c r="AH68" s="732" t="n"/>
-      <c r="AI68" s="732" t="n"/>
-      <c r="AJ68" s="732" t="n"/>
-      <c r="AK68" s="765" t="n"/>
-      <c r="AL68" s="1096" t="inlineStr">
+      <c r="I68" s="1270" t="n"/>
+      <c r="J68" s="1270" t="n"/>
+      <c r="K68" s="1270" t="n"/>
+      <c r="L68" s="1270" t="n"/>
+      <c r="M68" s="1270" t="n"/>
+      <c r="N68" s="1270" t="n"/>
+      <c r="O68" s="1270" t="n"/>
+      <c r="P68" s="1270" t="n"/>
+      <c r="Q68" s="1270" t="n"/>
+      <c r="R68" s="1270" t="n"/>
+      <c r="S68" s="1270" t="n"/>
+      <c r="T68" s="1270" t="n"/>
+      <c r="U68" s="1270" t="n"/>
+      <c r="V68" s="1270" t="n"/>
+      <c r="W68" s="1270" t="n"/>
+      <c r="X68" s="1270" t="n"/>
+      <c r="Y68" s="1270" t="n"/>
+      <c r="Z68" s="1270" t="n"/>
+      <c r="AA68" s="1270" t="n"/>
+      <c r="AB68" s="1270" t="n"/>
+      <c r="AC68" s="1270" t="n"/>
+      <c r="AD68" s="1270" t="n"/>
+      <c r="AE68" s="1270" t="n"/>
+      <c r="AF68" s="1270" t="n"/>
+      <c r="AG68" s="1270" t="n"/>
+      <c r="AH68" s="1270" t="n"/>
+      <c r="AI68" s="1270" t="n"/>
+      <c r="AJ68" s="1270" t="n"/>
+      <c r="AK68" s="1271" t="n"/>
+      <c r="AL68" s="1258" t="inlineStr">
         <is>
           <t>EX K</t>
         </is>
       </c>
-      <c r="AM68" s="1148" t="n"/>
       <c r="AN68" s="1149" t="n"/>
     </row>
     <row r="69" ht="15" customHeight="1">
-      <c r="A69" s="1039" t="inlineStr">
+      <c r="A69" s="1253" t="inlineStr">
         <is>
           <t>WO Wing</t>
         </is>
       </c>
-      <c r="B69" s="1154" t="n"/>
+      <c r="B69" s="1155" t="n"/>
       <c r="C69" s="1155" t="n"/>
       <c r="D69" s="1155" t="n"/>
       <c r="E69" s="1155" t="n"/>
@@ -10364,7 +10471,7 @@
       <c r="AJ69" s="1012" t="n"/>
       <c r="AK69" s="1045" t="n"/>
       <c r="AL69" s="1087" t="n"/>
-      <c r="AM69" s="1154" t="n"/>
+      <c r="AM69" s="1155" t="n"/>
       <c r="AN69" s="1156" t="n"/>
     </row>
     <row r="70" ht="6" customHeight="1">
@@ -10410,118 +10517,112 @@
       <c r="AN70" s="1225" t="n"/>
     </row>
     <row r="71" ht="14" customHeight="1" thickBot="1">
-      <c r="A71" s="1228" t="inlineStr">
+      <c r="A71" s="1236" t="inlineStr">
         <is>
           <t>June</t>
         </is>
       </c>
-      <c r="B71" s="1002" t="n"/>
-      <c r="C71" s="1147" t="n"/>
-      <c r="D71" s="720" t="n">
+      <c r="B71" s="1266" t="n"/>
+      <c r="C71" s="1149" t="n"/>
+      <c r="D71" s="1238" t="n">
         <v>1</v>
       </c>
-      <c r="E71" s="720" t="n">
+      <c r="E71" s="1238" t="n">
         <v>2</v>
       </c>
-      <c r="F71" s="720" t="n">
+      <c r="F71" s="1238" t="n">
         <v>3</v>
       </c>
-      <c r="G71" s="720" t="n">
+      <c r="G71" s="1238" t="n">
         <v>4</v>
       </c>
-      <c r="H71" s="721" t="n">
+      <c r="H71" s="1239" t="n">
         <v>5</v>
       </c>
-      <c r="I71" s="721" t="n">
+      <c r="I71" s="1239" t="n">
         <v>6</v>
       </c>
-      <c r="J71" s="720" t="n">
+      <c r="J71" s="1238" t="n">
         <v>7</v>
       </c>
-      <c r="K71" s="720" t="n">
+      <c r="K71" s="1238" t="n">
         <v>8</v>
       </c>
-      <c r="L71" s="720" t="n">
+      <c r="L71" s="1238" t="n">
         <v>9</v>
       </c>
-      <c r="M71" s="720" t="n">
+      <c r="M71" s="1238" t="n">
         <v>10</v>
       </c>
-      <c r="N71" s="720" t="n">
+      <c r="N71" s="1238" t="n">
         <v>11</v>
       </c>
-      <c r="O71" s="721" t="n">
+      <c r="O71" s="1239" t="n">
         <v>12</v>
       </c>
-      <c r="P71" s="721" t="n">
+      <c r="P71" s="1239" t="n">
         <v>13</v>
       </c>
-      <c r="Q71" s="720" t="n">
+      <c r="Q71" s="1238" t="n">
         <v>14</v>
       </c>
-      <c r="R71" s="720" t="n">
+      <c r="R71" s="1238" t="n">
         <v>15</v>
       </c>
-      <c r="S71" s="720" t="n">
+      <c r="S71" s="1238" t="n">
         <v>16</v>
       </c>
-      <c r="T71" s="720" t="n">
+      <c r="T71" s="1238" t="n">
         <v>17</v>
       </c>
-      <c r="U71" s="720" t="n">
+      <c r="U71" s="1238" t="n">
         <v>18</v>
       </c>
-      <c r="V71" s="721" t="n">
+      <c r="V71" s="1239" t="n">
         <v>19</v>
       </c>
-      <c r="W71" s="721" t="n">
+      <c r="W71" s="1239" t="n">
         <v>20</v>
       </c>
-      <c r="X71" s="720" t="n">
+      <c r="X71" s="1238" t="n">
         <v>21</v>
       </c>
-      <c r="Y71" s="720" t="n">
+      <c r="Y71" s="1238" t="n">
         <v>22</v>
       </c>
-      <c r="Z71" s="720" t="n">
+      <c r="Z71" s="1238" t="n">
         <v>23</v>
       </c>
-      <c r="AA71" s="720" t="n">
+      <c r="AA71" s="1238" t="n">
         <v>24</v>
       </c>
-      <c r="AB71" s="720" t="n">
+      <c r="AB71" s="1238" t="n">
         <v>25</v>
       </c>
-      <c r="AC71" s="721" t="n">
+      <c r="AC71" s="1239" t="n">
         <v>26</v>
       </c>
-      <c r="AD71" s="721" t="n">
+      <c r="AD71" s="1239" t="n">
         <v>27</v>
       </c>
-      <c r="AE71" s="720" t="n">
+      <c r="AE71" s="1238" t="n">
         <v>28</v>
       </c>
-      <c r="AF71" s="720" t="n">
+      <c r="AF71" s="1238" t="n">
         <v>29</v>
       </c>
-      <c r="AG71" s="720" t="n">
+      <c r="AG71" s="1238" t="n">
         <v>30</v>
       </c>
-      <c r="AH71" s="1002" t="n"/>
-      <c r="AI71" s="1146" t="n"/>
-      <c r="AJ71" s="1146" t="n"/>
-      <c r="AK71" s="1146" t="n"/>
-      <c r="AL71" s="1146" t="n"/>
-      <c r="AM71" s="1146" t="n"/>
-      <c r="AN71" s="1147" t="n"/>
+      <c r="AH71" s="1266" t="n"/>
+      <c r="AN71" s="1149" t="n"/>
     </row>
     <row r="72" ht="15" customHeight="1" thickBot="1">
-      <c r="A72" s="1206" t="inlineStr">
+      <c r="A72" s="1241" t="inlineStr">
         <is>
           <t>ACS</t>
         </is>
       </c>
-      <c r="B72" s="1148" t="n"/>
       <c r="C72" s="1149" t="n"/>
       <c r="D72" s="1008" t="n"/>
       <c r="E72" s="1008" t="n"/>
@@ -10553,12 +10654,10 @@
       <c r="AE72" s="1008" t="n"/>
       <c r="AF72" s="1013" t="n"/>
       <c r="AG72" s="1099" t="n"/>
-      <c r="AH72" s="1148" t="n"/>
       <c r="AN72" s="1149" t="n"/>
     </row>
     <row r="73" ht="15" customHeight="1" thickBot="1">
-      <c r="A73" s="729" t="n"/>
-      <c r="B73" s="1148" t="n"/>
+      <c r="A73" s="1268" t="n"/>
       <c r="C73" s="1149" t="n"/>
       <c r="D73" s="1008" t="n"/>
       <c r="E73" s="1008" t="n"/>
@@ -10590,16 +10689,14 @@
       <c r="AE73" s="1008" t="n"/>
       <c r="AF73" s="1013" t="n"/>
       <c r="AG73" s="1099" t="n"/>
-      <c r="AH73" s="1148" t="n"/>
       <c r="AN73" s="1149" t="n"/>
     </row>
     <row r="74" ht="15" customHeight="1">
-      <c r="A74" s="1211" t="inlineStr">
+      <c r="A74" s="1242" t="inlineStr">
         <is>
           <t>OCS (NZ)</t>
         </is>
       </c>
-      <c r="B74" s="1148" t="n"/>
       <c r="C74" s="1149" t="n"/>
       <c r="D74" s="1009" t="n"/>
       <c r="E74" s="1009" t="n"/>
@@ -10621,26 +10718,24 @@
       <c r="U74" s="1015" t="n"/>
       <c r="V74" s="1015" t="n"/>
       <c r="W74" s="1015" t="n"/>
-      <c r="X74" s="1017" t="inlineStr">
+      <c r="X74" s="1269" t="inlineStr">
         <is>
           <t>EX AEH</t>
         </is>
       </c>
-      <c r="Y74" s="732" t="n"/>
-      <c r="Z74" s="732" t="n"/>
-      <c r="AA74" s="732" t="n"/>
-      <c r="AB74" s="732" t="n"/>
-      <c r="AC74" s="732" t="n"/>
-      <c r="AD74" s="732" t="n"/>
-      <c r="AE74" s="732" t="n"/>
-      <c r="AF74" s="732" t="n"/>
-      <c r="AG74" s="733" t="n"/>
-      <c r="AH74" s="1148" t="n"/>
+      <c r="Y74" s="1270" t="n"/>
+      <c r="Z74" s="1270" t="n"/>
+      <c r="AA74" s="1270" t="n"/>
+      <c r="AB74" s="1270" t="n"/>
+      <c r="AC74" s="1270" t="n"/>
+      <c r="AD74" s="1270" t="n"/>
+      <c r="AE74" s="1270" t="n"/>
+      <c r="AF74" s="1270" t="n"/>
+      <c r="AG74" s="1271" t="n"/>
       <c r="AN74" s="1149" t="n"/>
     </row>
     <row r="75" ht="15" customHeight="1">
-      <c r="A75" s="726" t="n"/>
-      <c r="B75" s="1148" t="n"/>
+      <c r="A75" s="1272" t="n"/>
       <c r="C75" s="1149" t="n"/>
       <c r="D75" s="1008" t="n"/>
       <c r="E75" s="1008" t="n"/>
@@ -10672,12 +10767,10 @@
       <c r="AE75" s="1008" t="n"/>
       <c r="AF75" s="1013" t="n"/>
       <c r="AG75" s="1099" t="n"/>
-      <c r="AH75" s="1148" t="n"/>
       <c r="AN75" s="1149" t="n"/>
     </row>
     <row r="76" ht="15" customHeight="1">
-      <c r="A76" s="729" t="n"/>
-      <c r="B76" s="1148" t="n"/>
+      <c r="A76" s="1268" t="n"/>
       <c r="C76" s="1149" t="n"/>
       <c r="D76" s="1008" t="n"/>
       <c r="E76" s="1008" t="n"/>
@@ -10709,25 +10802,23 @@
       <c r="AE76" s="1008" t="n"/>
       <c r="AF76" s="1013" t="n"/>
       <c r="AG76" s="1099" t="n"/>
-      <c r="AH76" s="1148" t="n"/>
       <c r="AN76" s="1149" t="n"/>
     </row>
     <row r="77" ht="15" customHeight="1" thickBot="1">
-      <c r="A77" s="1020" t="inlineStr">
+      <c r="A77" s="1244" t="inlineStr">
         <is>
           <t>ALC LD Wing</t>
         </is>
       </c>
-      <c r="B77" s="1148" t="n"/>
       <c r="C77" s="1149" t="n"/>
-      <c r="D77" s="1021" t="inlineStr">
+      <c r="D77" s="1273" t="inlineStr">
         <is>
           <t>LEAD TEAMS LTN</t>
         </is>
       </c>
-      <c r="E77" s="739" t="n"/>
-      <c r="F77" s="739" t="n"/>
-      <c r="G77" s="740" t="n"/>
+      <c r="E77" s="1155" t="n"/>
+      <c r="F77" s="1155" t="n"/>
+      <c r="G77" s="1156" t="n"/>
       <c r="H77" s="1012" t="n"/>
       <c r="I77" s="1012" t="n"/>
       <c r="J77" s="1012" t="n"/>
@@ -10754,16 +10845,14 @@
       <c r="AE77" s="1008" t="n"/>
       <c r="AF77" s="1013" t="n"/>
       <c r="AG77" s="1099" t="n"/>
-      <c r="AH77" s="1148" t="n"/>
       <c r="AN77" s="1149" t="n"/>
     </row>
     <row r="78" ht="15" customHeight="1" thickBot="1">
-      <c r="A78" s="1027" t="inlineStr">
+      <c r="A78" s="1246" t="inlineStr">
         <is>
           <t>ALC ELDA Wing</t>
         </is>
       </c>
-      <c r="B78" s="1148" t="n"/>
       <c r="C78" s="1149" t="n"/>
       <c r="D78" s="1008" t="n"/>
       <c r="E78" s="1008" t="n"/>
@@ -10779,18 +10868,18 @@
       <c r="O78" s="1012" t="n"/>
       <c r="P78" s="1012" t="n"/>
       <c r="Q78" s="1008" t="n"/>
-      <c r="R78" s="1028" t="inlineStr">
+      <c r="R78" s="1274" t="inlineStr">
         <is>
           <t>LEAD SYS</t>
         </is>
       </c>
-      <c r="S78" s="744" t="n"/>
-      <c r="T78" s="744" t="n"/>
-      <c r="U78" s="744" t="n"/>
-      <c r="V78" s="744" t="n"/>
-      <c r="W78" s="744" t="n"/>
-      <c r="X78" s="744" t="n"/>
-      <c r="Y78" s="745" t="n"/>
+      <c r="S78" s="1155" t="n"/>
+      <c r="T78" s="1155" t="n"/>
+      <c r="U78" s="1155" t="n"/>
+      <c r="V78" s="1155" t="n"/>
+      <c r="W78" s="1155" t="n"/>
+      <c r="X78" s="1155" t="n"/>
+      <c r="Y78" s="1156" t="n"/>
       <c r="Z78" s="1013" t="n"/>
       <c r="AA78" s="1008" t="n"/>
       <c r="AB78" s="1012" t="n"/>
@@ -10799,159 +10888,152 @@
       <c r="AE78" s="1008" t="n"/>
       <c r="AF78" s="1013" t="n"/>
       <c r="AG78" s="1099" t="n"/>
-      <c r="AH78" s="1148" t="n"/>
       <c r="AN78" s="1149" t="n"/>
     </row>
     <row r="79" ht="15" customHeight="1">
-      <c r="A79" s="1030" t="inlineStr">
+      <c r="A79" s="1248" t="inlineStr">
         <is>
           <t>2 RTW</t>
         </is>
       </c>
-      <c r="B79" s="1148" t="n"/>
       <c r="C79" s="1149" t="n"/>
-      <c r="D79" s="1054" t="inlineStr">
+      <c r="D79" s="1275" t="inlineStr">
         <is>
           <t>RF JNCO 27/04</t>
         </is>
       </c>
-      <c r="E79" s="732" t="n"/>
-      <c r="F79" s="732" t="n"/>
-      <c r="G79" s="732" t="n"/>
-      <c r="H79" s="732" t="n"/>
-      <c r="I79" s="732" t="n"/>
-      <c r="J79" s="732" t="n"/>
-      <c r="K79" s="732" t="n"/>
-      <c r="L79" s="732" t="n"/>
-      <c r="M79" s="732" t="n"/>
-      <c r="N79" s="732" t="n"/>
-      <c r="O79" s="732" t="n"/>
-      <c r="P79" s="732" t="n"/>
-      <c r="Q79" s="732" t="n"/>
-      <c r="R79" s="732" t="n"/>
-      <c r="S79" s="732" t="n"/>
-      <c r="T79" s="732" t="n"/>
-      <c r="U79" s="732" t="n"/>
-      <c r="V79" s="732" t="n"/>
-      <c r="W79" s="732" t="n"/>
-      <c r="X79" s="732" t="n"/>
-      <c r="Y79" s="732" t="n"/>
-      <c r="Z79" s="732" t="n"/>
-      <c r="AA79" s="732" t="n"/>
-      <c r="AB79" s="732" t="n"/>
-      <c r="AC79" s="732" t="n"/>
-      <c r="AD79" s="732" t="n"/>
-      <c r="AE79" s="732" t="n"/>
-      <c r="AF79" s="732" t="n"/>
-      <c r="AG79" s="733" t="n"/>
-      <c r="AH79" s="1148" t="n"/>
+      <c r="E79" s="1270" t="n"/>
+      <c r="F79" s="1270" t="n"/>
+      <c r="G79" s="1270" t="n"/>
+      <c r="H79" s="1270" t="n"/>
+      <c r="I79" s="1270" t="n"/>
+      <c r="J79" s="1270" t="n"/>
+      <c r="K79" s="1270" t="n"/>
+      <c r="L79" s="1270" t="n"/>
+      <c r="M79" s="1270" t="n"/>
+      <c r="N79" s="1270" t="n"/>
+      <c r="O79" s="1270" t="n"/>
+      <c r="P79" s="1270" t="n"/>
+      <c r="Q79" s="1270" t="n"/>
+      <c r="R79" s="1270" t="n"/>
+      <c r="S79" s="1270" t="n"/>
+      <c r="T79" s="1270" t="n"/>
+      <c r="U79" s="1270" t="n"/>
+      <c r="V79" s="1270" t="n"/>
+      <c r="W79" s="1270" t="n"/>
+      <c r="X79" s="1270" t="n"/>
+      <c r="Y79" s="1270" t="n"/>
+      <c r="Z79" s="1270" t="n"/>
+      <c r="AA79" s="1270" t="n"/>
+      <c r="AB79" s="1270" t="n"/>
+      <c r="AC79" s="1270" t="n"/>
+      <c r="AD79" s="1270" t="n"/>
+      <c r="AE79" s="1270" t="n"/>
+      <c r="AF79" s="1270" t="n"/>
+      <c r="AG79" s="1271" t="n"/>
       <c r="AN79" s="1149" t="n"/>
     </row>
     <row r="80" ht="15" customHeight="1" thickBot="1">
-      <c r="A80" s="1033" t="inlineStr">
+      <c r="A80" s="1250" t="inlineStr">
         <is>
           <t>3 RTW</t>
         </is>
       </c>
-      <c r="B80" s="1148" t="n"/>
       <c r="C80" s="1149" t="n"/>
-      <c r="D80" s="1101" t="inlineStr">
+      <c r="D80" s="1276" t="inlineStr">
         <is>
           <t>RF JNCO 27/03</t>
         </is>
       </c>
-      <c r="E80" s="732" t="n"/>
-      <c r="F80" s="732" t="n"/>
-      <c r="G80" s="732" t="n"/>
-      <c r="H80" s="732" t="n"/>
-      <c r="I80" s="732" t="n"/>
-      <c r="J80" s="732" t="n"/>
-      <c r="K80" s="732" t="n"/>
-      <c r="L80" s="732" t="n"/>
-      <c r="M80" s="732" t="n"/>
-      <c r="N80" s="732" t="n"/>
-      <c r="O80" s="732" t="n"/>
-      <c r="P80" s="732" t="n"/>
-      <c r="Q80" s="732" t="n"/>
-      <c r="R80" s="732" t="n"/>
-      <c r="S80" s="732" t="n"/>
-      <c r="T80" s="732" t="n"/>
-      <c r="U80" s="732" t="n"/>
-      <c r="V80" s="732" t="n"/>
-      <c r="W80" s="732" t="n"/>
-      <c r="X80" s="732" t="n"/>
-      <c r="Y80" s="732" t="n"/>
-      <c r="Z80" s="732" t="n"/>
-      <c r="AA80" s="732" t="n"/>
-      <c r="AB80" s="732" t="n"/>
-      <c r="AC80" s="732" t="n"/>
-      <c r="AD80" s="765" t="n"/>
-      <c r="AE80" s="1035" t="inlineStr">
+      <c r="E80" s="1270" t="n"/>
+      <c r="F80" s="1270" t="n"/>
+      <c r="G80" s="1270" t="n"/>
+      <c r="H80" s="1270" t="n"/>
+      <c r="I80" s="1270" t="n"/>
+      <c r="J80" s="1270" t="n"/>
+      <c r="K80" s="1270" t="n"/>
+      <c r="L80" s="1270" t="n"/>
+      <c r="M80" s="1270" t="n"/>
+      <c r="N80" s="1270" t="n"/>
+      <c r="O80" s="1270" t="n"/>
+      <c r="P80" s="1270" t="n"/>
+      <c r="Q80" s="1270" t="n"/>
+      <c r="R80" s="1270" t="n"/>
+      <c r="S80" s="1270" t="n"/>
+      <c r="T80" s="1270" t="n"/>
+      <c r="U80" s="1270" t="n"/>
+      <c r="V80" s="1270" t="n"/>
+      <c r="W80" s="1270" t="n"/>
+      <c r="X80" s="1270" t="n"/>
+      <c r="Y80" s="1270" t="n"/>
+      <c r="Z80" s="1270" t="n"/>
+      <c r="AA80" s="1270" t="n"/>
+      <c r="AB80" s="1270" t="n"/>
+      <c r="AC80" s="1270" t="n"/>
+      <c r="AD80" s="1271" t="n"/>
+      <c r="AE80" s="1276" t="inlineStr">
         <is>
           <t>EX YOUNG LION</t>
         </is>
       </c>
-      <c r="AF80" s="732" t="n"/>
-      <c r="AG80" s="733" t="n"/>
-      <c r="AH80" s="1148" t="n"/>
+      <c r="AF80" s="1270" t="n"/>
+      <c r="AG80" s="1271" t="n"/>
       <c r="AN80" s="1149" t="n"/>
     </row>
     <row r="81" ht="15" customHeight="1">
-      <c r="A81" s="1037" t="inlineStr">
+      <c r="A81" s="1252" t="inlineStr">
         <is>
           <t>SNCO Wing</t>
         </is>
       </c>
-      <c r="B81" s="1148" t="n"/>
       <c r="C81" s="1149" t="n"/>
-      <c r="D81" s="1168" t="inlineStr">
+      <c r="D81" s="1279" t="inlineStr">
         <is>
           <t>EX KALAMATI</t>
         </is>
       </c>
-      <c r="E81" s="732" t="n"/>
-      <c r="F81" s="732" t="n"/>
-      <c r="G81" s="732" t="n"/>
-      <c r="H81" s="732" t="n"/>
-      <c r="I81" s="732" t="n"/>
-      <c r="J81" s="732" t="n"/>
-      <c r="K81" s="732" t="n"/>
-      <c r="L81" s="732" t="n"/>
-      <c r="M81" s="732" t="n"/>
-      <c r="N81" s="732" t="n"/>
-      <c r="O81" s="732" t="n"/>
-      <c r="P81" s="732" t="n"/>
-      <c r="Q81" s="732" t="n"/>
-      <c r="R81" s="732" t="n"/>
-      <c r="S81" s="732" t="n"/>
-      <c r="T81" s="732" t="n"/>
-      <c r="U81" s="1160" t="n"/>
-      <c r="V81" s="1103" t="inlineStr">
+      <c r="E81" s="1270" t="n"/>
+      <c r="F81" s="1270" t="n"/>
+      <c r="G81" s="1270" t="n"/>
+      <c r="H81" s="1270" t="n"/>
+      <c r="I81" s="1270" t="n"/>
+      <c r="J81" s="1270" t="n"/>
+      <c r="K81" s="1270" t="n"/>
+      <c r="L81" s="1270" t="n"/>
+      <c r="M81" s="1270" t="n"/>
+      <c r="N81" s="1270" t="n"/>
+      <c r="O81" s="1270" t="n"/>
+      <c r="P81" s="1270" t="n"/>
+      <c r="Q81" s="1270" t="n"/>
+      <c r="R81" s="1270" t="n"/>
+      <c r="S81" s="1270" t="n"/>
+      <c r="T81" s="1270" t="n"/>
+      <c r="U81" s="1271" t="n"/>
+      <c r="V81" s="1279" t="inlineStr">
         <is>
           <t>RF SNCO 27/02</t>
         </is>
       </c>
-      <c r="W81" s="732" t="n"/>
-      <c r="X81" s="732" t="n"/>
-      <c r="Y81" s="732" t="n"/>
-      <c r="Z81" s="732" t="n"/>
-      <c r="AA81" s="732" t="n"/>
-      <c r="AB81" s="765" t="n"/>
+      <c r="W81" s="1270" t="n"/>
+      <c r="X81" s="1270" t="n"/>
+      <c r="Y81" s="1270" t="n"/>
+      <c r="Z81" s="1270" t="n"/>
+      <c r="AA81" s="1270" t="n"/>
+      <c r="AB81" s="1271" t="n"/>
       <c r="AC81" s="1012" t="n"/>
       <c r="AD81" s="1012" t="n"/>
       <c r="AE81" s="1008" t="n"/>
       <c r="AF81" s="1013" t="n"/>
       <c r="AG81" s="1099" t="n"/>
-      <c r="AH81" s="1148" t="n"/>
       <c r="AN81" s="1149" t="n"/>
     </row>
     <row r="82" ht="15" customHeight="1">
-      <c r="A82" s="1039" t="inlineStr">
+      <c r="A82" s="1253" t="inlineStr">
         <is>
           <t>WO Wing</t>
         </is>
       </c>
-      <c r="B82" s="1154" t="n"/>
+      <c r="B82" s="1155" t="n"/>
       <c r="C82" s="1156" t="n"/>
       <c r="D82" s="1008" t="n"/>
       <c r="E82" s="1008" t="n"/>
@@ -10983,7 +11065,7 @@
       <c r="AE82" s="1008" t="n"/>
       <c r="AF82" s="1013" t="n"/>
       <c r="AG82" s="1099" t="n"/>
-      <c r="AH82" s="1154" t="n"/>
+      <c r="AH82" s="1155" t="n"/>
       <c r="AI82" s="1155" t="n"/>
       <c r="AJ82" s="1155" t="n"/>
       <c r="AK82" s="1155" t="n"/>
@@ -11034,120 +11116,115 @@
       <c r="AN83" s="1225" t="n"/>
     </row>
     <row r="84" ht="14" customHeight="1">
-      <c r="A84" s="1228" t="inlineStr">
+      <c r="A84" s="1236" t="inlineStr">
         <is>
           <t>July</t>
         </is>
       </c>
-      <c r="B84" s="1042" t="n"/>
-      <c r="C84" s="1146" t="n"/>
-      <c r="D84" s="1146" t="n"/>
-      <c r="E84" s="1147" t="n"/>
-      <c r="F84" s="720" t="n">
+      <c r="B84" s="1278" t="n"/>
+      <c r="E84" s="1149" t="n"/>
+      <c r="F84" s="1238" t="n">
         <v>1</v>
       </c>
-      <c r="G84" s="720" t="n">
+      <c r="G84" s="1238" t="n">
         <v>2</v>
       </c>
-      <c r="H84" s="721" t="n">
+      <c r="H84" s="1239" t="n">
         <v>3</v>
       </c>
-      <c r="I84" s="721" t="n">
+      <c r="I84" s="1239" t="n">
         <v>4</v>
       </c>
-      <c r="J84" s="720" t="n">
+      <c r="J84" s="1238" t="n">
         <v>5</v>
       </c>
-      <c r="K84" s="720" t="n">
+      <c r="K84" s="1238" t="n">
         <v>6</v>
       </c>
-      <c r="L84" s="720" t="n">
+      <c r="L84" s="1238" t="n">
         <v>7</v>
       </c>
-      <c r="M84" s="720" t="n">
+      <c r="M84" s="1238" t="n">
         <v>8</v>
       </c>
-      <c r="N84" s="720" t="n">
+      <c r="N84" s="1238" t="n">
         <v>9</v>
       </c>
-      <c r="O84" s="721" t="n">
+      <c r="O84" s="1239" t="n">
         <v>10</v>
       </c>
-      <c r="P84" s="721" t="n">
+      <c r="P84" s="1239" t="n">
         <v>11</v>
       </c>
-      <c r="Q84" s="720" t="n">
+      <c r="Q84" s="1238" t="n">
         <v>12</v>
       </c>
-      <c r="R84" s="720" t="n">
+      <c r="R84" s="1238" t="n">
         <v>13</v>
       </c>
-      <c r="S84" s="720" t="n">
+      <c r="S84" s="1238" t="n">
         <v>14</v>
       </c>
-      <c r="T84" s="720" t="n">
+      <c r="T84" s="1238" t="n">
         <v>15</v>
       </c>
-      <c r="U84" s="720" t="n">
+      <c r="U84" s="1238" t="n">
         <v>16</v>
       </c>
-      <c r="V84" s="721" t="n">
+      <c r="V84" s="1239" t="n">
         <v>17</v>
       </c>
-      <c r="W84" s="721" t="n">
+      <c r="W84" s="1239" t="n">
         <v>18</v>
       </c>
-      <c r="X84" s="720" t="n">
+      <c r="X84" s="1238" t="n">
         <v>19</v>
       </c>
-      <c r="Y84" s="720" t="n">
+      <c r="Y84" s="1238" t="n">
         <v>20</v>
       </c>
-      <c r="Z84" s="720" t="n">
+      <c r="Z84" s="1238" t="n">
         <v>21</v>
       </c>
-      <c r="AA84" s="720" t="n">
+      <c r="AA84" s="1238" t="n">
         <v>22</v>
       </c>
-      <c r="AB84" s="720" t="n">
+      <c r="AB84" s="1238" t="n">
         <v>23</v>
       </c>
-      <c r="AC84" s="721" t="n">
+      <c r="AC84" s="1239" t="n">
         <v>24</v>
       </c>
-      <c r="AD84" s="721" t="n">
+      <c r="AD84" s="1239" t="n">
         <v>25</v>
       </c>
-      <c r="AE84" s="720" t="n">
+      <c r="AE84" s="1238" t="n">
         <v>26</v>
       </c>
-      <c r="AF84" s="720" t="n">
+      <c r="AF84" s="1238" t="n">
         <v>27</v>
       </c>
-      <c r="AG84" s="720" t="n">
+      <c r="AG84" s="1238" t="n">
         <v>28</v>
       </c>
-      <c r="AH84" s="720" t="n">
+      <c r="AH84" s="1238" t="n">
         <v>29</v>
       </c>
-      <c r="AI84" s="720" t="n">
+      <c r="AI84" s="1238" t="n">
         <v>30</v>
       </c>
-      <c r="AJ84" s="721" t="n">
+      <c r="AJ84" s="1239" t="n">
         <v>31</v>
       </c>
-      <c r="AK84" s="1002" t="n"/>
-      <c r="AL84" s="1146" t="n"/>
-      <c r="AM84" s="1146" t="n"/>
-      <c r="AN84" s="1147" t="n"/>
+      <c r="AK84" s="1266" t="n"/>
+      <c r="AN84" s="1149" t="n"/>
     </row>
     <row r="85" ht="15" customHeight="1" thickBot="1">
-      <c r="A85" s="1206" t="inlineStr">
+      <c r="A85" s="1241" t="inlineStr">
         <is>
           <t>ACS</t>
         </is>
       </c>
-      <c r="B85" s="1148" t="n"/>
       <c r="E85" s="1149" t="n"/>
       <c r="F85" s="1024" t="n"/>
       <c r="G85" s="1024" t="n"/>
@@ -11180,12 +11257,10 @@
       <c r="AH85" s="1008" t="n"/>
       <c r="AI85" s="1099" t="n"/>
       <c r="AJ85" s="1074" t="n"/>
-      <c r="AK85" s="1148" t="n"/>
       <c r="AN85" s="1149" t="n"/>
     </row>
     <row r="86" ht="15" customHeight="1">
-      <c r="A86" s="729" t="n"/>
-      <c r="B86" s="1148" t="n"/>
+      <c r="A86" s="1268" t="n"/>
       <c r="E86" s="1149" t="n"/>
       <c r="F86" s="1024" t="n"/>
       <c r="G86" s="1024" t="n"/>
@@ -11218,33 +11293,31 @@
       <c r="AH86" s="1008" t="n"/>
       <c r="AI86" s="1099" t="n"/>
       <c r="AJ86" s="1074" t="n"/>
-      <c r="AK86" s="1148" t="n"/>
       <c r="AN86" s="1149" t="n"/>
     </row>
     <row r="87" ht="15" customHeight="1">
-      <c r="A87" s="1211" t="inlineStr">
+      <c r="A87" s="1242" t="inlineStr">
         <is>
           <t>OCS (NZ)</t>
         </is>
       </c>
-      <c r="B87" s="1148" t="n"/>
       <c r="E87" s="1149" t="n"/>
-      <c r="F87" s="1048" t="inlineStr">
+      <c r="F87" s="1269" t="inlineStr">
         <is>
           <t>EX AEH</t>
         </is>
       </c>
-      <c r="G87" s="732" t="n"/>
-      <c r="H87" s="732" t="n"/>
-      <c r="I87" s="732" t="n"/>
-      <c r="J87" s="732" t="n"/>
-      <c r="K87" s="732" t="n"/>
-      <c r="L87" s="732" t="n"/>
-      <c r="M87" s="732" t="n"/>
-      <c r="N87" s="732" t="n"/>
-      <c r="O87" s="732" t="n"/>
-      <c r="P87" s="732" t="n"/>
-      <c r="Q87" s="765" t="n"/>
+      <c r="G87" s="1270" t="n"/>
+      <c r="H87" s="1270" t="n"/>
+      <c r="I87" s="1270" t="n"/>
+      <c r="J87" s="1270" t="n"/>
+      <c r="K87" s="1270" t="n"/>
+      <c r="L87" s="1270" t="n"/>
+      <c r="M87" s="1270" t="n"/>
+      <c r="N87" s="1270" t="n"/>
+      <c r="O87" s="1270" t="n"/>
+      <c r="P87" s="1270" t="n"/>
+      <c r="Q87" s="1271" t="n"/>
       <c r="R87" s="1009" t="n"/>
       <c r="S87" s="1009" t="n"/>
       <c r="T87" s="1009" t="n"/>
@@ -11264,12 +11337,10 @@
       <c r="AH87" s="1009" t="n"/>
       <c r="AI87" s="1099" t="n"/>
       <c r="AJ87" s="1074" t="n"/>
-      <c r="AK87" s="1148" t="n"/>
       <c r="AN87" s="1149" t="n"/>
     </row>
     <row r="88" ht="15" customHeight="1">
-      <c r="A88" s="726" t="n"/>
-      <c r="B88" s="1148" t="n"/>
+      <c r="A88" s="1272" t="n"/>
       <c r="E88" s="1149" t="n"/>
       <c r="F88" s="1024" t="n"/>
       <c r="G88" s="1024" t="n"/>
@@ -11302,12 +11373,10 @@
       <c r="AH88" s="1009" t="n"/>
       <c r="AI88" s="1099" t="n"/>
       <c r="AJ88" s="1074" t="n"/>
-      <c r="AK88" s="1148" t="n"/>
       <c r="AN88" s="1149" t="n"/>
     </row>
     <row r="89" ht="15" customHeight="1" thickBot="1">
-      <c r="A89" s="729" t="n"/>
-      <c r="B89" s="1148" t="n"/>
+      <c r="A89" s="1268" t="n"/>
       <c r="E89" s="1149" t="n"/>
       <c r="F89" s="1024" t="n"/>
       <c r="G89" s="1024" t="n"/>
@@ -11340,16 +11409,14 @@
       <c r="AH89" s="1008" t="n"/>
       <c r="AI89" s="1099" t="n"/>
       <c r="AJ89" s="1074" t="n"/>
-      <c r="AK89" s="1148" t="n"/>
       <c r="AN89" s="1149" t="n"/>
     </row>
     <row r="90" ht="15" customHeight="1" thickBot="1">
-      <c r="A90" s="1020" t="inlineStr">
+      <c r="A90" s="1244" t="inlineStr">
         <is>
           <t>ALC LD Wing</t>
         </is>
       </c>
-      <c r="B90" s="1148" t="n"/>
       <c r="E90" s="1149" t="n"/>
       <c r="F90" s="1024" t="n"/>
       <c r="G90" s="1024" t="n"/>
@@ -11382,16 +11449,14 @@
       <c r="AH90" s="1008" t="n"/>
       <c r="AI90" s="1099" t="n"/>
       <c r="AJ90" s="1074" t="n"/>
-      <c r="AK90" s="1148" t="n"/>
       <c r="AN90" s="1149" t="n"/>
     </row>
     <row r="91" ht="15" customHeight="1">
-      <c r="A91" s="1027" t="inlineStr">
+      <c r="A91" s="1246" t="inlineStr">
         <is>
           <t>ALC ELDA Wing</t>
         </is>
       </c>
-      <c r="B91" s="1148" t="n"/>
       <c r="E91" s="1149" t="n"/>
       <c r="F91" s="1024" t="n"/>
       <c r="G91" s="1024" t="n"/>
@@ -11424,95 +11489,91 @@
       <c r="AH91" s="1008" t="n"/>
       <c r="AI91" s="1099" t="n"/>
       <c r="AJ91" s="1074" t="n"/>
-      <c r="AK91" s="1148" t="n"/>
       <c r="AN91" s="1149" t="n"/>
     </row>
     <row r="92" ht="15" customHeight="1" thickBot="1">
-      <c r="A92" s="1030" t="inlineStr">
+      <c r="A92" s="1248" t="inlineStr">
         <is>
           <t>2 RTW</t>
         </is>
       </c>
-      <c r="B92" s="1148" t="n"/>
       <c r="E92" s="1149" t="n"/>
-      <c r="F92" s="1082" t="inlineStr">
+      <c r="F92" s="1275" t="inlineStr">
         <is>
           <t>RF JNCO 27/04</t>
         </is>
       </c>
-      <c r="G92" s="732" t="n"/>
-      <c r="H92" s="732" t="n"/>
-      <c r="I92" s="732" t="n"/>
-      <c r="J92" s="732" t="n"/>
-      <c r="K92" s="732" t="n"/>
-      <c r="L92" s="732" t="n"/>
-      <c r="M92" s="732" t="n"/>
-      <c r="N92" s="732" t="n"/>
-      <c r="O92" s="732" t="n"/>
-      <c r="P92" s="765" t="n"/>
-      <c r="Q92" s="1067" t="inlineStr">
+      <c r="G92" s="1270" t="n"/>
+      <c r="H92" s="1270" t="n"/>
+      <c r="I92" s="1270" t="n"/>
+      <c r="J92" s="1270" t="n"/>
+      <c r="K92" s="1270" t="n"/>
+      <c r="L92" s="1270" t="n"/>
+      <c r="M92" s="1270" t="n"/>
+      <c r="N92" s="1270" t="n"/>
+      <c r="O92" s="1270" t="n"/>
+      <c r="P92" s="1271" t="n"/>
+      <c r="Q92" s="1275" t="inlineStr">
         <is>
           <t>EX YOUNG LION</t>
         </is>
       </c>
-      <c r="R92" s="732" t="n"/>
-      <c r="S92" s="732" t="n"/>
-      <c r="T92" s="732" t="n"/>
-      <c r="U92" s="732" t="n"/>
-      <c r="V92" s="732" t="n"/>
-      <c r="W92" s="732" t="n"/>
-      <c r="X92" s="732" t="n"/>
-      <c r="Y92" s="732" t="n"/>
-      <c r="Z92" s="732" t="n"/>
-      <c r="AA92" s="732" t="n"/>
-      <c r="AB92" s="765" t="n"/>
-      <c r="AC92" s="1031" t="inlineStr">
+      <c r="R92" s="1270" t="n"/>
+      <c r="S92" s="1270" t="n"/>
+      <c r="T92" s="1270" t="n"/>
+      <c r="U92" s="1270" t="n"/>
+      <c r="V92" s="1270" t="n"/>
+      <c r="W92" s="1270" t="n"/>
+      <c r="X92" s="1270" t="n"/>
+      <c r="Y92" s="1270" t="n"/>
+      <c r="Z92" s="1270" t="n"/>
+      <c r="AA92" s="1270" t="n"/>
+      <c r="AB92" s="1271" t="n"/>
+      <c r="AC92" s="1275" t="inlineStr">
         <is>
           <t>RF JNCO 27/04</t>
         </is>
       </c>
-      <c r="AD92" s="732" t="n"/>
-      <c r="AE92" s="732" t="n"/>
-      <c r="AF92" s="732" t="n"/>
-      <c r="AG92" s="732" t="n"/>
-      <c r="AH92" s="732" t="n"/>
-      <c r="AI92" s="732" t="n"/>
-      <c r="AJ92" s="733" t="n"/>
-      <c r="AK92" s="1148" t="n"/>
+      <c r="AD92" s="1270" t="n"/>
+      <c r="AE92" s="1270" t="n"/>
+      <c r="AF92" s="1270" t="n"/>
+      <c r="AG92" s="1270" t="n"/>
+      <c r="AH92" s="1270" t="n"/>
+      <c r="AI92" s="1270" t="n"/>
+      <c r="AJ92" s="1271" t="n"/>
       <c r="AN92" s="1149" t="n"/>
     </row>
     <row r="93" ht="15" customHeight="1">
-      <c r="A93" s="1033" t="inlineStr">
+      <c r="A93" s="1250" t="inlineStr">
         <is>
           <t>3 RTW</t>
         </is>
       </c>
-      <c r="B93" s="1148" t="n"/>
       <c r="E93" s="1149" t="n"/>
-      <c r="F93" s="1101" t="inlineStr">
+      <c r="F93" s="1276" t="inlineStr">
         <is>
           <t>EX YOUNG LION</t>
         </is>
       </c>
-      <c r="G93" s="732" t="n"/>
-      <c r="H93" s="732" t="n"/>
-      <c r="I93" s="732" t="n"/>
-      <c r="J93" s="732" t="n"/>
-      <c r="K93" s="732" t="n"/>
-      <c r="L93" s="732" t="n"/>
-      <c r="M93" s="732" t="n"/>
-      <c r="N93" s="765" t="n"/>
-      <c r="O93" s="1069" t="inlineStr">
+      <c r="G93" s="1270" t="n"/>
+      <c r="H93" s="1270" t="n"/>
+      <c r="I93" s="1270" t="n"/>
+      <c r="J93" s="1270" t="n"/>
+      <c r="K93" s="1270" t="n"/>
+      <c r="L93" s="1270" t="n"/>
+      <c r="M93" s="1270" t="n"/>
+      <c r="N93" s="1271" t="n"/>
+      <c r="O93" s="1276" t="inlineStr">
         <is>
           <t>RF JNCO 27/03</t>
         </is>
       </c>
-      <c r="P93" s="732" t="n"/>
-      <c r="Q93" s="732" t="n"/>
-      <c r="R93" s="732" t="n"/>
-      <c r="S93" s="732" t="n"/>
-      <c r="T93" s="732" t="n"/>
-      <c r="U93" s="765" t="n"/>
+      <c r="P93" s="1270" t="n"/>
+      <c r="Q93" s="1270" t="n"/>
+      <c r="R93" s="1270" t="n"/>
+      <c r="S93" s="1270" t="n"/>
+      <c r="T93" s="1270" t="n"/>
+      <c r="U93" s="1271" t="n"/>
       <c r="V93" s="1012" t="n"/>
       <c r="W93" s="1012" t="n"/>
       <c r="X93" s="1008" t="n"/>
@@ -11528,16 +11589,14 @@
       <c r="AH93" s="1008" t="n"/>
       <c r="AI93" s="1099" t="n"/>
       <c r="AJ93" s="1074" t="n"/>
-      <c r="AK93" s="1148" t="n"/>
       <c r="AN93" s="1149" t="n"/>
     </row>
     <row r="94" ht="15" customHeight="1">
-      <c r="A94" s="1037" t="inlineStr">
+      <c r="A94" s="1252" t="inlineStr">
         <is>
           <t>SNCO Wing</t>
         </is>
       </c>
-      <c r="B94" s="1148" t="n"/>
       <c r="E94" s="1149" t="n"/>
       <c r="F94" s="1024" t="n"/>
       <c r="G94" s="1024" t="n"/>
@@ -11570,16 +11629,15 @@
       <c r="AH94" s="1008" t="n"/>
       <c r="AI94" s="1099" t="n"/>
       <c r="AJ94" s="1074" t="n"/>
-      <c r="AK94" s="1148" t="n"/>
       <c r="AN94" s="1149" t="n"/>
     </row>
     <row r="95" ht="15" customHeight="1" thickBot="1">
-      <c r="A95" s="1039" t="inlineStr">
+      <c r="A95" s="1253" t="inlineStr">
         <is>
           <t>WO Wing</t>
         </is>
       </c>
-      <c r="B95" s="1154" t="n"/>
+      <c r="B95" s="1155" t="n"/>
       <c r="C95" s="1155" t="n"/>
       <c r="D95" s="1155" t="n"/>
       <c r="E95" s="1156" t="n"/>
@@ -11614,7 +11672,7 @@
       <c r="AH95" s="1008" t="n"/>
       <c r="AI95" s="1099" t="n"/>
       <c r="AJ95" s="1074" t="n"/>
-      <c r="AK95" s="1154" t="n"/>
+      <c r="AK95" s="1155" t="n"/>
       <c r="AL95" s="1155" t="n"/>
       <c r="AM95" s="1155" t="n"/>
       <c r="AN95" s="1156" t="n"/>
@@ -11662,120 +11720,114 @@
       <c r="AN96" s="1225" t="n"/>
     </row>
     <row r="97" ht="14" customHeight="1" thickBot="1">
-      <c r="A97" s="1228" t="inlineStr">
+      <c r="A97" s="1236" t="inlineStr">
         <is>
           <t>August</t>
         </is>
       </c>
-      <c r="B97" s="1042" t="n"/>
-      <c r="C97" s="1146" t="n"/>
-      <c r="D97" s="1146" t="n"/>
-      <c r="E97" s="1146" t="n"/>
-      <c r="F97" s="1146" t="n"/>
-      <c r="G97" s="1146" t="n"/>
-      <c r="H97" s="1147" t="n"/>
-      <c r="I97" s="721" t="n">
+      <c r="B97" s="1278" t="n"/>
+      <c r="H97" s="1149" t="n"/>
+      <c r="I97" s="1239" t="n">
         <v>1</v>
       </c>
-      <c r="J97" s="720" t="n">
+      <c r="J97" s="1238" t="n">
         <v>2</v>
       </c>
-      <c r="K97" s="720" t="n">
+      <c r="K97" s="1238" t="n">
         <v>3</v>
       </c>
-      <c r="L97" s="720" t="n">
+      <c r="L97" s="1238" t="n">
         <v>4</v>
       </c>
-      <c r="M97" s="720" t="n">
+      <c r="M97" s="1238" t="n">
         <v>5</v>
       </c>
-      <c r="N97" s="720" t="n">
+      <c r="N97" s="1238" t="n">
         <v>6</v>
       </c>
-      <c r="O97" s="721" t="n">
+      <c r="O97" s="1239" t="n">
         <v>7</v>
       </c>
-      <c r="P97" s="721" t="n">
+      <c r="P97" s="1239" t="n">
         <v>8</v>
       </c>
-      <c r="Q97" s="720" t="n">
+      <c r="Q97" s="1238" t="n">
         <v>9</v>
       </c>
-      <c r="R97" s="720" t="n">
+      <c r="R97" s="1238" t="n">
         <v>10</v>
       </c>
-      <c r="S97" s="720" t="n">
+      <c r="S97" s="1238" t="n">
         <v>11</v>
       </c>
-      <c r="T97" s="720" t="n">
+      <c r="T97" s="1238" t="n">
         <v>12</v>
       </c>
-      <c r="U97" s="720" t="n">
+      <c r="U97" s="1238" t="n">
         <v>13</v>
       </c>
-      <c r="V97" s="721" t="n">
+      <c r="V97" s="1239" t="n">
         <v>14</v>
       </c>
-      <c r="W97" s="721" t="n">
+      <c r="W97" s="1239" t="n">
         <v>15</v>
       </c>
-      <c r="X97" s="720" t="n">
+      <c r="X97" s="1238" t="n">
         <v>16</v>
       </c>
-      <c r="Y97" s="720" t="n">
+      <c r="Y97" s="1238" t="n">
         <v>17</v>
       </c>
-      <c r="Z97" s="720" t="n">
+      <c r="Z97" s="1238" t="n">
         <v>18</v>
       </c>
-      <c r="AA97" s="720" t="n">
+      <c r="AA97" s="1238" t="n">
         <v>19</v>
       </c>
-      <c r="AB97" s="720" t="n">
+      <c r="AB97" s="1238" t="n">
         <v>20</v>
       </c>
-      <c r="AC97" s="721" t="n">
+      <c r="AC97" s="1239" t="n">
         <v>21</v>
       </c>
-      <c r="AD97" s="721" t="n">
+      <c r="AD97" s="1239" t="n">
         <v>22</v>
       </c>
-      <c r="AE97" s="720" t="n">
+      <c r="AE97" s="1238" t="n">
         <v>23</v>
       </c>
-      <c r="AF97" s="720" t="n">
+      <c r="AF97" s="1238" t="n">
         <v>24</v>
       </c>
-      <c r="AG97" s="720" t="n">
+      <c r="AG97" s="1238" t="n">
         <v>25</v>
       </c>
-      <c r="AH97" s="720" t="n">
+      <c r="AH97" s="1238" t="n">
         <v>26</v>
       </c>
-      <c r="AI97" s="720" t="n">
+      <c r="AI97" s="1238" t="n">
         <v>27</v>
       </c>
-      <c r="AJ97" s="721" t="n">
+      <c r="AJ97" s="1239" t="n">
         <v>28</v>
       </c>
-      <c r="AK97" s="721" t="n">
+      <c r="AK97" s="1239" t="n">
         <v>29</v>
       </c>
-      <c r="AL97" s="720" t="n">
+      <c r="AL97" s="1238" t="n">
         <v>30</v>
       </c>
-      <c r="AM97" s="720" t="n">
+      <c r="AM97" s="1238" t="n">
         <v>31</v>
       </c>
-      <c r="AN97" s="1002" t="n"/>
+      <c r="AN97" s="1266" t="n"/>
     </row>
     <row r="98" ht="15" customHeight="1">
-      <c r="A98" s="1206" t="inlineStr">
+      <c r="A98" s="1241" t="inlineStr">
         <is>
           <t>ACS</t>
         </is>
       </c>
-      <c r="B98" s="1148" t="n"/>
       <c r="H98" s="1149" t="n"/>
       <c r="I98" s="1012" t="n"/>
       <c r="J98" s="1008" t="n"/>
@@ -11808,11 +11860,10 @@
       <c r="AK98" s="1012" t="n"/>
       <c r="AL98" s="1013" t="n"/>
       <c r="AM98" s="1013" t="n"/>
-      <c r="AN98" s="1169" t="n"/>
+      <c r="AN98" s="1149" t="n"/>
     </row>
     <row r="99" ht="15" customHeight="1">
-      <c r="A99" s="729" t="n"/>
-      <c r="B99" s="1148" t="n"/>
+      <c r="A99" s="1268" t="n"/>
       <c r="H99" s="1149" t="n"/>
       <c r="I99" s="1012" t="n"/>
       <c r="J99" s="1008" t="n"/>
@@ -11845,15 +11896,14 @@
       <c r="AK99" s="1012" t="n"/>
       <c r="AL99" s="1013" t="n"/>
       <c r="AM99" s="1013" t="n"/>
-      <c r="AN99" s="1169" t="n"/>
+      <c r="AN99" s="1149" t="n"/>
     </row>
     <row r="100" ht="15" customHeight="1">
-      <c r="A100" s="1211" t="inlineStr">
+      <c r="A100" s="1242" t="inlineStr">
         <is>
           <t>OCS (NZ)</t>
         </is>
       </c>
-      <c r="B100" s="1148" t="n"/>
       <c r="H100" s="1149" t="n"/>
       <c r="I100" s="1015" t="n"/>
       <c r="J100" s="1009" t="n"/>
@@ -11865,40 +11915,39 @@
       <c r="P100" s="1015" t="n"/>
       <c r="Q100" s="1009" t="n"/>
       <c r="R100" s="1009" t="n"/>
-      <c r="S100" s="1170" t="inlineStr">
+      <c r="S100" s="1269" t="inlineStr">
         <is>
           <t>EX SANTICI</t>
         </is>
       </c>
-      <c r="T100" s="732" t="n"/>
-      <c r="U100" s="732" t="n"/>
-      <c r="V100" s="732" t="n"/>
-      <c r="W100" s="732" t="n"/>
-      <c r="X100" s="732" t="n"/>
-      <c r="Y100" s="732" t="n"/>
-      <c r="Z100" s="732" t="n"/>
-      <c r="AA100" s="732" t="n"/>
-      <c r="AB100" s="732" t="n"/>
-      <c r="AC100" s="732" t="n"/>
-      <c r="AD100" s="1160" t="n"/>
-      <c r="AE100" s="1063" t="inlineStr">
+      <c r="T100" s="1270" t="n"/>
+      <c r="U100" s="1270" t="n"/>
+      <c r="V100" s="1270" t="n"/>
+      <c r="W100" s="1270" t="n"/>
+      <c r="X100" s="1270" t="n"/>
+      <c r="Y100" s="1270" t="n"/>
+      <c r="Z100" s="1270" t="n"/>
+      <c r="AA100" s="1270" t="n"/>
+      <c r="AB100" s="1270" t="n"/>
+      <c r="AC100" s="1270" t="n"/>
+      <c r="AD100" s="1271" t="n"/>
+      <c r="AE100" s="1269" t="inlineStr">
         <is>
           <t>EX NEMESIS</t>
         </is>
       </c>
-      <c r="AF100" s="732" t="n"/>
-      <c r="AG100" s="732" t="n"/>
-      <c r="AH100" s="732" t="n"/>
-      <c r="AI100" s="732" t="n"/>
-      <c r="AJ100" s="765" t="n"/>
+      <c r="AF100" s="1270" t="n"/>
+      <c r="AG100" s="1270" t="n"/>
+      <c r="AH100" s="1270" t="n"/>
+      <c r="AI100" s="1270" t="n"/>
+      <c r="AJ100" s="1271" t="n"/>
       <c r="AK100" s="1015" t="n"/>
       <c r="AL100" s="1013" t="n"/>
       <c r="AM100" s="1013" t="n"/>
-      <c r="AN100" s="1169" t="n"/>
+      <c r="AN100" s="1149" t="n"/>
     </row>
     <row r="101" ht="15" customHeight="1">
-      <c r="A101" s="726" t="n"/>
-      <c r="B101" s="1148" t="n"/>
+      <c r="A101" s="1272" t="n"/>
       <c r="H101" s="1149" t="n"/>
       <c r="I101" s="1015" t="n"/>
       <c r="J101" s="1009" t="n"/>
@@ -11931,11 +11980,10 @@
       <c r="AK101" s="1012" t="n"/>
       <c r="AL101" s="1013" t="n"/>
       <c r="AM101" s="1013" t="n"/>
-      <c r="AN101" s="1169" t="n"/>
+      <c r="AN101" s="1149" t="n"/>
     </row>
     <row r="102" ht="15" customHeight="1" thickBot="1">
-      <c r="A102" s="729" t="n"/>
-      <c r="B102" s="1148" t="n"/>
+      <c r="A102" s="1268" t="n"/>
       <c r="H102" s="1149" t="n"/>
       <c r="I102" s="1012" t="n"/>
       <c r="J102" s="1008" t="n"/>
@@ -11968,15 +12016,14 @@
       <c r="AK102" s="1012" t="n"/>
       <c r="AL102" s="1013" t="n"/>
       <c r="AM102" s="1013" t="n"/>
-      <c r="AN102" s="1169" t="n"/>
+      <c r="AN102" s="1149" t="n"/>
     </row>
     <row r="103" ht="15" customHeight="1" thickBot="1">
-      <c r="A103" s="1020" t="inlineStr">
+      <c r="A103" s="1244" t="inlineStr">
         <is>
           <t>ALC LD Wing</t>
         </is>
       </c>
-      <c r="B103" s="1148" t="n"/>
       <c r="H103" s="1149" t="n"/>
       <c r="I103" s="1012" t="n"/>
       <c r="J103" s="1008" t="n"/>
@@ -12009,33 +12056,32 @@
       <c r="AK103" s="1012" t="n"/>
       <c r="AL103" s="1013" t="n"/>
       <c r="AM103" s="1013" t="n"/>
-      <c r="AN103" s="1169" t="n"/>
+      <c r="AN103" s="1149" t="n"/>
     </row>
     <row r="104" ht="15" customHeight="1">
-      <c r="A104" s="1027" t="inlineStr">
+      <c r="A104" s="1246" t="inlineStr">
         <is>
           <t>ALC ELDA Wing</t>
         </is>
       </c>
-      <c r="B104" s="1148" t="n"/>
       <c r="H104" s="1149" t="n"/>
       <c r="I104" s="1012" t="n"/>
       <c r="J104" s="1008" t="n"/>
       <c r="K104" s="1008" t="n"/>
       <c r="L104" s="1008" t="n"/>
       <c r="M104" s="1008" t="n"/>
-      <c r="N104" s="1028" t="inlineStr">
+      <c r="N104" s="1274" t="inlineStr">
         <is>
           <t>LEAD SYS (ADV RACE)</t>
         </is>
       </c>
-      <c r="O104" s="744" t="n"/>
-      <c r="P104" s="744" t="n"/>
-      <c r="Q104" s="744" t="n"/>
-      <c r="R104" s="744" t="n"/>
-      <c r="S104" s="744" t="n"/>
-      <c r="T104" s="744" t="n"/>
-      <c r="U104" s="745" t="n"/>
+      <c r="O104" s="1155" t="n"/>
+      <c r="P104" s="1155" t="n"/>
+      <c r="Q104" s="1155" t="n"/>
+      <c r="R104" s="1155" t="n"/>
+      <c r="S104" s="1155" t="n"/>
+      <c r="T104" s="1155" t="n"/>
+      <c r="U104" s="1156" t="n"/>
       <c r="V104" s="1012" t="n"/>
       <c r="W104" s="1012" t="n"/>
       <c r="X104" s="1008" t="n"/>
@@ -12045,32 +12091,31 @@
       <c r="AB104" s="1008" t="n"/>
       <c r="AC104" s="1012" t="n"/>
       <c r="AD104" s="1012" t="n"/>
-      <c r="AE104" s="1028" t="inlineStr">
+      <c r="AE104" s="1274" t="inlineStr">
         <is>
           <t>LEAD SYS (ALPINE TOUR)</t>
         </is>
       </c>
-      <c r="AF104" s="744" t="n"/>
-      <c r="AG104" s="744" t="n"/>
-      <c r="AH104" s="744" t="n"/>
-      <c r="AI104" s="744" t="n"/>
-      <c r="AJ104" s="744" t="n"/>
-      <c r="AK104" s="745" t="n"/>
-      <c r="AL104" s="1028" t="inlineStr">
+      <c r="AF104" s="1155" t="n"/>
+      <c r="AG104" s="1155" t="n"/>
+      <c r="AH104" s="1155" t="n"/>
+      <c r="AI104" s="1155" t="n"/>
+      <c r="AJ104" s="1155" t="n"/>
+      <c r="AK104" s="1156" t="n"/>
+      <c r="AL104" s="1274" t="inlineStr">
         <is>
           <t>LEAD TEAMS</t>
         </is>
       </c>
-      <c r="AM104" s="745" t="n"/>
-      <c r="AN104" s="1169" t="n"/>
+      <c r="AM104" s="1156" t="n"/>
+      <c r="AN104" s="1149" t="n"/>
     </row>
     <row r="105" ht="15" customHeight="1" thickBot="1">
-      <c r="A105" s="1030" t="inlineStr">
+      <c r="A105" s="1248" t="inlineStr">
         <is>
           <t>2 RTW</t>
         </is>
       </c>
-      <c r="B105" s="1148" t="n"/>
       <c r="H105" s="1149" t="n"/>
       <c r="I105" s="1012" t="n"/>
       <c r="J105" s="1008" t="n"/>
@@ -12100,22 +12145,21 @@
       <c r="AH105" s="1104" t="n"/>
       <c r="AI105" s="1025" t="n"/>
       <c r="AJ105" s="1012" t="n"/>
-      <c r="AK105" s="1031" t="inlineStr">
+      <c r="AK105" s="1275" t="inlineStr">
         <is>
           <t>TF JNCO 27/01</t>
         </is>
       </c>
-      <c r="AL105" s="732" t="n"/>
-      <c r="AM105" s="733" t="n"/>
-      <c r="AN105" s="1169" t="n"/>
+      <c r="AL105" s="1270" t="n"/>
+      <c r="AM105" s="1271" t="n"/>
+      <c r="AN105" s="1149" t="n"/>
     </row>
     <row r="106" ht="15" customHeight="1">
-      <c r="A106" s="1033" t="inlineStr">
+      <c r="A106" s="1250" t="inlineStr">
         <is>
           <t>3 RTW</t>
         </is>
       </c>
-      <c r="B106" s="1148" t="n"/>
       <c r="H106" s="1149" t="n"/>
       <c r="I106" s="1015" t="n"/>
       <c r="J106" s="1009" t="n"/>
@@ -12148,15 +12192,14 @@
       <c r="AK106" s="1012" t="n"/>
       <c r="AL106" s="1013" t="n"/>
       <c r="AM106" s="1013" t="n"/>
-      <c r="AN106" s="1169" t="n"/>
+      <c r="AN106" s="1149" t="n"/>
     </row>
     <row r="107" ht="15" customHeight="1">
-      <c r="A107" s="1037" t="inlineStr">
+      <c r="A107" s="1252" t="inlineStr">
         <is>
           <t>SNCO Wing</t>
         </is>
       </c>
-      <c r="B107" s="1148" t="n"/>
       <c r="H107" s="1149" t="n"/>
       <c r="I107" s="1015" t="n"/>
       <c r="J107" s="1009" t="n"/>
@@ -12165,24 +12208,24 @@
       <c r="M107" s="1009" t="n"/>
       <c r="N107" s="1009" t="n"/>
       <c r="O107" s="1015" t="n"/>
-      <c r="P107" s="1071" t="inlineStr">
+      <c r="P107" s="1279" t="inlineStr">
         <is>
           <t>TF SNCO 27/01</t>
         </is>
       </c>
-      <c r="Q107" s="732" t="n"/>
-      <c r="R107" s="732" t="n"/>
-      <c r="S107" s="732" t="n"/>
-      <c r="T107" s="732" t="n"/>
-      <c r="U107" s="732" t="n"/>
-      <c r="V107" s="732" t="n"/>
-      <c r="W107" s="732" t="n"/>
-      <c r="X107" s="732" t="n"/>
-      <c r="Y107" s="732" t="n"/>
-      <c r="Z107" s="732" t="n"/>
-      <c r="AA107" s="732" t="n"/>
-      <c r="AB107" s="732" t="n"/>
-      <c r="AC107" s="765" t="n"/>
+      <c r="Q107" s="1270" t="n"/>
+      <c r="R107" s="1270" t="n"/>
+      <c r="S107" s="1270" t="n"/>
+      <c r="T107" s="1270" t="n"/>
+      <c r="U107" s="1270" t="n"/>
+      <c r="V107" s="1270" t="n"/>
+      <c r="W107" s="1270" t="n"/>
+      <c r="X107" s="1270" t="n"/>
+      <c r="Y107" s="1270" t="n"/>
+      <c r="Z107" s="1270" t="n"/>
+      <c r="AA107" s="1270" t="n"/>
+      <c r="AB107" s="1270" t="n"/>
+      <c r="AC107" s="1271" t="n"/>
       <c r="AD107" s="1012" t="n"/>
       <c r="AE107" s="1008" t="n"/>
       <c r="AF107" s="1008" t="n"/>
@@ -12193,15 +12236,14 @@
       <c r="AK107" s="1012" t="n"/>
       <c r="AL107" s="1013" t="n"/>
       <c r="AM107" s="1013" t="n"/>
-      <c r="AN107" s="1169" t="n"/>
+      <c r="AN107" s="1149" t="n"/>
     </row>
     <row r="108" ht="15" customHeight="1" thickBot="1">
-      <c r="A108" s="1220" t="inlineStr">
+      <c r="A108" s="1253" t="inlineStr">
         <is>
           <t>WO Wing</t>
         </is>
       </c>
-      <c r="B108" s="1148" t="n"/>
       <c r="H108" s="1149" t="n"/>
       <c r="I108" s="1012" t="n"/>
       <c r="J108" s="1008" t="n"/>
@@ -12234,11 +12276,11 @@
       <c r="AK108" s="1007" t="n"/>
       <c r="AL108" s="1013" t="n"/>
       <c r="AM108" s="1013" t="n"/>
-      <c r="AN108" s="1169" t="n"/>
+      <c r="AN108" s="1149" t="n"/>
     </row>
     <row r="109" ht="15" customHeight="1" thickBot="1">
-      <c r="A109" s="735" t="n"/>
-      <c r="B109" s="1154" t="n"/>
+      <c r="A109" s="1268" t="n"/>
+      <c r="B109" s="1155" t="n"/>
       <c r="C109" s="1155" t="n"/>
       <c r="D109" s="1155" t="n"/>
       <c r="E109" s="1155" t="n"/>
@@ -12276,7 +12318,7 @@
       <c r="AK109" s="1007" t="n"/>
       <c r="AL109" s="1013" t="n"/>
       <c r="AM109" s="1013" t="n"/>
-      <c r="AN109" s="1171" t="n"/>
+      <c r="AN109" s="1156" t="n"/>
     </row>
     <row r="110" ht="6" customHeight="1" thickBot="1">
       <c r="A110" s="1225" t="n"/>
@@ -12321,118 +12363,112 @@
       <c r="AN110" s="1225" t="n"/>
     </row>
     <row r="111" ht="14" customHeight="1">
-      <c r="A111" s="1228" t="inlineStr">
+      <c r="A111" s="1236" t="inlineStr">
         <is>
           <t>September</t>
         </is>
       </c>
-      <c r="B111" s="1042" t="n"/>
-      <c r="C111" s="1146" t="n"/>
-      <c r="D111" s="1147" t="n"/>
-      <c r="E111" s="720" t="n">
+      <c r="B111" s="1278" t="n"/>
+      <c r="D111" s="1149" t="n"/>
+      <c r="E111" s="1238" t="n">
         <v>1</v>
       </c>
-      <c r="F111" s="720" t="n">
+      <c r="F111" s="1238" t="n">
         <v>2</v>
       </c>
-      <c r="G111" s="720" t="n">
+      <c r="G111" s="1238" t="n">
         <v>3</v>
       </c>
-      <c r="H111" s="721" t="n">
+      <c r="H111" s="1239" t="n">
         <v>4</v>
       </c>
-      <c r="I111" s="721" t="n">
+      <c r="I111" s="1239" t="n">
         <v>5</v>
       </c>
-      <c r="J111" s="720" t="n">
+      <c r="J111" s="1238" t="n">
         <v>6</v>
       </c>
-      <c r="K111" s="720" t="n">
+      <c r="K111" s="1238" t="n">
         <v>7</v>
       </c>
-      <c r="L111" s="720" t="n">
+      <c r="L111" s="1238" t="n">
         <v>8</v>
       </c>
-      <c r="M111" s="720" t="n">
+      <c r="M111" s="1238" t="n">
         <v>9</v>
       </c>
-      <c r="N111" s="720" t="n">
+      <c r="N111" s="1238" t="n">
         <v>10</v>
       </c>
-      <c r="O111" s="721" t="n">
+      <c r="O111" s="1239" t="n">
         <v>11</v>
       </c>
-      <c r="P111" s="721" t="n">
+      <c r="P111" s="1239" t="n">
         <v>12</v>
       </c>
-      <c r="Q111" s="720" t="n">
+      <c r="Q111" s="1238" t="n">
         <v>13</v>
       </c>
-      <c r="R111" s="720" t="n">
+      <c r="R111" s="1238" t="n">
         <v>14</v>
       </c>
-      <c r="S111" s="720" t="n">
+      <c r="S111" s="1238" t="n">
         <v>15</v>
       </c>
-      <c r="T111" s="720" t="n">
+      <c r="T111" s="1238" t="n">
         <v>16</v>
       </c>
-      <c r="U111" s="720" t="n">
+      <c r="U111" s="1238" t="n">
         <v>17</v>
       </c>
-      <c r="V111" s="721" t="n">
+      <c r="V111" s="1239" t="n">
         <v>18</v>
       </c>
-      <c r="W111" s="721" t="n">
+      <c r="W111" s="1239" t="n">
         <v>19</v>
       </c>
-      <c r="X111" s="720" t="n">
+      <c r="X111" s="1238" t="n">
         <v>20</v>
       </c>
-      <c r="Y111" s="720" t="n">
+      <c r="Y111" s="1238" t="n">
         <v>21</v>
       </c>
-      <c r="Z111" s="720" t="n">
+      <c r="Z111" s="1238" t="n">
         <v>22</v>
       </c>
-      <c r="AA111" s="720" t="n">
+      <c r="AA111" s="1238" t="n">
         <v>23</v>
       </c>
-      <c r="AB111" s="720" t="n">
+      <c r="AB111" s="1238" t="n">
         <v>24</v>
       </c>
-      <c r="AC111" s="721" t="n">
+      <c r="AC111" s="1239" t="n">
         <v>25</v>
       </c>
-      <c r="AD111" s="721" t="n">
+      <c r="AD111" s="1239" t="n">
         <v>26</v>
       </c>
-      <c r="AE111" s="720" t="n">
+      <c r="AE111" s="1238" t="n">
         <v>27</v>
       </c>
-      <c r="AF111" s="720" t="n">
+      <c r="AF111" s="1238" t="n">
         <v>28</v>
       </c>
-      <c r="AG111" s="720" t="n">
+      <c r="AG111" s="1238" t="n">
         <v>29</v>
       </c>
-      <c r="AH111" s="720" t="n">
+      <c r="AH111" s="1238" t="n">
         <v>30</v>
       </c>
-      <c r="AI111" s="1002" t="n"/>
-      <c r="AJ111" s="1146" t="n"/>
-      <c r="AK111" s="1146" t="n"/>
-      <c r="AL111" s="1146" t="n"/>
-      <c r="AM111" s="1146" t="n"/>
-      <c r="AN111" s="1147" t="n"/>
+      <c r="AI111" s="1266" t="n"/>
+      <c r="AN111" s="1149" t="n"/>
     </row>
     <row r="112" ht="15" customHeight="1">
-      <c r="A112" s="1206" t="inlineStr">
+      <c r="A112" s="1241" t="inlineStr">
         <is>
           <t>ACS</t>
         </is>
       </c>
-      <c r="B112" s="1148" t="n"/>
       <c r="D112" s="1149" t="n"/>
       <c r="E112" s="1022" t="n"/>
       <c r="F112" s="1022" t="n"/>
@@ -12464,12 +12500,10 @@
       <c r="AF112" s="1008" t="n"/>
       <c r="AG112" s="1013" t="n"/>
       <c r="AH112" s="1099" t="n"/>
-      <c r="AI112" s="1148" t="n"/>
       <c r="AN112" s="1149" t="n"/>
     </row>
     <row r="113" ht="15" customHeight="1">
-      <c r="A113" s="729" t="n"/>
-      <c r="B113" s="1148" t="n"/>
+      <c r="A113" s="1268" t="n"/>
       <c r="D113" s="1149" t="n"/>
       <c r="E113" s="1022" t="n"/>
       <c r="F113" s="1022" t="n"/>
@@ -12501,16 +12535,14 @@
       <c r="AF113" s="1008" t="n"/>
       <c r="AG113" s="1013" t="n"/>
       <c r="AH113" s="1099" t="n"/>
-      <c r="AI113" s="1148" t="n"/>
       <c r="AN113" s="1149" t="n"/>
     </row>
     <row r="114" ht="15" customHeight="1" thickBot="1">
-      <c r="A114" s="1211" t="inlineStr">
+      <c r="A114" s="1242" t="inlineStr">
         <is>
           <t>OCS (NZ)</t>
         </is>
       </c>
-      <c r="B114" s="1148" t="n"/>
       <c r="D114" s="1149" t="n"/>
       <c r="E114" s="1009" t="n"/>
       <c r="F114" s="1009" t="n"/>
@@ -12524,34 +12556,32 @@
       <c r="N114" s="1009" t="n"/>
       <c r="O114" s="1015" t="n"/>
       <c r="P114" s="1015" t="n"/>
-      <c r="Q114" s="1017" t="inlineStr">
+      <c r="Q114" s="1269" t="inlineStr">
         <is>
           <t>EX TAKROUNA</t>
         </is>
       </c>
-      <c r="R114" s="732" t="n"/>
-      <c r="S114" s="732" t="n"/>
-      <c r="T114" s="732" t="n"/>
-      <c r="U114" s="732" t="n"/>
-      <c r="V114" s="732" t="n"/>
-      <c r="W114" s="732" t="n"/>
-      <c r="X114" s="732" t="n"/>
-      <c r="Y114" s="732" t="n"/>
-      <c r="Z114" s="732" t="n"/>
-      <c r="AA114" s="732" t="n"/>
-      <c r="AB114" s="732" t="n"/>
-      <c r="AC114" s="732" t="n"/>
-      <c r="AD114" s="732" t="n"/>
-      <c r="AE114" s="732" t="n"/>
-      <c r="AF114" s="732" t="n"/>
-      <c r="AG114" s="732" t="n"/>
-      <c r="AH114" s="733" t="n"/>
-      <c r="AI114" s="1148" t="n"/>
+      <c r="R114" s="1270" t="n"/>
+      <c r="S114" s="1270" t="n"/>
+      <c r="T114" s="1270" t="n"/>
+      <c r="U114" s="1270" t="n"/>
+      <c r="V114" s="1270" t="n"/>
+      <c r="W114" s="1270" t="n"/>
+      <c r="X114" s="1270" t="n"/>
+      <c r="Y114" s="1270" t="n"/>
+      <c r="Z114" s="1270" t="n"/>
+      <c r="AA114" s="1270" t="n"/>
+      <c r="AB114" s="1270" t="n"/>
+      <c r="AC114" s="1270" t="n"/>
+      <c r="AD114" s="1270" t="n"/>
+      <c r="AE114" s="1270" t="n"/>
+      <c r="AF114" s="1270" t="n"/>
+      <c r="AG114" s="1270" t="n"/>
+      <c r="AH114" s="1271" t="n"/>
       <c r="AN114" s="1149" t="n"/>
     </row>
     <row r="115" ht="15" customHeight="1" thickBot="1">
-      <c r="A115" s="726" t="n"/>
-      <c r="B115" s="1148" t="n"/>
+      <c r="A115" s="1272" t="n"/>
       <c r="D115" s="1149" t="n"/>
       <c r="E115" s="1022" t="n"/>
       <c r="F115" s="1022" t="n"/>
@@ -12583,12 +12613,10 @@
       <c r="AF115" s="1008" t="n"/>
       <c r="AG115" s="1013" t="n"/>
       <c r="AH115" s="1099" t="n"/>
-      <c r="AI115" s="1148" t="n"/>
       <c r="AN115" s="1149" t="n"/>
     </row>
     <row r="116" ht="15" customHeight="1">
-      <c r="A116" s="729" t="n"/>
-      <c r="B116" s="1148" t="n"/>
+      <c r="A116" s="1268" t="n"/>
       <c r="D116" s="1149" t="n"/>
       <c r="E116" s="1022" t="n"/>
       <c r="F116" s="1022" t="n"/>
@@ -12620,31 +12648,29 @@
       <c r="AF116" s="1013" t="n"/>
       <c r="AG116" s="1013" t="n"/>
       <c r="AH116" s="1099" t="n"/>
-      <c r="AI116" s="1148" t="n"/>
       <c r="AN116" s="1149" t="n"/>
     </row>
     <row r="117" ht="15" customHeight="1" thickBot="1">
-      <c r="A117" s="1020" t="inlineStr">
+      <c r="A117" s="1244" t="inlineStr">
         <is>
           <t>ALC LD Wing</t>
         </is>
       </c>
-      <c r="B117" s="1148" t="n"/>
       <c r="D117" s="1149" t="n"/>
       <c r="E117" s="1022" t="n"/>
       <c r="F117" s="1022" t="n"/>
       <c r="G117" s="1022" t="n"/>
       <c r="H117" s="1044" t="n"/>
       <c r="I117" s="1044" t="n"/>
-      <c r="J117" s="1021" t="inlineStr">
+      <c r="J117" s="1273" t="inlineStr">
         <is>
           <t>LEAD TEAMS BMC</t>
         </is>
       </c>
-      <c r="K117" s="739" t="n"/>
-      <c r="L117" s="739" t="n"/>
-      <c r="M117" s="739" t="n"/>
-      <c r="N117" s="740" t="n"/>
+      <c r="K117" s="1155" t="n"/>
+      <c r="L117" s="1155" t="n"/>
+      <c r="M117" s="1155" t="n"/>
+      <c r="N117" s="1156" t="n"/>
       <c r="O117" s="1044" t="n"/>
       <c r="P117" s="1044" t="n"/>
       <c r="Q117" s="1109" t="n"/>
@@ -12654,40 +12680,38 @@
       <c r="U117" s="1110" t="n"/>
       <c r="V117" s="1012" t="n"/>
       <c r="W117" s="1108" t="n"/>
-      <c r="X117" s="1021" t="inlineStr">
+      <c r="X117" s="1273" t="inlineStr">
         <is>
           <t>LEAD TEAMS LTN</t>
         </is>
       </c>
-      <c r="Y117" s="739" t="n"/>
-      <c r="Z117" s="739" t="n"/>
-      <c r="AA117" s="739" t="n"/>
-      <c r="AB117" s="740" t="n"/>
+      <c r="Y117" s="1155" t="n"/>
+      <c r="Z117" s="1155" t="n"/>
+      <c r="AA117" s="1155" t="n"/>
+      <c r="AB117" s="1156" t="n"/>
       <c r="AC117" s="1044" t="n"/>
       <c r="AD117" s="1044" t="n"/>
       <c r="AE117" s="1022" t="n"/>
       <c r="AF117" s="1008" t="n"/>
       <c r="AG117" s="1013" t="n"/>
       <c r="AH117" s="1099" t="n"/>
-      <c r="AI117" s="1148" t="n"/>
       <c r="AN117" s="1149" t="n"/>
     </row>
     <row r="118" ht="15" customHeight="1">
-      <c r="A118" s="1027" t="inlineStr">
+      <c r="A118" s="1246" t="inlineStr">
         <is>
           <t>ALC ELDA Wing</t>
         </is>
       </c>
-      <c r="B118" s="1148" t="n"/>
       <c r="D118" s="1149" t="n"/>
-      <c r="E118" s="1111" t="inlineStr">
+      <c r="E118" s="1274" t="inlineStr">
         <is>
           <t>LEAD TEAMS BMC</t>
         </is>
       </c>
-      <c r="F118" s="795" t="n"/>
-      <c r="G118" s="795" t="n"/>
-      <c r="H118" s="819" t="n"/>
+      <c r="F118" s="1155" t="n"/>
+      <c r="G118" s="1155" t="n"/>
+      <c r="H118" s="1156" t="n"/>
       <c r="I118" s="1044" t="n"/>
       <c r="J118" s="1009" t="n"/>
       <c r="K118" s="1024" t="n"/>
@@ -12696,16 +12720,16 @@
       <c r="N118" s="1024" t="n"/>
       <c r="O118" s="1044" t="n"/>
       <c r="P118" s="1044" t="n"/>
-      <c r="Q118" s="1028" t="inlineStr">
+      <c r="Q118" s="1274" t="inlineStr">
         <is>
           <t>LEAD TEAMS LTN</t>
         </is>
       </c>
-      <c r="R118" s="744" t="n"/>
-      <c r="S118" s="744" t="n"/>
-      <c r="T118" s="744" t="n"/>
-      <c r="U118" s="744" t="n"/>
-      <c r="V118" s="745" t="n"/>
+      <c r="R118" s="1155" t="n"/>
+      <c r="S118" s="1155" t="n"/>
+      <c r="T118" s="1155" t="n"/>
+      <c r="U118" s="1155" t="n"/>
+      <c r="V118" s="1156" t="n"/>
       <c r="W118" s="1012" t="n"/>
       <c r="X118" s="1009" t="n"/>
       <c r="Y118" s="1024" t="n"/>
@@ -12713,41 +12737,39 @@
       <c r="AA118" s="1024" t="n"/>
       <c r="AB118" s="1024" t="n"/>
       <c r="AC118" s="1044" t="n"/>
-      <c r="AD118" s="1028" t="inlineStr">
+      <c r="AD118" s="1274" t="inlineStr">
         <is>
           <t>LEAD LEADERS</t>
         </is>
       </c>
-      <c r="AE118" s="744" t="n"/>
-      <c r="AF118" s="744" t="n"/>
-      <c r="AG118" s="744" t="n"/>
-      <c r="AH118" s="745" t="n"/>
-      <c r="AI118" s="1148" t="n"/>
+      <c r="AE118" s="1155" t="n"/>
+      <c r="AF118" s="1155" t="n"/>
+      <c r="AG118" s="1155" t="n"/>
+      <c r="AH118" s="1156" t="n"/>
       <c r="AN118" s="1149" t="n"/>
     </row>
     <row r="119" ht="15" customHeight="1">
-      <c r="A119" s="1030" t="inlineStr">
+      <c r="A119" s="1248" t="inlineStr">
         <is>
           <t>2 RTW</t>
         </is>
       </c>
-      <c r="B119" s="1148" t="n"/>
       <c r="D119" s="1149" t="n"/>
-      <c r="E119" s="1082" t="inlineStr">
+      <c r="E119" s="1275" t="inlineStr">
         <is>
           <t>TF JNCO 27/01</t>
         </is>
       </c>
-      <c r="F119" s="732" t="n"/>
-      <c r="G119" s="732" t="n"/>
-      <c r="H119" s="732" t="n"/>
-      <c r="I119" s="732" t="n"/>
-      <c r="J119" s="732" t="n"/>
-      <c r="K119" s="732" t="n"/>
-      <c r="L119" s="732" t="n"/>
-      <c r="M119" s="732" t="n"/>
-      <c r="N119" s="732" t="n"/>
-      <c r="O119" s="765" t="n"/>
+      <c r="F119" s="1270" t="n"/>
+      <c r="G119" s="1270" t="n"/>
+      <c r="H119" s="1270" t="n"/>
+      <c r="I119" s="1270" t="n"/>
+      <c r="J119" s="1270" t="n"/>
+      <c r="K119" s="1270" t="n"/>
+      <c r="L119" s="1270" t="n"/>
+      <c r="M119" s="1270" t="n"/>
+      <c r="N119" s="1270" t="n"/>
+      <c r="O119" s="1271" t="n"/>
       <c r="P119" s="1044" t="n"/>
       <c r="Q119" s="1009" t="n"/>
       <c r="R119" s="1009" t="n"/>
@@ -12756,76 +12778,72 @@
       <c r="U119" s="1008" t="n"/>
       <c r="V119" s="1012" t="n"/>
       <c r="W119" s="1012" t="n"/>
-      <c r="X119" s="1031" t="inlineStr">
+      <c r="X119" s="1275" t="inlineStr">
         <is>
           <t>RF JNCO 27/06</t>
         </is>
       </c>
-      <c r="Y119" s="732" t="n"/>
-      <c r="Z119" s="732" t="n"/>
-      <c r="AA119" s="732" t="n"/>
-      <c r="AB119" s="732" t="n"/>
-      <c r="AC119" s="732" t="n"/>
-      <c r="AD119" s="732" t="n"/>
-      <c r="AE119" s="732" t="n"/>
-      <c r="AF119" s="732" t="n"/>
-      <c r="AG119" s="732" t="n"/>
-      <c r="AH119" s="733" t="n"/>
-      <c r="AI119" s="1148" t="n"/>
+      <c r="Y119" s="1270" t="n"/>
+      <c r="Z119" s="1270" t="n"/>
+      <c r="AA119" s="1270" t="n"/>
+      <c r="AB119" s="1270" t="n"/>
+      <c r="AC119" s="1270" t="n"/>
+      <c r="AD119" s="1270" t="n"/>
+      <c r="AE119" s="1270" t="n"/>
+      <c r="AF119" s="1270" t="n"/>
+      <c r="AG119" s="1270" t="n"/>
+      <c r="AH119" s="1271" t="n"/>
       <c r="AN119" s="1149" t="n"/>
     </row>
     <row r="120" ht="15" customHeight="1" thickBot="1">
-      <c r="A120" s="1033" t="inlineStr">
+      <c r="A120" s="1250" t="inlineStr">
         <is>
           <t>3 RTW</t>
         </is>
       </c>
-      <c r="B120" s="1148" t="n"/>
       <c r="D120" s="1149" t="n"/>
       <c r="E120" s="1022" t="n"/>
       <c r="F120" s="1022" t="n"/>
       <c r="G120" s="1022" t="n"/>
       <c r="H120" s="1044" t="n"/>
       <c r="I120" s="1044" t="n"/>
-      <c r="J120" s="1035" t="inlineStr">
+      <c r="J120" s="1276" t="inlineStr">
         <is>
           <t>RF JNCO 27/05</t>
         </is>
       </c>
-      <c r="K120" s="732" t="n"/>
-      <c r="L120" s="732" t="n"/>
-      <c r="M120" s="732" t="n"/>
-      <c r="N120" s="732" t="n"/>
-      <c r="O120" s="732" t="n"/>
-      <c r="P120" s="732" t="n"/>
-      <c r="Q120" s="732" t="n"/>
-      <c r="R120" s="732" t="n"/>
-      <c r="S120" s="732" t="n"/>
-      <c r="T120" s="732" t="n"/>
-      <c r="U120" s="732" t="n"/>
-      <c r="V120" s="732" t="n"/>
-      <c r="W120" s="732" t="n"/>
-      <c r="X120" s="732" t="n"/>
-      <c r="Y120" s="732" t="n"/>
-      <c r="Z120" s="732" t="n"/>
-      <c r="AA120" s="732" t="n"/>
-      <c r="AB120" s="732" t="n"/>
-      <c r="AC120" s="732" t="n"/>
-      <c r="AD120" s="732" t="n"/>
-      <c r="AE120" s="732" t="n"/>
-      <c r="AF120" s="732" t="n"/>
-      <c r="AG120" s="732" t="n"/>
-      <c r="AH120" s="733" t="n"/>
-      <c r="AI120" s="1148" t="n"/>
+      <c r="K120" s="1270" t="n"/>
+      <c r="L120" s="1270" t="n"/>
+      <c r="M120" s="1270" t="n"/>
+      <c r="N120" s="1270" t="n"/>
+      <c r="O120" s="1270" t="n"/>
+      <c r="P120" s="1270" t="n"/>
+      <c r="Q120" s="1270" t="n"/>
+      <c r="R120" s="1270" t="n"/>
+      <c r="S120" s="1270" t="n"/>
+      <c r="T120" s="1270" t="n"/>
+      <c r="U120" s="1270" t="n"/>
+      <c r="V120" s="1270" t="n"/>
+      <c r="W120" s="1270" t="n"/>
+      <c r="X120" s="1270" t="n"/>
+      <c r="Y120" s="1270" t="n"/>
+      <c r="Z120" s="1270" t="n"/>
+      <c r="AA120" s="1270" t="n"/>
+      <c r="AB120" s="1270" t="n"/>
+      <c r="AC120" s="1270" t="n"/>
+      <c r="AD120" s="1270" t="n"/>
+      <c r="AE120" s="1270" t="n"/>
+      <c r="AF120" s="1270" t="n"/>
+      <c r="AG120" s="1270" t="n"/>
+      <c r="AH120" s="1271" t="n"/>
       <c r="AN120" s="1149" t="n"/>
     </row>
     <row r="121" ht="15" customHeight="1" thickBot="1">
-      <c r="A121" s="1037" t="inlineStr">
+      <c r="A121" s="1252" t="inlineStr">
         <is>
           <t>SNCO Wing</t>
         </is>
       </c>
-      <c r="B121" s="1148" t="n"/>
       <c r="D121" s="1149" t="n"/>
       <c r="E121" s="1022" t="n"/>
       <c r="F121" s="1022" t="n"/>
@@ -12853,24 +12871,23 @@
       <c r="AB121" s="1107" t="n"/>
       <c r="AC121" s="1044" t="n"/>
       <c r="AD121" s="1044" t="n"/>
-      <c r="AE121" s="1058" t="inlineStr">
+      <c r="AE121" s="1279" t="inlineStr">
         <is>
           <t>RF SNCO 27/03</t>
         </is>
       </c>
-      <c r="AF121" s="732" t="n"/>
-      <c r="AG121" s="732" t="n"/>
-      <c r="AH121" s="733" t="n"/>
-      <c r="AI121" s="1148" t="n"/>
+      <c r="AF121" s="1270" t="n"/>
+      <c r="AG121" s="1270" t="n"/>
+      <c r="AH121" s="1271" t="n"/>
       <c r="AN121" s="1149" t="n"/>
     </row>
     <row r="122" ht="15" customHeight="1" thickBot="1">
-      <c r="A122" s="1112" t="inlineStr">
+      <c r="A122" s="1253" t="inlineStr">
         <is>
           <t>WO Wing</t>
         </is>
       </c>
-      <c r="B122" s="1154" t="n"/>
+      <c r="B122" s="1155" t="n"/>
       <c r="C122" s="1155" t="n"/>
       <c r="D122" s="1156" t="n"/>
       <c r="E122" s="1006" t="n"/>
@@ -12903,7 +12920,7 @@
       <c r="AF122" s="1006" t="n"/>
       <c r="AG122" s="1013" t="n"/>
       <c r="AH122" s="1099" t="n"/>
-      <c r="AI122" s="1154" t="n"/>
+      <c r="AI122" s="1155" t="n"/>
       <c r="AJ122" s="1155" t="n"/>
       <c r="AK122" s="1155" t="n"/>
       <c r="AL122" s="1155" t="n"/>
@@ -12953,120 +12970,115 @@
       <c r="AN123" s="1225" t="n"/>
     </row>
     <row r="124" ht="14" customHeight="1">
-      <c r="A124" s="1229" t="inlineStr">
+      <c r="A124" s="1236" t="inlineStr">
         <is>
           <t>October</t>
         </is>
       </c>
-      <c r="B124" s="1002" t="n"/>
-      <c r="C124" s="1146" t="n"/>
-      <c r="D124" s="1146" t="n"/>
-      <c r="E124" s="1146" t="n"/>
-      <c r="F124" s="1147" t="n"/>
-      <c r="G124" s="720" t="n">
+      <c r="B124" s="1266" t="n"/>
+      <c r="F124" s="1149" t="n"/>
+      <c r="G124" s="1238" t="n">
         <v>1</v>
       </c>
-      <c r="H124" s="721" t="n">
+      <c r="H124" s="1239" t="n">
         <v>2</v>
       </c>
-      <c r="I124" s="721" t="n">
+      <c r="I124" s="1239" t="n">
         <v>3</v>
       </c>
-      <c r="J124" s="720" t="n">
+      <c r="J124" s="1238" t="n">
         <v>4</v>
       </c>
-      <c r="K124" s="720" t="n">
+      <c r="K124" s="1238" t="n">
         <v>5</v>
       </c>
-      <c r="L124" s="720" t="n">
+      <c r="L124" s="1238" t="n">
         <v>6</v>
       </c>
-      <c r="M124" s="720" t="n">
+      <c r="M124" s="1238" t="n">
         <v>7</v>
       </c>
-      <c r="N124" s="720" t="n">
+      <c r="N124" s="1238" t="n">
         <v>8</v>
       </c>
-      <c r="O124" s="721" t="n">
+      <c r="O124" s="1239" t="n">
         <v>9</v>
       </c>
-      <c r="P124" s="721" t="n">
+      <c r="P124" s="1239" t="n">
         <v>10</v>
       </c>
-      <c r="Q124" s="720" t="n">
+      <c r="Q124" s="1238" t="n">
         <v>11</v>
       </c>
-      <c r="R124" s="720" t="n">
+      <c r="R124" s="1238" t="n">
         <v>12</v>
       </c>
-      <c r="S124" s="720" t="n">
+      <c r="S124" s="1238" t="n">
         <v>13</v>
       </c>
-      <c r="T124" s="720" t="n">
+      <c r="T124" s="1238" t="n">
         <v>14</v>
       </c>
-      <c r="U124" s="720" t="n">
+      <c r="U124" s="1238" t="n">
         <v>15</v>
       </c>
-      <c r="V124" s="721" t="n">
+      <c r="V124" s="1239" t="n">
         <v>16</v>
       </c>
-      <c r="W124" s="721" t="n">
+      <c r="W124" s="1239" t="n">
         <v>17</v>
       </c>
-      <c r="X124" s="720" t="n">
+      <c r="X124" s="1238" t="n">
         <v>18</v>
       </c>
-      <c r="Y124" s="720" t="n">
+      <c r="Y124" s="1238" t="n">
         <v>19</v>
       </c>
-      <c r="Z124" s="720" t="n">
+      <c r="Z124" s="1238" t="n">
         <v>20</v>
       </c>
-      <c r="AA124" s="720" t="n">
+      <c r="AA124" s="1238" t="n">
         <v>21</v>
       </c>
-      <c r="AB124" s="720" t="n">
+      <c r="AB124" s="1238" t="n">
         <v>22</v>
       </c>
-      <c r="AC124" s="721" t="n">
+      <c r="AC124" s="1239" t="n">
         <v>23</v>
       </c>
-      <c r="AD124" s="721" t="n">
+      <c r="AD124" s="1239" t="n">
         <v>24</v>
       </c>
-      <c r="AE124" s="720" t="n">
+      <c r="AE124" s="1238" t="n">
         <v>25</v>
       </c>
-      <c r="AF124" s="720" t="n">
+      <c r="AF124" s="1238" t="n">
         <v>25</v>
       </c>
-      <c r="AG124" s="720" t="n">
+      <c r="AG124" s="1238" t="n">
         <v>27</v>
       </c>
-      <c r="AH124" s="720" t="n">
+      <c r="AH124" s="1238" t="n">
         <v>28</v>
       </c>
-      <c r="AI124" s="720" t="n">
+      <c r="AI124" s="1238" t="n">
         <v>29</v>
       </c>
-      <c r="AJ124" s="721" t="n">
+      <c r="AJ124" s="1239" t="n">
         <v>30</v>
       </c>
-      <c r="AK124" s="721" t="n">
+      <c r="AK124" s="1239" t="n">
         <v>31</v>
       </c>
-      <c r="AL124" s="1042" t="n"/>
-      <c r="AM124" s="1146" t="n"/>
-      <c r="AN124" s="1147" t="n"/>
+      <c r="AL124" s="1278" t="n"/>
+      <c r="AN124" s="1149" t="n"/>
     </row>
     <row r="125" ht="15" customHeight="1">
-      <c r="A125" s="1222" t="inlineStr">
+      <c r="A125" s="1241" t="inlineStr">
         <is>
           <t>ACS</t>
         </is>
       </c>
-      <c r="B125" s="1148" t="n"/>
       <c r="F125" s="1149" t="n"/>
       <c r="G125" s="1013" t="n"/>
       <c r="H125" s="1007" t="n"/>
@@ -13099,12 +13111,10 @@
       <c r="AI125" s="1009" t="n"/>
       <c r="AJ125" s="1045" t="n"/>
       <c r="AK125" s="1045" t="n"/>
-      <c r="AL125" s="1148" t="n"/>
       <c r="AN125" s="1149" t="n"/>
     </row>
     <row r="126" ht="15" customHeight="1" thickBot="1">
-      <c r="A126" s="735" t="n"/>
-      <c r="B126" s="1148" t="n"/>
+      <c r="A126" s="1268" t="n"/>
       <c r="F126" s="1149" t="n"/>
       <c r="G126" s="1110" t="n"/>
       <c r="H126" s="1091" t="n"/>
@@ -13137,24 +13147,22 @@
       <c r="AI126" s="1009" t="n"/>
       <c r="AJ126" s="1045" t="n"/>
       <c r="AK126" s="1045" t="n"/>
-      <c r="AL126" s="1148" t="n"/>
       <c r="AN126" s="1149" t="n"/>
     </row>
     <row r="127" ht="15" customHeight="1" thickBot="1">
-      <c r="A127" s="1208" t="inlineStr">
+      <c r="A127" s="1242" t="inlineStr">
         <is>
           <t>OCS (NZ)</t>
         </is>
       </c>
-      <c r="B127" s="1148" t="n"/>
       <c r="F127" s="1149" t="n"/>
-      <c r="G127" s="1048" t="inlineStr">
+      <c r="G127" s="1269" t="inlineStr">
         <is>
           <t>EX TAKROUNA</t>
         </is>
       </c>
-      <c r="H127" s="732" t="n"/>
-      <c r="I127" s="765" t="n"/>
+      <c r="H127" s="1270" t="n"/>
+      <c r="I127" s="1271" t="n"/>
       <c r="J127" s="1009" t="n"/>
       <c r="K127" s="1009" t="n"/>
       <c r="L127" s="1009" t="n"/>
@@ -13183,12 +13191,10 @@
       <c r="AI127" s="1009" t="n"/>
       <c r="AJ127" s="1045" t="n"/>
       <c r="AK127" s="1045" t="n"/>
-      <c r="AL127" s="1148" t="n"/>
       <c r="AN127" s="1149" t="n"/>
     </row>
     <row r="128" ht="15" customHeight="1">
-      <c r="A128" s="724" t="n"/>
-      <c r="B128" s="1148" t="n"/>
+      <c r="A128" s="1272" t="n"/>
       <c r="F128" s="1149" t="n"/>
       <c r="G128" s="1110" t="n"/>
       <c r="H128" s="1091" t="n"/>
@@ -13221,12 +13227,10 @@
       <c r="AI128" s="1009" t="n"/>
       <c r="AJ128" s="1045" t="n"/>
       <c r="AK128" s="1045" t="n"/>
-      <c r="AL128" s="1148" t="n"/>
       <c r="AN128" s="1149" t="n"/>
     </row>
     <row r="129" ht="15" customHeight="1" thickBot="1">
-      <c r="A129" s="735" t="n"/>
-      <c r="B129" s="1148" t="n"/>
+      <c r="A129" s="1268" t="n"/>
       <c r="F129" s="1149" t="n"/>
       <c r="G129" s="1110" t="n"/>
       <c r="H129" s="1091" t="n"/>
@@ -13259,29 +13263,27 @@
       <c r="AI129" s="1009" t="n"/>
       <c r="AJ129" s="1045" t="n"/>
       <c r="AK129" s="1045" t="n"/>
-      <c r="AL129" s="1148" t="n"/>
       <c r="AN129" s="1149" t="n"/>
     </row>
     <row r="130" ht="15" customHeight="1">
-      <c r="A130" s="1115" t="inlineStr">
+      <c r="A130" s="1244" t="inlineStr">
         <is>
           <t>ALC LD Wing</t>
         </is>
       </c>
-      <c r="B130" s="1148" t="n"/>
       <c r="F130" s="1149" t="n"/>
       <c r="G130" s="1034" t="n"/>
       <c r="H130" s="1091" t="n"/>
       <c r="I130" s="1091" t="n"/>
-      <c r="J130" s="1021" t="inlineStr">
+      <c r="J130" s="1273" t="inlineStr">
         <is>
           <t>LEAD LEADERS</t>
         </is>
       </c>
-      <c r="K130" s="739" t="n"/>
-      <c r="L130" s="739" t="n"/>
-      <c r="M130" s="739" t="n"/>
-      <c r="N130" s="740" t="n"/>
+      <c r="K130" s="1155" t="n"/>
+      <c r="L130" s="1155" t="n"/>
+      <c r="M130" s="1155" t="n"/>
+      <c r="N130" s="1156" t="n"/>
       <c r="O130" s="1091" t="n"/>
       <c r="P130" s="1091" t="n"/>
       <c r="Q130" s="1009" t="n"/>
@@ -13305,19 +13307,17 @@
       <c r="AI130" s="1009" t="n"/>
       <c r="AJ130" s="1045" t="n"/>
       <c r="AK130" s="1045" t="n"/>
-      <c r="AL130" s="1148" t="n"/>
       <c r="AN130" s="1149" t="n"/>
     </row>
     <row r="131" ht="15" customHeight="1">
-      <c r="A131" s="1116" t="inlineStr">
+      <c r="A131" s="1246" t="inlineStr">
         <is>
           <t>ALC ELDA Wing</t>
         </is>
       </c>
-      <c r="B131" s="1148" t="n"/>
       <c r="F131" s="1149" t="n"/>
-      <c r="G131" s="1117" t="n"/>
-      <c r="H131" s="745" t="n"/>
+      <c r="G131" s="1280" t="n"/>
+      <c r="H131" s="1156" t="n"/>
       <c r="I131" s="1091" t="n"/>
       <c r="J131" s="1009" t="n"/>
       <c r="K131" s="1024" t="n"/>
@@ -13325,16 +13325,16 @@
       <c r="M131" s="1024" t="n"/>
       <c r="N131" s="1024" t="n"/>
       <c r="O131" s="1043" t="n"/>
-      <c r="P131" s="1028" t="inlineStr">
+      <c r="P131" s="1274" t="inlineStr">
         <is>
           <t>LEAD LEADERS (OFFICERS)</t>
         </is>
       </c>
-      <c r="Q131" s="744" t="n"/>
-      <c r="R131" s="744" t="n"/>
-      <c r="S131" s="744" t="n"/>
-      <c r="T131" s="744" t="n"/>
-      <c r="U131" s="745" t="n"/>
+      <c r="Q131" s="1155" t="n"/>
+      <c r="R131" s="1155" t="n"/>
+      <c r="S131" s="1155" t="n"/>
+      <c r="T131" s="1155" t="n"/>
+      <c r="U131" s="1156" t="n"/>
       <c r="V131" s="1015" t="n"/>
       <c r="W131" s="1012" t="n"/>
       <c r="X131" s="1009" t="n"/>
@@ -13351,158 +13351,151 @@
       <c r="AI131" s="1009" t="n"/>
       <c r="AJ131" s="1045" t="n"/>
       <c r="AK131" s="1045" t="n"/>
-      <c r="AL131" s="1148" t="n"/>
       <c r="AN131" s="1149" t="n"/>
     </row>
     <row r="132" ht="15" customHeight="1" thickBot="1">
-      <c r="A132" s="1118" t="inlineStr">
+      <c r="A132" s="1248" t="inlineStr">
         <is>
           <t>2 RTW</t>
         </is>
       </c>
-      <c r="B132" s="1148" t="n"/>
       <c r="F132" s="1149" t="n"/>
-      <c r="G132" s="1054" t="inlineStr">
+      <c r="G132" s="1275" t="inlineStr">
         <is>
           <t>RF JNCO 27/06</t>
         </is>
       </c>
-      <c r="H132" s="732" t="n"/>
-      <c r="I132" s="732" t="n"/>
-      <c r="J132" s="732" t="n"/>
-      <c r="K132" s="732" t="n"/>
-      <c r="L132" s="732" t="n"/>
-      <c r="M132" s="732" t="n"/>
-      <c r="N132" s="732" t="n"/>
-      <c r="O132" s="732" t="n"/>
-      <c r="P132" s="732" t="n"/>
-      <c r="Q132" s="732" t="n"/>
-      <c r="R132" s="732" t="n"/>
-      <c r="S132" s="732" t="n"/>
-      <c r="T132" s="732" t="n"/>
-      <c r="U132" s="732" t="n"/>
-      <c r="V132" s="732" t="n"/>
-      <c r="W132" s="732" t="n"/>
-      <c r="X132" s="732" t="n"/>
-      <c r="Y132" s="732" t="n"/>
-      <c r="Z132" s="732" t="n"/>
-      <c r="AA132" s="732" t="n"/>
-      <c r="AB132" s="732" t="n"/>
-      <c r="AC132" s="732" t="n"/>
-      <c r="AD132" s="732" t="n"/>
-      <c r="AE132" s="732" t="n"/>
-      <c r="AF132" s="732" t="n"/>
-      <c r="AG132" s="732" t="n"/>
-      <c r="AH132" s="732" t="n"/>
-      <c r="AI132" s="732" t="n"/>
-      <c r="AJ132" s="732" t="n"/>
-      <c r="AK132" s="733" t="n"/>
-      <c r="AL132" s="1148" t="n"/>
+      <c r="H132" s="1270" t="n"/>
+      <c r="I132" s="1270" t="n"/>
+      <c r="J132" s="1270" t="n"/>
+      <c r="K132" s="1270" t="n"/>
+      <c r="L132" s="1270" t="n"/>
+      <c r="M132" s="1270" t="n"/>
+      <c r="N132" s="1270" t="n"/>
+      <c r="O132" s="1270" t="n"/>
+      <c r="P132" s="1270" t="n"/>
+      <c r="Q132" s="1270" t="n"/>
+      <c r="R132" s="1270" t="n"/>
+      <c r="S132" s="1270" t="n"/>
+      <c r="T132" s="1270" t="n"/>
+      <c r="U132" s="1270" t="n"/>
+      <c r="V132" s="1270" t="n"/>
+      <c r="W132" s="1270" t="n"/>
+      <c r="X132" s="1270" t="n"/>
+      <c r="Y132" s="1270" t="n"/>
+      <c r="Z132" s="1270" t="n"/>
+      <c r="AA132" s="1270" t="n"/>
+      <c r="AB132" s="1270" t="n"/>
+      <c r="AC132" s="1270" t="n"/>
+      <c r="AD132" s="1270" t="n"/>
+      <c r="AE132" s="1270" t="n"/>
+      <c r="AF132" s="1270" t="n"/>
+      <c r="AG132" s="1270" t="n"/>
+      <c r="AH132" s="1270" t="n"/>
+      <c r="AI132" s="1270" t="n"/>
+      <c r="AJ132" s="1270" t="n"/>
+      <c r="AK132" s="1271" t="n"/>
       <c r="AN132" s="1149" t="n"/>
     </row>
     <row r="133" ht="15" customHeight="1" thickBot="1">
-      <c r="A133" s="1119" t="inlineStr">
+      <c r="A133" s="1250" t="inlineStr">
         <is>
           <t>3 RTW</t>
         </is>
       </c>
-      <c r="B133" s="1148" t="n"/>
       <c r="F133" s="1149" t="n"/>
-      <c r="G133" s="1173" t="inlineStr">
+      <c r="G133" s="1276" t="inlineStr">
         <is>
           <t>RF JNCO 27/05</t>
         </is>
       </c>
-      <c r="H133" s="732" t="n"/>
-      <c r="I133" s="732" t="n"/>
-      <c r="J133" s="732" t="n"/>
-      <c r="K133" s="732" t="n"/>
-      <c r="L133" s="732" t="n"/>
-      <c r="M133" s="732" t="n"/>
-      <c r="N133" s="732" t="n"/>
-      <c r="O133" s="732" t="n"/>
-      <c r="P133" s="732" t="n"/>
-      <c r="Q133" s="732" t="n"/>
-      <c r="R133" s="732" t="n"/>
-      <c r="S133" s="732" t="n"/>
-      <c r="T133" s="732" t="n"/>
-      <c r="U133" s="732" t="n"/>
-      <c r="V133" s="732" t="n"/>
-      <c r="W133" s="732" t="n"/>
-      <c r="X133" s="732" t="n"/>
-      <c r="Y133" s="732" t="n"/>
-      <c r="Z133" s="732" t="n"/>
-      <c r="AA133" s="732" t="n"/>
-      <c r="AB133" s="732" t="n"/>
-      <c r="AC133" s="732" t="n"/>
-      <c r="AD133" s="1160" t="n"/>
-      <c r="AE133" s="1121" t="inlineStr">
+      <c r="H133" s="1270" t="n"/>
+      <c r="I133" s="1270" t="n"/>
+      <c r="J133" s="1270" t="n"/>
+      <c r="K133" s="1270" t="n"/>
+      <c r="L133" s="1270" t="n"/>
+      <c r="M133" s="1270" t="n"/>
+      <c r="N133" s="1270" t="n"/>
+      <c r="O133" s="1270" t="n"/>
+      <c r="P133" s="1270" t="n"/>
+      <c r="Q133" s="1270" t="n"/>
+      <c r="R133" s="1270" t="n"/>
+      <c r="S133" s="1270" t="n"/>
+      <c r="T133" s="1270" t="n"/>
+      <c r="U133" s="1270" t="n"/>
+      <c r="V133" s="1270" t="n"/>
+      <c r="W133" s="1270" t="n"/>
+      <c r="X133" s="1270" t="n"/>
+      <c r="Y133" s="1270" t="n"/>
+      <c r="Z133" s="1270" t="n"/>
+      <c r="AA133" s="1270" t="n"/>
+      <c r="AB133" s="1270" t="n"/>
+      <c r="AC133" s="1270" t="n"/>
+      <c r="AD133" s="1271" t="n"/>
+      <c r="AE133" s="1276" t="inlineStr">
         <is>
           <t>EX YOUNG LION</t>
         </is>
       </c>
-      <c r="AF133" s="732" t="n"/>
-      <c r="AG133" s="732" t="n"/>
-      <c r="AH133" s="732" t="n"/>
-      <c r="AI133" s="732" t="n"/>
-      <c r="AJ133" s="732" t="n"/>
-      <c r="AK133" s="733" t="n"/>
-      <c r="AL133" s="1148" t="n"/>
+      <c r="AF133" s="1270" t="n"/>
+      <c r="AG133" s="1270" t="n"/>
+      <c r="AH133" s="1270" t="n"/>
+      <c r="AI133" s="1270" t="n"/>
+      <c r="AJ133" s="1270" t="n"/>
+      <c r="AK133" s="1271" t="n"/>
       <c r="AN133" s="1149" t="n"/>
     </row>
     <row r="134" ht="15" customHeight="1" thickBot="1">
-      <c r="A134" s="1122" t="inlineStr">
+      <c r="A134" s="1252" t="inlineStr">
         <is>
           <t>SNCO Wing</t>
         </is>
       </c>
-      <c r="B134" s="1148" t="n"/>
       <c r="F134" s="1149" t="n"/>
-      <c r="G134" s="1123" t="inlineStr">
+      <c r="G134" s="1279" t="inlineStr">
         <is>
           <t>RF SNCO 27/03</t>
         </is>
       </c>
-      <c r="H134" s="732" t="n"/>
-      <c r="I134" s="732" t="n"/>
-      <c r="J134" s="732" t="n"/>
-      <c r="K134" s="732" t="n"/>
-      <c r="L134" s="732" t="n"/>
-      <c r="M134" s="732" t="n"/>
-      <c r="N134" s="732" t="n"/>
-      <c r="O134" s="732" t="n"/>
-      <c r="P134" s="732" t="n"/>
-      <c r="Q134" s="732" t="n"/>
-      <c r="R134" s="732" t="n"/>
-      <c r="S134" s="732" t="n"/>
-      <c r="T134" s="732" t="n"/>
-      <c r="U134" s="732" t="n"/>
-      <c r="V134" s="732" t="n"/>
-      <c r="W134" s="732" t="n"/>
-      <c r="X134" s="732" t="n"/>
-      <c r="Y134" s="732" t="n"/>
-      <c r="Z134" s="732" t="n"/>
-      <c r="AA134" s="732" t="n"/>
-      <c r="AB134" s="732" t="n"/>
-      <c r="AC134" s="732" t="n"/>
-      <c r="AD134" s="732" t="n"/>
-      <c r="AE134" s="732" t="n"/>
-      <c r="AF134" s="732" t="n"/>
-      <c r="AG134" s="732" t="n"/>
-      <c r="AH134" s="732" t="n"/>
-      <c r="AI134" s="732" t="n"/>
-      <c r="AJ134" s="732" t="n"/>
-      <c r="AK134" s="733" t="n"/>
-      <c r="AL134" s="1148" t="n"/>
+      <c r="H134" s="1270" t="n"/>
+      <c r="I134" s="1270" t="n"/>
+      <c r="J134" s="1270" t="n"/>
+      <c r="K134" s="1270" t="n"/>
+      <c r="L134" s="1270" t="n"/>
+      <c r="M134" s="1270" t="n"/>
+      <c r="N134" s="1270" t="n"/>
+      <c r="O134" s="1270" t="n"/>
+      <c r="P134" s="1270" t="n"/>
+      <c r="Q134" s="1270" t="n"/>
+      <c r="R134" s="1270" t="n"/>
+      <c r="S134" s="1270" t="n"/>
+      <c r="T134" s="1270" t="n"/>
+      <c r="U134" s="1270" t="n"/>
+      <c r="V134" s="1270" t="n"/>
+      <c r="W134" s="1270" t="n"/>
+      <c r="X134" s="1270" t="n"/>
+      <c r="Y134" s="1270" t="n"/>
+      <c r="Z134" s="1270" t="n"/>
+      <c r="AA134" s="1270" t="n"/>
+      <c r="AB134" s="1270" t="n"/>
+      <c r="AC134" s="1270" t="n"/>
+      <c r="AD134" s="1270" t="n"/>
+      <c r="AE134" s="1270" t="n"/>
+      <c r="AF134" s="1270" t="n"/>
+      <c r="AG134" s="1270" t="n"/>
+      <c r="AH134" s="1270" t="n"/>
+      <c r="AI134" s="1270" t="n"/>
+      <c r="AJ134" s="1270" t="n"/>
+      <c r="AK134" s="1271" t="n"/>
       <c r="AN134" s="1149" t="n"/>
     </row>
     <row r="135" ht="15" customHeight="1">
-      <c r="A135" s="1106" t="inlineStr">
+      <c r="A135" s="1253" t="inlineStr">
         <is>
           <t>WO Wing</t>
         </is>
       </c>
-      <c r="B135" s="1154" t="n"/>
+      <c r="B135" s="1155" t="n"/>
       <c r="C135" s="1155" t="n"/>
       <c r="D135" s="1155" t="n"/>
       <c r="E135" s="1155" t="n"/>
@@ -13538,7 +13531,7 @@
       <c r="AI135" s="1008" t="n"/>
       <c r="AJ135" s="1045" t="n"/>
       <c r="AK135" s="1045" t="n"/>
-      <c r="AL135" s="1154" t="n"/>
+      <c r="AL135" s="1155" t="n"/>
       <c r="AM135" s="1155" t="n"/>
       <c r="AN135" s="1156" t="n"/>
     </row>
@@ -13585,118 +13578,111 @@
       <c r="AN136" s="1225" t="n"/>
     </row>
     <row r="137" ht="14" customHeight="1">
-      <c r="A137" s="1228" t="inlineStr">
+      <c r="A137" s="1236" t="inlineStr">
         <is>
           <t>November</t>
         </is>
       </c>
-      <c r="B137" s="1042" t="n"/>
-      <c r="C137" s="1146" t="n"/>
-      <c r="D137" s="1146" t="n"/>
-      <c r="E137" s="1146" t="n"/>
-      <c r="F137" s="1146" t="n"/>
-      <c r="G137" s="1146" t="n"/>
-      <c r="H137" s="1146" t="n"/>
-      <c r="I137" s="1147" t="n"/>
-      <c r="J137" s="720" t="n">
+      <c r="B137" s="1278" t="n"/>
+      <c r="I137" s="1149" t="n"/>
+      <c r="J137" s="1238" t="n">
         <v>1</v>
       </c>
-      <c r="K137" s="720" t="n">
+      <c r="K137" s="1238" t="n">
         <v>2</v>
       </c>
-      <c r="L137" s="720" t="n">
+      <c r="L137" s="1238" t="n">
         <v>3</v>
       </c>
-      <c r="M137" s="720" t="n">
+      <c r="M137" s="1238" t="n">
         <v>4</v>
       </c>
-      <c r="N137" s="720" t="n">
+      <c r="N137" s="1238" t="n">
         <v>5</v>
       </c>
-      <c r="O137" s="721" t="n">
+      <c r="O137" s="1239" t="n">
         <v>6</v>
       </c>
-      <c r="P137" s="721" t="n">
+      <c r="P137" s="1239" t="n">
         <v>7</v>
       </c>
-      <c r="Q137" s="720" t="n">
+      <c r="Q137" s="1238" t="n">
         <v>8</v>
       </c>
-      <c r="R137" s="720" t="n">
+      <c r="R137" s="1238" t="n">
         <v>9</v>
       </c>
-      <c r="S137" s="720" t="n">
+      <c r="S137" s="1238" t="n">
         <v>10</v>
       </c>
-      <c r="T137" s="720" t="n">
+      <c r="T137" s="1238" t="n">
         <v>11</v>
       </c>
-      <c r="U137" s="720" t="n">
+      <c r="U137" s="1238" t="n">
         <v>12</v>
       </c>
-      <c r="V137" s="721" t="n">
+      <c r="V137" s="1239" t="n">
         <v>13</v>
       </c>
-      <c r="W137" s="721" t="n">
+      <c r="W137" s="1239" t="n">
         <v>14</v>
       </c>
-      <c r="X137" s="720" t="n">
+      <c r="X137" s="1238" t="n">
         <v>15</v>
       </c>
-      <c r="Y137" s="720" t="n">
+      <c r="Y137" s="1238" t="n">
         <v>16</v>
       </c>
-      <c r="Z137" s="720" t="n">
+      <c r="Z137" s="1238" t="n">
         <v>17</v>
       </c>
-      <c r="AA137" s="720" t="n">
+      <c r="AA137" s="1238" t="n">
         <v>18</v>
       </c>
-      <c r="AB137" s="720" t="n">
+      <c r="AB137" s="1238" t="n">
         <v>19</v>
       </c>
-      <c r="AC137" s="721" t="n">
+      <c r="AC137" s="1239" t="n">
         <v>20</v>
       </c>
-      <c r="AD137" s="721" t="n">
+      <c r="AD137" s="1239" t="n">
         <v>21</v>
       </c>
-      <c r="AE137" s="720" t="n">
+      <c r="AE137" s="1238" t="n">
         <v>22</v>
       </c>
-      <c r="AF137" s="720" t="n">
+      <c r="AF137" s="1238" t="n">
         <v>23</v>
       </c>
-      <c r="AG137" s="720" t="n">
+      <c r="AG137" s="1238" t="n">
         <v>24</v>
       </c>
-      <c r="AH137" s="720" t="n">
+      <c r="AH137" s="1238" t="n">
         <v>25</v>
       </c>
-      <c r="AI137" s="720" t="n">
+      <c r="AI137" s="1238" t="n">
         <v>26</v>
       </c>
-      <c r="AJ137" s="721" t="n">
+      <c r="AJ137" s="1239" t="n">
         <v>27</v>
       </c>
-      <c r="AK137" s="721" t="n">
+      <c r="AK137" s="1239" t="n">
         <v>28</v>
       </c>
-      <c r="AL137" s="720" t="n">
+      <c r="AL137" s="1238" t="n">
         <v>29</v>
       </c>
-      <c r="AM137" s="720" t="n">
+      <c r="AM137" s="1238" t="n">
         <v>30</v>
       </c>
-      <c r="AN137" s="1042" t="n"/>
+      <c r="AN137" s="1278" t="n"/>
     </row>
     <row r="138" ht="15" customHeight="1" thickBot="1">
-      <c r="A138" s="1206" t="inlineStr">
+      <c r="A138" s="1241" t="inlineStr">
         <is>
           <t>ACS</t>
         </is>
       </c>
-      <c r="B138" s="1148" t="n"/>
       <c r="I138" s="1149" t="n"/>
       <c r="J138" s="1022" t="n"/>
       <c r="K138" s="1022" t="n"/>
@@ -13728,11 +13714,10 @@
       <c r="AK138" s="1043" t="n"/>
       <c r="AL138" s="1087" t="n"/>
       <c r="AM138" s="1087" t="n"/>
-      <c r="AN138" s="1169" t="n"/>
+      <c r="AN138" s="1149" t="n"/>
     </row>
     <row r="139" ht="15" customHeight="1" thickBot="1">
-      <c r="A139" s="729" t="n"/>
-      <c r="B139" s="1148" t="n"/>
+      <c r="A139" s="1268" t="n"/>
       <c r="I139" s="1149" t="n"/>
       <c r="J139" s="1006" t="n"/>
       <c r="K139" s="1006" t="n"/>
@@ -13764,15 +13749,14 @@
       <c r="AK139" s="1043" t="n"/>
       <c r="AL139" s="1087" t="n"/>
       <c r="AM139" s="1087" t="n"/>
-      <c r="AN139" s="1169" t="n"/>
+      <c r="AN139" s="1149" t="n"/>
     </row>
     <row r="140" ht="15" customHeight="1">
-      <c r="A140" s="1211" t="inlineStr">
+      <c r="A140" s="1242" t="inlineStr">
         <is>
           <t>OCS (NZ)</t>
         </is>
       </c>
-      <c r="B140" s="1148" t="n"/>
       <c r="I140" s="1149" t="n"/>
       <c r="J140" s="1009" t="n"/>
       <c r="K140" s="1009" t="n"/>
@@ -13804,11 +13788,10 @@
       <c r="AK140" s="1015" t="n"/>
       <c r="AL140" s="1087" t="n"/>
       <c r="AM140" s="1087" t="n"/>
-      <c r="AN140" s="1169" t="n"/>
+      <c r="AN140" s="1149" t="n"/>
     </row>
     <row r="141" ht="15" customHeight="1" thickBot="1">
-      <c r="A141" s="726" t="n"/>
-      <c r="B141" s="1148" t="n"/>
+      <c r="A141" s="1272" t="n"/>
       <c r="I141" s="1149" t="n"/>
       <c r="J141" s="1009" t="n"/>
       <c r="K141" s="1009" t="n"/>
@@ -13840,11 +13823,10 @@
       <c r="AK141" s="1007" t="n"/>
       <c r="AL141" s="1087" t="n"/>
       <c r="AM141" s="1087" t="n"/>
-      <c r="AN141" s="1169" t="n"/>
+      <c r="AN141" s="1149" t="n"/>
     </row>
     <row r="142" ht="15" customHeight="1">
-      <c r="A142" s="729" t="n"/>
-      <c r="B142" s="1148" t="n"/>
+      <c r="A142" s="1268" t="n"/>
       <c r="I142" s="1149" t="n"/>
       <c r="J142" s="1022" t="n"/>
       <c r="K142" s="1022" t="n"/>
@@ -13876,15 +13858,14 @@
       <c r="AK142" s="1043" t="n"/>
       <c r="AL142" s="1087" t="n"/>
       <c r="AM142" s="1087" t="n"/>
-      <c r="AN142" s="1169" t="n"/>
+      <c r="AN142" s="1149" t="n"/>
     </row>
     <row r="143" ht="15" customHeight="1">
-      <c r="A143" s="1020" t="inlineStr">
+      <c r="A143" s="1244" t="inlineStr">
         <is>
           <t>ALC LD Wing</t>
         </is>
       </c>
-      <c r="B143" s="1148" t="n"/>
       <c r="I143" s="1149" t="n"/>
       <c r="J143" s="1022" t="n"/>
       <c r="K143" s="1022" t="n"/>
@@ -13916,15 +13897,14 @@
       <c r="AK143" s="1043" t="n"/>
       <c r="AL143" s="1087" t="n"/>
       <c r="AM143" s="1087" t="n"/>
-      <c r="AN143" s="1169" t="n"/>
+      <c r="AN143" s="1149" t="n"/>
     </row>
     <row r="144" ht="15" customHeight="1" thickBot="1">
-      <c r="A144" s="1027" t="inlineStr">
+      <c r="A144" s="1246" t="inlineStr">
         <is>
           <t>ALC ELDA Wing</t>
         </is>
       </c>
-      <c r="B144" s="1148" t="n"/>
       <c r="I144" s="1149" t="n"/>
       <c r="J144" s="1022" t="n"/>
       <c r="K144" s="1022" t="n"/>
@@ -13932,16 +13912,16 @@
       <c r="M144" s="1022" t="n"/>
       <c r="N144" s="1022" t="n"/>
       <c r="O144" s="1043" t="n"/>
-      <c r="P144" s="1028" t="inlineStr">
+      <c r="P144" s="1274" t="inlineStr">
         <is>
           <t>LEAD INTEGRATED CAP</t>
         </is>
       </c>
-      <c r="Q144" s="744" t="n"/>
-      <c r="R144" s="744" t="n"/>
-      <c r="S144" s="744" t="n"/>
-      <c r="T144" s="744" t="n"/>
-      <c r="U144" s="745" t="n"/>
+      <c r="Q144" s="1155" t="n"/>
+      <c r="R144" s="1155" t="n"/>
+      <c r="S144" s="1155" t="n"/>
+      <c r="T144" s="1155" t="n"/>
+      <c r="U144" s="1156" t="n"/>
       <c r="V144" s="1043" t="n"/>
       <c r="W144" s="1043" t="n"/>
       <c r="X144" s="1024" t="n"/>
@@ -13960,88 +13940,86 @@
       <c r="AK144" s="1043" t="n"/>
       <c r="AL144" s="1087" t="n"/>
       <c r="AM144" s="1087" t="n"/>
-      <c r="AN144" s="1169" t="n"/>
+      <c r="AN144" s="1149" t="n"/>
     </row>
     <row r="145" ht="15" customHeight="1">
-      <c r="A145" s="1030" t="inlineStr">
+      <c r="A145" s="1248" t="inlineStr">
         <is>
           <t>2 RTW</t>
         </is>
       </c>
-      <c r="B145" s="1148" t="n"/>
       <c r="I145" s="1149" t="n"/>
-      <c r="J145" s="1082" t="inlineStr">
+      <c r="J145" s="1275" t="inlineStr">
         <is>
           <t>RF JNCO 27/06</t>
         </is>
       </c>
-      <c r="K145" s="732" t="n"/>
-      <c r="L145" s="732" t="n"/>
-      <c r="M145" s="732" t="n"/>
-      <c r="N145" s="732" t="n"/>
-      <c r="O145" s="732" t="n"/>
-      <c r="P145" s="765" t="n"/>
-      <c r="Q145" s="1067" t="inlineStr">
+      <c r="K145" s="1270" t="n"/>
+      <c r="L145" s="1270" t="n"/>
+      <c r="M145" s="1270" t="n"/>
+      <c r="N145" s="1270" t="n"/>
+      <c r="O145" s="1270" t="n"/>
+      <c r="P145" s="1271" t="n"/>
+      <c r="Q145" s="1275" t="inlineStr">
         <is>
           <t>EX YOUNG LION</t>
         </is>
       </c>
-      <c r="R145" s="732" t="n"/>
-      <c r="S145" s="732" t="n"/>
-      <c r="T145" s="732" t="n"/>
-      <c r="U145" s="732" t="n"/>
-      <c r="V145" s="732" t="n"/>
-      <c r="W145" s="732" t="n"/>
-      <c r="X145" s="732" t="n"/>
-      <c r="Y145" s="732" t="n"/>
-      <c r="Z145" s="732" t="n"/>
-      <c r="AA145" s="732" t="n"/>
-      <c r="AB145" s="765" t="n"/>
-      <c r="AC145" s="1067" t="inlineStr">
+      <c r="R145" s="1270" t="n"/>
+      <c r="S145" s="1270" t="n"/>
+      <c r="T145" s="1270" t="n"/>
+      <c r="U145" s="1270" t="n"/>
+      <c r="V145" s="1270" t="n"/>
+      <c r="W145" s="1270" t="n"/>
+      <c r="X145" s="1270" t="n"/>
+      <c r="Y145" s="1270" t="n"/>
+      <c r="Z145" s="1270" t="n"/>
+      <c r="AA145" s="1270" t="n"/>
+      <c r="AB145" s="1271" t="n"/>
+      <c r="AC145" s="1275" t="inlineStr">
         <is>
           <t>RF JNCO 27/06</t>
         </is>
       </c>
-      <c r="AD145" s="732" t="n"/>
-      <c r="AE145" s="732" t="n"/>
-      <c r="AF145" s="732" t="n"/>
-      <c r="AG145" s="732" t="n"/>
-      <c r="AH145" s="732" t="n"/>
-      <c r="AI145" s="765" t="n"/>
+      <c r="AD145" s="1270" t="n"/>
+      <c r="AE145" s="1270" t="n"/>
+      <c r="AF145" s="1270" t="n"/>
+      <c r="AG145" s="1270" t="n"/>
+      <c r="AH145" s="1270" t="n"/>
+      <c r="AI145" s="1271" t="n"/>
       <c r="AJ145" s="1012" t="n"/>
       <c r="AK145" s="1043" t="n"/>
       <c r="AL145" s="1087" t="n"/>
       <c r="AM145" s="1087" t="n"/>
-      <c r="AN145" s="1169" t="n"/>
+      <c r="AN145" s="1149" t="n"/>
     </row>
     <row r="146" ht="15" customHeight="1" thickBot="1">
-      <c r="A146" s="1033" t="inlineStr">
+      <c r="A146" s="1250" t="inlineStr">
         <is>
           <t>3 RTW</t>
         </is>
       </c>
-      <c r="B146" s="1148" t="n"/>
       <c r="I146" s="1149" t="n"/>
-      <c r="J146" s="1101" t="inlineStr">
+      <c r="J146" s="1276" t="inlineStr">
         <is>
           <t>EX YOUNG LION</t>
         </is>
       </c>
-      <c r="K146" s="732" t="n"/>
-      <c r="L146" s="732" t="n"/>
-      <c r="M146" s="732" t="n"/>
-      <c r="N146" s="765" t="n"/>
-      <c r="O146" s="1069" t="inlineStr">
+      <c r="K146" s="1270" t="n"/>
+      <c r="L146" s="1270" t="n"/>
+      <c r="M146" s="1270" t="n"/>
+      <c r="N146" s="1271" t="n"/>
+      <c r="O146" s="1276" t="inlineStr">
         <is>
           <t>RF JNCO 27/05</t>
         </is>
       </c>
-      <c r="P146" s="732" t="n"/>
-      <c r="Q146" s="732" t="n"/>
-      <c r="R146" s="732" t="n"/>
-      <c r="S146" s="732" t="n"/>
-      <c r="T146" s="732" t="n"/>
-      <c r="U146" s="765" t="n"/>
+      <c r="P146" s="1270" t="n"/>
+      <c r="Q146" s="1270" t="n"/>
+      <c r="R146" s="1270" t="n"/>
+      <c r="S146" s="1270" t="n"/>
+      <c r="T146" s="1270" t="n"/>
+      <c r="U146" s="1271" t="n"/>
       <c r="V146" s="1043" t="n"/>
       <c r="W146" s="1043" t="n"/>
       <c r="X146" s="1024" t="n"/>
@@ -14060,63 +14038,62 @@
       <c r="AK146" s="1043" t="n"/>
       <c r="AL146" s="1087" t="n"/>
       <c r="AM146" s="1087" t="n"/>
-      <c r="AN146" s="1169" t="n"/>
+      <c r="AN146" s="1149" t="n"/>
     </row>
     <row r="147" ht="15" customHeight="1">
-      <c r="A147" s="1037" t="inlineStr">
+      <c r="A147" s="1252" t="inlineStr">
         <is>
           <t>SNCO Wing</t>
         </is>
       </c>
-      <c r="B147" s="1148" t="n"/>
       <c r="I147" s="1149" t="n"/>
-      <c r="J147" s="1083" t="inlineStr">
+      <c r="J147" s="1279" t="inlineStr">
         <is>
           <t>EX KALAMATI</t>
         </is>
       </c>
-      <c r="K147" s="732" t="n"/>
-      <c r="L147" s="732" t="n"/>
-      <c r="M147" s="732" t="n"/>
-      <c r="N147" s="732" t="n"/>
-      <c r="O147" s="732" t="n"/>
-      <c r="P147" s="732" t="n"/>
-      <c r="Q147" s="732" t="n"/>
-      <c r="R147" s="732" t="n"/>
-      <c r="S147" s="732" t="n"/>
-      <c r="T147" s="732" t="n"/>
-      <c r="U147" s="732" t="n"/>
-      <c r="V147" s="732" t="n"/>
-      <c r="W147" s="732" t="n"/>
-      <c r="X147" s="732" t="n"/>
-      <c r="Y147" s="732" t="n"/>
-      <c r="Z147" s="732" t="n"/>
-      <c r="AA147" s="732" t="n"/>
-      <c r="AB147" s="765" t="n"/>
-      <c r="AC147" s="1071" t="inlineStr">
+      <c r="K147" s="1270" t="n"/>
+      <c r="L147" s="1270" t="n"/>
+      <c r="M147" s="1270" t="n"/>
+      <c r="N147" s="1270" t="n"/>
+      <c r="O147" s="1270" t="n"/>
+      <c r="P147" s="1270" t="n"/>
+      <c r="Q147" s="1270" t="n"/>
+      <c r="R147" s="1270" t="n"/>
+      <c r="S147" s="1270" t="n"/>
+      <c r="T147" s="1270" t="n"/>
+      <c r="U147" s="1270" t="n"/>
+      <c r="V147" s="1270" t="n"/>
+      <c r="W147" s="1270" t="n"/>
+      <c r="X147" s="1270" t="n"/>
+      <c r="Y147" s="1270" t="n"/>
+      <c r="Z147" s="1270" t="n"/>
+      <c r="AA147" s="1270" t="n"/>
+      <c r="AB147" s="1271" t="n"/>
+      <c r="AC147" s="1279" t="inlineStr">
         <is>
           <t>RF SNCO 27/03</t>
         </is>
       </c>
-      <c r="AD147" s="732" t="n"/>
-      <c r="AE147" s="732" t="n"/>
-      <c r="AF147" s="732" t="n"/>
-      <c r="AG147" s="732" t="n"/>
-      <c r="AH147" s="732" t="n"/>
-      <c r="AI147" s="765" t="n"/>
+      <c r="AD147" s="1270" t="n"/>
+      <c r="AE147" s="1270" t="n"/>
+      <c r="AF147" s="1270" t="n"/>
+      <c r="AG147" s="1270" t="n"/>
+      <c r="AH147" s="1270" t="n"/>
+      <c r="AI147" s="1271" t="n"/>
       <c r="AJ147" s="1007" t="n"/>
       <c r="AK147" s="1007" t="n"/>
       <c r="AL147" s="1087" t="n"/>
       <c r="AM147" s="1087" t="n"/>
-      <c r="AN147" s="1169" t="n"/>
+      <c r="AN147" s="1149" t="n"/>
     </row>
     <row r="148" ht="15" customHeight="1">
-      <c r="A148" s="1039" t="inlineStr">
+      <c r="A148" s="1253" t="inlineStr">
         <is>
           <t>WO Wing</t>
         </is>
       </c>
-      <c r="B148" s="1154" t="n"/>
+      <c r="B148" s="1155" t="n"/>
       <c r="C148" s="1155" t="n"/>
       <c r="D148" s="1155" t="n"/>
       <c r="E148" s="1155" t="n"/>
@@ -14154,7 +14131,7 @@
       <c r="AK148" s="1043" t="n"/>
       <c r="AL148" s="1087" t="n"/>
       <c r="AM148" s="1087" t="n"/>
-      <c r="AN148" s="1171" t="n"/>
+      <c r="AN148" s="1156" t="n"/>
     </row>
     <row r="149" ht="6" customHeight="1">
       <c r="A149" s="1225" t="n"/>
@@ -14199,137 +14176,132 @@
       <c r="AN149" s="1225" t="n"/>
     </row>
     <row r="150" ht="14" customHeight="1" thickBot="1">
-      <c r="A150" s="1228" t="inlineStr">
+      <c r="A150" s="1236" t="inlineStr">
         <is>
           <t>December</t>
         </is>
       </c>
-      <c r="B150" s="1002" t="n"/>
-      <c r="C150" s="1146" t="n"/>
-      <c r="D150" s="1147" t="n"/>
-      <c r="E150" s="720" t="n">
+      <c r="B150" s="1266" t="n"/>
+      <c r="D150" s="1149" t="n"/>
+      <c r="E150" s="1238" t="n">
         <v>1</v>
       </c>
-      <c r="F150" s="720" t="n">
+      <c r="F150" s="1238" t="n">
         <v>2</v>
       </c>
-      <c r="G150" s="720" t="n">
+      <c r="G150" s="1238" t="n">
         <v>3</v>
       </c>
-      <c r="H150" s="721" t="n">
+      <c r="H150" s="1239" t="n">
         <v>4</v>
       </c>
-      <c r="I150" s="721" t="n">
+      <c r="I150" s="1239" t="n">
         <v>5</v>
       </c>
-      <c r="J150" s="720" t="n">
+      <c r="J150" s="1238" t="n">
         <v>6</v>
       </c>
-      <c r="K150" s="720" t="n">
+      <c r="K150" s="1238" t="n">
         <v>7</v>
       </c>
-      <c r="L150" s="720" t="n">
+      <c r="L150" s="1238" t="n">
         <v>8</v>
       </c>
-      <c r="M150" s="720" t="n">
+      <c r="M150" s="1238" t="n">
         <v>9</v>
       </c>
-      <c r="N150" s="720" t="n">
+      <c r="N150" s="1238" t="n">
         <v>10</v>
       </c>
-      <c r="O150" s="721" t="n">
+      <c r="O150" s="1239" t="n">
         <v>11</v>
       </c>
-      <c r="P150" s="721" t="n">
+      <c r="P150" s="1239" t="n">
         <v>12</v>
       </c>
-      <c r="Q150" s="720" t="n">
+      <c r="Q150" s="1238" t="n">
         <v>13</v>
       </c>
-      <c r="R150" s="720" t="n">
+      <c r="R150" s="1238" t="n">
         <v>14</v>
       </c>
-      <c r="S150" s="720" t="n">
+      <c r="S150" s="1238" t="n">
         <v>15</v>
       </c>
-      <c r="T150" s="720" t="n">
+      <c r="T150" s="1238" t="n">
         <v>16</v>
       </c>
-      <c r="U150" s="720" t="n">
+      <c r="U150" s="1238" t="n">
         <v>17</v>
       </c>
-      <c r="V150" s="721" t="n">
+      <c r="V150" s="1239" t="n">
         <v>18</v>
       </c>
-      <c r="W150" s="721" t="n">
+      <c r="W150" s="1239" t="n">
         <v>19</v>
       </c>
-      <c r="X150" s="720" t="n">
+      <c r="X150" s="1238" t="n">
         <v>20</v>
       </c>
-      <c r="Y150" s="720" t="n">
+      <c r="Y150" s="1238" t="n">
         <v>21</v>
       </c>
-      <c r="Z150" s="720" t="n">
+      <c r="Z150" s="1238" t="n">
         <v>22</v>
       </c>
-      <c r="AA150" s="720" t="n">
+      <c r="AA150" s="1238" t="n">
         <v>23</v>
       </c>
-      <c r="AB150" s="720" t="n">
+      <c r="AB150" s="1238" t="n">
         <v>24</v>
       </c>
-      <c r="AC150" s="721" t="n">
+      <c r="AC150" s="1239" t="n">
         <v>25</v>
       </c>
-      <c r="AD150" s="721" t="n">
+      <c r="AD150" s="1239" t="n">
         <v>26</v>
       </c>
-      <c r="AE150" s="720" t="n">
+      <c r="AE150" s="1238" t="n">
         <v>27</v>
       </c>
-      <c r="AF150" s="720" t="n">
+      <c r="AF150" s="1238" t="n">
         <v>28</v>
       </c>
-      <c r="AG150" s="720" t="n">
+      <c r="AG150" s="1238" t="n">
         <v>29</v>
       </c>
-      <c r="AH150" s="720" t="n">
+      <c r="AH150" s="1238" t="n">
         <v>30</v>
       </c>
-      <c r="AI150" s="720" t="n">
+      <c r="AI150" s="1238" t="n">
         <v>31</v>
       </c>
-      <c r="AJ150" s="1002" t="n"/>
-      <c r="AK150" s="1146" t="n"/>
-      <c r="AL150" s="1146" t="n"/>
-      <c r="AM150" s="1146" t="n"/>
-      <c r="AN150" s="1147" t="n"/>
+      <c r="AJ150" s="1266" t="n"/>
+      <c r="AN150" s="1149" t="n"/>
     </row>
     <row r="151" ht="15" customHeight="1" thickBot="1">
-      <c r="A151" s="1206" t="inlineStr">
+      <c r="A151" s="1241" t="inlineStr">
         <is>
           <t>ACS</t>
         </is>
       </c>
-      <c r="B151" s="1148" t="n"/>
       <c r="D151" s="1149" t="n"/>
       <c r="E151" s="1024" t="n"/>
       <c r="F151" s="1024" t="n"/>
       <c r="G151" s="1024" t="n"/>
       <c r="H151" s="1012" t="n"/>
       <c r="I151" s="1012" t="n"/>
-      <c r="J151" s="1132" t="inlineStr">
+      <c r="J151" s="1281" t="inlineStr">
         <is>
           <t>Unit
 Closedown
 HOTO/Induction</t>
         </is>
       </c>
-      <c r="K151" s="840" t="n"/>
-      <c r="L151" s="840" t="n"/>
-      <c r="M151" s="840" t="n"/>
-      <c r="N151" s="841" t="n"/>
+      <c r="K151" s="844" t="n"/>
+      <c r="L151" s="844" t="n"/>
+      <c r="M151" s="844" t="n"/>
+      <c r="N151" s="1282" t="n"/>
       <c r="O151" s="1012" t="n"/>
       <c r="P151" s="1012" t="n"/>
       <c r="Q151" s="1008" t="n"/>
@@ -14337,41 +14309,39 @@
       <c r="S151" s="1133" t="n"/>
       <c r="T151" s="1134" t="n"/>
       <c r="U151" s="1134" t="n"/>
-      <c r="V151" s="1177" t="inlineStr">
+      <c r="V151" s="1261" t="inlineStr">
         <is>
           <t>SCHOOL HOLIDAYS (NLT 20 DEC)</t>
         </is>
       </c>
-      <c r="W151" s="1136" t="n"/>
-      <c r="X151" s="1136" t="n"/>
-      <c r="Y151" s="1136" t="n"/>
-      <c r="Z151" s="1136" t="n"/>
-      <c r="AA151" s="1136" t="n"/>
-      <c r="AB151" s="1136" t="n"/>
-      <c r="AC151" s="1136" t="n"/>
-      <c r="AD151" s="1136" t="n"/>
-      <c r="AE151" s="1136" t="n"/>
-      <c r="AF151" s="1136" t="n"/>
-      <c r="AG151" s="1137" t="n"/>
+      <c r="W151" s="1262" t="n"/>
+      <c r="X151" s="1262" t="n"/>
+      <c r="Y151" s="1262" t="n"/>
+      <c r="Z151" s="1262" t="n"/>
+      <c r="AA151" s="1262" t="n"/>
+      <c r="AB151" s="1262" t="n"/>
+      <c r="AC151" s="1262" t="n"/>
+      <c r="AD151" s="1262" t="n"/>
+      <c r="AE151" s="1262" t="n"/>
+      <c r="AF151" s="1262" t="n"/>
+      <c r="AG151" s="1262" t="n"/>
       <c r="AH151" s="1099" t="n"/>
       <c r="AI151" s="1099" t="n"/>
-      <c r="AJ151" s="1148" t="n"/>
       <c r="AN151" s="1149" t="n"/>
     </row>
     <row r="152" ht="15" customHeight="1">
-      <c r="A152" s="729" t="n"/>
-      <c r="B152" s="1148" t="n"/>
+      <c r="A152" s="1268" t="n"/>
       <c r="D152" s="1149" t="n"/>
       <c r="E152" s="1024" t="n"/>
       <c r="F152" s="1024" t="n"/>
       <c r="G152" s="1024" t="n"/>
       <c r="H152" s="1012" t="n"/>
       <c r="I152" s="1012" t="n"/>
-      <c r="J152" s="843" t="n"/>
+      <c r="J152" s="844" t="n"/>
       <c r="K152" s="844" t="n"/>
       <c r="L152" s="844" t="n"/>
       <c r="M152" s="844" t="n"/>
-      <c r="N152" s="845" t="n"/>
+      <c r="N152" s="1282" t="n"/>
       <c r="O152" s="1012" t="n"/>
       <c r="P152" s="1012" t="n"/>
       <c r="Q152" s="1008" t="n"/>
@@ -14393,27 +14363,25 @@
       <c r="AG152" s="1134" t="n"/>
       <c r="AH152" s="1099" t="n"/>
       <c r="AI152" s="1099" t="n"/>
-      <c r="AJ152" s="1148" t="n"/>
       <c r="AN152" s="1149" t="n"/>
     </row>
     <row r="153" ht="15" customHeight="1">
-      <c r="A153" s="1211" t="inlineStr">
+      <c r="A153" s="1242" t="inlineStr">
         <is>
           <t>OCS (NZ)</t>
         </is>
       </c>
-      <c r="B153" s="1148" t="n"/>
       <c r="D153" s="1149" t="n"/>
       <c r="E153" s="1009" t="n"/>
       <c r="F153" s="1024" t="n"/>
       <c r="G153" s="1024" t="n"/>
       <c r="H153" s="1012" t="n"/>
       <c r="I153" s="1012" t="n"/>
-      <c r="J153" s="843" t="n"/>
+      <c r="J153" s="844" t="n"/>
       <c r="K153" s="844" t="n"/>
       <c r="L153" s="844" t="n"/>
       <c r="M153" s="844" t="n"/>
-      <c r="N153" s="845" t="n"/>
+      <c r="N153" s="1282" t="n"/>
       <c r="O153" s="1012" t="n"/>
       <c r="P153" s="1012" t="n"/>
       <c r="Q153" s="1008" t="n"/>
@@ -14435,23 +14403,21 @@
       <c r="AG153" s="1134" t="n"/>
       <c r="AH153" s="1099" t="n"/>
       <c r="AI153" s="1099" t="n"/>
-      <c r="AJ153" s="1148" t="n"/>
       <c r="AN153" s="1149" t="n"/>
     </row>
     <row r="154" ht="15" customHeight="1">
-      <c r="A154" s="726" t="n"/>
-      <c r="B154" s="1148" t="n"/>
+      <c r="A154" s="1272" t="n"/>
       <c r="D154" s="1149" t="n"/>
       <c r="E154" s="1024" t="n"/>
       <c r="F154" s="1024" t="n"/>
       <c r="G154" s="1024" t="n"/>
       <c r="H154" s="1012" t="n"/>
       <c r="I154" s="1012" t="n"/>
-      <c r="J154" s="843" t="n"/>
+      <c r="J154" s="844" t="n"/>
       <c r="K154" s="844" t="n"/>
       <c r="L154" s="844" t="n"/>
       <c r="M154" s="844" t="n"/>
-      <c r="N154" s="845" t="n"/>
+      <c r="N154" s="1282" t="n"/>
       <c r="O154" s="1012" t="n"/>
       <c r="P154" s="1012" t="n"/>
       <c r="Q154" s="1008" t="n"/>
@@ -14473,23 +14439,21 @@
       <c r="AG154" s="1134" t="n"/>
       <c r="AH154" s="1099" t="n"/>
       <c r="AI154" s="1099" t="n"/>
-      <c r="AJ154" s="1148" t="n"/>
       <c r="AN154" s="1149" t="n"/>
     </row>
     <row r="155" ht="15" customHeight="1">
-      <c r="A155" s="729" t="n"/>
-      <c r="B155" s="1148" t="n"/>
+      <c r="A155" s="1268" t="n"/>
       <c r="D155" s="1149" t="n"/>
       <c r="E155" s="1024" t="n"/>
       <c r="F155" s="1024" t="n"/>
       <c r="G155" s="1024" t="n"/>
       <c r="H155" s="1012" t="n"/>
       <c r="I155" s="1012" t="n"/>
-      <c r="J155" s="843" t="n"/>
+      <c r="J155" s="844" t="n"/>
       <c r="K155" s="844" t="n"/>
       <c r="L155" s="844" t="n"/>
       <c r="M155" s="844" t="n"/>
-      <c r="N155" s="845" t="n"/>
+      <c r="N155" s="1282" t="n"/>
       <c r="O155" s="1012" t="n"/>
       <c r="P155" s="1012" t="n"/>
       <c r="Q155" s="1008" t="n"/>
@@ -14511,27 +14475,25 @@
       <c r="AG155" s="1134" t="n"/>
       <c r="AH155" s="1099" t="n"/>
       <c r="AI155" s="1099" t="n"/>
-      <c r="AJ155" s="1148" t="n"/>
       <c r="AN155" s="1149" t="n"/>
     </row>
     <row r="156" ht="15" customHeight="1">
-      <c r="A156" s="1020" t="inlineStr">
+      <c r="A156" s="1244" t="inlineStr">
         <is>
           <t>ALC LD Wing</t>
         </is>
       </c>
-      <c r="B156" s="1148" t="n"/>
       <c r="D156" s="1149" t="n"/>
       <c r="E156" s="1024" t="n"/>
       <c r="F156" s="1024" t="n"/>
       <c r="G156" s="1024" t="n"/>
       <c r="H156" s="1012" t="n"/>
       <c r="I156" s="1012" t="n"/>
-      <c r="J156" s="843" t="n"/>
+      <c r="J156" s="844" t="n"/>
       <c r="K156" s="844" t="n"/>
       <c r="L156" s="844" t="n"/>
       <c r="M156" s="844" t="n"/>
-      <c r="N156" s="845" t="n"/>
+      <c r="N156" s="1282" t="n"/>
       <c r="O156" s="1012" t="n"/>
       <c r="P156" s="1012" t="n"/>
       <c r="Q156" s="1008" t="n"/>
@@ -14553,27 +14515,25 @@
       <c r="AG156" s="1134" t="n"/>
       <c r="AH156" s="1099" t="n"/>
       <c r="AI156" s="1099" t="n"/>
-      <c r="AJ156" s="1148" t="n"/>
       <c r="AN156" s="1149" t="n"/>
     </row>
     <row r="157" ht="15" customHeight="1">
-      <c r="A157" s="1027" t="inlineStr">
+      <c r="A157" s="1246" t="inlineStr">
         <is>
           <t>ALC ELDA Wing</t>
         </is>
       </c>
-      <c r="B157" s="1148" t="n"/>
       <c r="D157" s="1149" t="n"/>
       <c r="E157" s="1024" t="n"/>
       <c r="F157" s="1024" t="n"/>
       <c r="G157" s="1024" t="n"/>
       <c r="H157" s="1012" t="n"/>
       <c r="I157" s="1012" t="n"/>
-      <c r="J157" s="843" t="n"/>
+      <c r="J157" s="844" t="n"/>
       <c r="K157" s="844" t="n"/>
       <c r="L157" s="844" t="n"/>
       <c r="M157" s="844" t="n"/>
-      <c r="N157" s="845" t="n"/>
+      <c r="N157" s="1282" t="n"/>
       <c r="O157" s="1012" t="n"/>
       <c r="P157" s="1012" t="n"/>
       <c r="Q157" s="1008" t="n"/>
@@ -14595,27 +14555,25 @@
       <c r="AG157" s="1134" t="n"/>
       <c r="AH157" s="1099" t="n"/>
       <c r="AI157" s="1099" t="n"/>
-      <c r="AJ157" s="1148" t="n"/>
       <c r="AN157" s="1149" t="n"/>
     </row>
     <row r="158" ht="15" customHeight="1">
-      <c r="A158" s="1030" t="inlineStr">
+      <c r="A158" s="1248" t="inlineStr">
         <is>
           <t>2 RTW</t>
         </is>
       </c>
-      <c r="B158" s="1148" t="n"/>
       <c r="D158" s="1149" t="n"/>
       <c r="E158" s="1024" t="n"/>
       <c r="F158" s="1024" t="n"/>
       <c r="G158" s="1024" t="n"/>
       <c r="H158" s="1012" t="n"/>
       <c r="I158" s="1012" t="n"/>
-      <c r="J158" s="843" t="n"/>
+      <c r="J158" s="844" t="n"/>
       <c r="K158" s="844" t="n"/>
       <c r="L158" s="844" t="n"/>
       <c r="M158" s="844" t="n"/>
-      <c r="N158" s="845" t="n"/>
+      <c r="N158" s="1282" t="n"/>
       <c r="O158" s="1012" t="n"/>
       <c r="P158" s="1012" t="n"/>
       <c r="Q158" s="1008" t="n"/>
@@ -14637,27 +14595,25 @@
       <c r="AG158" s="1134" t="n"/>
       <c r="AH158" s="1099" t="n"/>
       <c r="AI158" s="1099" t="n"/>
-      <c r="AJ158" s="1148" t="n"/>
       <c r="AN158" s="1149" t="n"/>
     </row>
     <row r="159" ht="15" customHeight="1">
-      <c r="A159" s="1033" t="inlineStr">
+      <c r="A159" s="1250" t="inlineStr">
         <is>
           <t>3 RTW</t>
         </is>
       </c>
-      <c r="B159" s="1148" t="n"/>
       <c r="D159" s="1149" t="n"/>
       <c r="E159" s="1024" t="n"/>
       <c r="F159" s="1024" t="n"/>
       <c r="G159" s="1024" t="n"/>
       <c r="H159" s="1012" t="n"/>
       <c r="I159" s="1012" t="n"/>
-      <c r="J159" s="843" t="n"/>
+      <c r="J159" s="844" t="n"/>
       <c r="K159" s="844" t="n"/>
       <c r="L159" s="844" t="n"/>
       <c r="M159" s="844" t="n"/>
-      <c r="N159" s="845" t="n"/>
+      <c r="N159" s="1282" t="n"/>
       <c r="O159" s="1012" t="n"/>
       <c r="P159" s="1012" t="n"/>
       <c r="Q159" s="1008" t="n"/>
@@ -14679,27 +14635,25 @@
       <c r="AG159" s="1134" t="n"/>
       <c r="AH159" s="1099" t="n"/>
       <c r="AI159" s="1099" t="n"/>
-      <c r="AJ159" s="1148" t="n"/>
       <c r="AN159" s="1149" t="n"/>
     </row>
     <row r="160" ht="15" customHeight="1">
-      <c r="A160" s="1037" t="inlineStr">
+      <c r="A160" s="1252" t="inlineStr">
         <is>
           <t>SNCO Wing</t>
         </is>
       </c>
-      <c r="B160" s="1148" t="n"/>
       <c r="D160" s="1149" t="n"/>
       <c r="E160" s="1006" t="n"/>
       <c r="F160" s="1006" t="n"/>
       <c r="G160" s="1006" t="n"/>
       <c r="H160" s="1012" t="n"/>
       <c r="I160" s="1012" t="n"/>
-      <c r="J160" s="846" t="n"/>
-      <c r="K160" s="847" t="n"/>
-      <c r="L160" s="847" t="n"/>
-      <c r="M160" s="847" t="n"/>
-      <c r="N160" s="848" t="n"/>
+      <c r="J160" s="1270" t="n"/>
+      <c r="K160" s="1270" t="n"/>
+      <c r="L160" s="1270" t="n"/>
+      <c r="M160" s="1270" t="n"/>
+      <c r="N160" s="1271" t="n"/>
       <c r="O160" s="1012" t="n"/>
       <c r="P160" s="1012" t="n"/>
       <c r="Q160" s="1008" t="n"/>
@@ -14721,16 +14675,15 @@
       <c r="AG160" s="1134" t="n"/>
       <c r="AH160" s="1099" t="n"/>
       <c r="AI160" s="1099" t="n"/>
-      <c r="AJ160" s="1148" t="n"/>
       <c r="AN160" s="1149" t="n"/>
     </row>
     <row r="161" ht="15" customHeight="1">
-      <c r="A161" s="1039" t="inlineStr">
+      <c r="A161" s="1253" t="inlineStr">
         <is>
           <t>WO Wing</t>
         </is>
       </c>
-      <c r="B161" s="1154" t="n"/>
+      <c r="B161" s="1155" t="n"/>
       <c r="C161" s="1155" t="n"/>
       <c r="D161" s="1156" t="n"/>
       <c r="E161" s="1024" t="n"/>
@@ -14764,7 +14717,7 @@
       <c r="AG161" s="1134" t="n"/>
       <c r="AH161" s="1099" t="n"/>
       <c r="AI161" s="1099" t="n"/>
-      <c r="AJ161" s="1154" t="n"/>
+      <c r="AJ161" s="1155" t="n"/>
       <c r="AK161" s="1155" t="n"/>
       <c r="AL161" s="1155" t="n"/>
       <c r="AM161" s="1155" t="n"/>
@@ -14813,201 +14766,240 @@
       <c r="AN162" s="1225" t="n"/>
     </row>
     <row r="163" ht="13" customHeight="1">
-      <c r="A163" s="337" t="n"/>
-      <c r="B163" s="1138" t="inlineStr">
+      <c r="A163" s="1263" t="n"/>
+      <c r="B163" s="1234" t="inlineStr">
         <is>
           <t>Su</t>
         </is>
       </c>
-      <c r="C163" s="1139" t="inlineStr">
+      <c r="C163" s="1235" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="D163" s="1139" t="inlineStr">
+      <c r="D163" s="1235" t="inlineStr">
         <is>
           <t>Tu</t>
         </is>
       </c>
-      <c r="E163" s="1139" t="inlineStr">
+      <c r="E163" s="1235" t="inlineStr">
         <is>
           <t>We</t>
         </is>
       </c>
-      <c r="F163" s="1139" t="inlineStr">
+      <c r="F163" s="1235" t="inlineStr">
         <is>
           <t>Th</t>
         </is>
       </c>
-      <c r="G163" s="1139" t="inlineStr">
+      <c r="G163" s="1235" t="inlineStr">
         <is>
           <t>Fr</t>
         </is>
       </c>
-      <c r="H163" s="1138" t="inlineStr">
+      <c r="H163" s="1234" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="I163" s="1138" t="inlineStr">
+      <c r="I163" s="1234" t="inlineStr">
         <is>
           <t>Su</t>
         </is>
       </c>
-      <c r="J163" s="1139" t="inlineStr">
+      <c r="J163" s="1235" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="K163" s="1139" t="inlineStr">
+      <c r="K163" s="1235" t="inlineStr">
         <is>
           <t>Tu</t>
         </is>
       </c>
-      <c r="L163" s="1139" t="inlineStr">
+      <c r="L163" s="1235" t="inlineStr">
         <is>
           <t>We</t>
         </is>
       </c>
-      <c r="M163" s="1139" t="inlineStr">
+      <c r="M163" s="1235" t="inlineStr">
         <is>
           <t>Th</t>
         </is>
       </c>
-      <c r="N163" s="1139" t="inlineStr">
+      <c r="N163" s="1235" t="inlineStr">
         <is>
           <t>Fr</t>
         </is>
       </c>
-      <c r="O163" s="1138" t="inlineStr">
+      <c r="O163" s="1234" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="P163" s="1138" t="inlineStr">
+      <c r="P163" s="1234" t="inlineStr">
         <is>
           <t>Su</t>
         </is>
       </c>
-      <c r="Q163" s="1139" t="inlineStr">
+      <c r="Q163" s="1235" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="R163" s="1139" t="inlineStr">
+      <c r="R163" s="1235" t="inlineStr">
         <is>
           <t>Tu</t>
         </is>
       </c>
-      <c r="S163" s="1139" t="inlineStr">
+      <c r="S163" s="1235" t="inlineStr">
         <is>
           <t>We</t>
         </is>
       </c>
-      <c r="T163" s="1139" t="inlineStr">
+      <c r="T163" s="1235" t="inlineStr">
         <is>
           <t>Th</t>
         </is>
       </c>
-      <c r="U163" s="1139" t="inlineStr">
+      <c r="U163" s="1235" t="inlineStr">
         <is>
           <t>Fr</t>
         </is>
       </c>
-      <c r="V163" s="1138" t="inlineStr">
+      <c r="V163" s="1234" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="W163" s="1138" t="inlineStr">
+      <c r="W163" s="1234" t="inlineStr">
         <is>
           <t>Su</t>
         </is>
       </c>
-      <c r="X163" s="1139" t="inlineStr">
+      <c r="X163" s="1235" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="Y163" s="1139" t="inlineStr">
+      <c r="Y163" s="1235" t="inlineStr">
         <is>
           <t>Tu</t>
         </is>
       </c>
-      <c r="Z163" s="1139" t="inlineStr">
+      <c r="Z163" s="1235" t="inlineStr">
         <is>
           <t>We</t>
         </is>
       </c>
-      <c r="AA163" s="1139" t="inlineStr">
+      <c r="AA163" s="1235" t="inlineStr">
         <is>
           <t>Th</t>
         </is>
       </c>
-      <c r="AB163" s="1139" t="inlineStr">
+      <c r="AB163" s="1235" t="inlineStr">
         <is>
           <t>Fr</t>
         </is>
       </c>
-      <c r="AC163" s="1138" t="inlineStr">
+      <c r="AC163" s="1234" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="AD163" s="1138" t="inlineStr">
+      <c r="AD163" s="1234" t="inlineStr">
         <is>
           <t>Su</t>
         </is>
       </c>
-      <c r="AE163" s="1139" t="inlineStr">
+      <c r="AE163" s="1235" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="AF163" s="1139" t="inlineStr">
+      <c r="AF163" s="1235" t="inlineStr">
         <is>
           <t>Tu</t>
         </is>
       </c>
-      <c r="AG163" s="1139" t="inlineStr">
+      <c r="AG163" s="1235" t="inlineStr">
         <is>
           <t>We</t>
         </is>
       </c>
-      <c r="AH163" s="1139" t="inlineStr">
+      <c r="AH163" s="1235" t="inlineStr">
         <is>
           <t>Th</t>
         </is>
       </c>
-      <c r="AI163" s="1139" t="inlineStr">
+      <c r="AI163" s="1235" t="inlineStr">
         <is>
           <t>Fr</t>
         </is>
       </c>
-      <c r="AJ163" s="1140" t="inlineStr">
+      <c r="AJ163" s="1234" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="AK163" s="1141" t="inlineStr">
+      <c r="AK163" s="1234" t="inlineStr">
         <is>
           <t>Su</t>
         </is>
       </c>
-      <c r="AL163" s="1142" t="inlineStr">
+      <c r="AL163" s="1235" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="AM163" s="1143" t="n"/>
-      <c r="AN163" s="1143" t="n"/>
+      <c r="AM163" s="1235" t="n"/>
+      <c r="AN163" s="1235" t="n"/>
     </row>
     <row r="164" ht="14" customHeight="1">
-      <c r="A164" s="1144" t="inlineStr">
+      <c r="A164" s="1264" t="inlineStr">
         <is>
           <t>ACS ACTIVITY CALENDAR 2027</t>
         </is>
       </c>
+      <c r="B164" s="1225" t="n"/>
+      <c r="C164" s="1225" t="n"/>
+      <c r="D164" s="1225" t="n"/>
+      <c r="E164" s="1225" t="n"/>
+      <c r="F164" s="1225" t="n"/>
+      <c r="G164" s="1225" t="n"/>
+      <c r="H164" s="1225" t="n"/>
+      <c r="I164" s="1225" t="n"/>
+      <c r="J164" s="1225" t="n"/>
+      <c r="K164" s="1225" t="n"/>
+      <c r="L164" s="1225" t="n"/>
+      <c r="M164" s="1225" t="n"/>
+      <c r="N164" s="1225" t="n"/>
+      <c r="O164" s="1225" t="n"/>
+      <c r="P164" s="1225" t="n"/>
+      <c r="Q164" s="1225" t="n"/>
+      <c r="R164" s="1225" t="n"/>
+      <c r="S164" s="1225" t="n"/>
+      <c r="T164" s="1225" t="n"/>
+      <c r="U164" s="1225" t="n"/>
+      <c r="V164" s="1225" t="n"/>
+      <c r="W164" s="1225" t="n"/>
+      <c r="X164" s="1225" t="n"/>
+      <c r="Y164" s="1225" t="n"/>
+      <c r="Z164" s="1225" t="n"/>
+      <c r="AA164" s="1225" t="n"/>
+      <c r="AB164" s="1225" t="n"/>
+      <c r="AC164" s="1225" t="n"/>
+      <c r="AD164" s="1225" t="n"/>
+      <c r="AE164" s="1225" t="n"/>
+      <c r="AF164" s="1225" t="n"/>
+      <c r="AG164" s="1225" t="n"/>
+      <c r="AH164" s="1225" t="n"/>
+      <c r="AI164" s="1225" t="n"/>
+      <c r="AJ164" s="1225" t="n"/>
+      <c r="AK164" s="1225" t="n"/>
+      <c r="AL164" s="1225" t="n"/>
+      <c r="AM164" s="1225" t="n"/>
+      <c r="AN164" s="1225" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="141">

--- a/output/acs-activity-calendar-2027.xlsx
+++ b/output/acs-activity-calendar-2027.xlsx
@@ -2574,7 +2574,7 @@
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1283">
+  <cellXfs count="1287">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6459,6 +6459,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="109" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -7433,7 +7445,7 @@
           <t>January</t>
         </is>
       </c>
-      <c r="B4" s="1266" t="n"/>
+      <c r="B4" s="1283" t="n"/>
       <c r="F4" s="1149" t="n"/>
       <c r="G4" s="1238" t="n">
         <v>1</v>
@@ -7528,7 +7540,7 @@
       <c r="AK4" s="1239" t="n">
         <v>31</v>
       </c>
-      <c r="AL4" s="1267" t="n"/>
+      <c r="AL4" s="1284" t="n"/>
       <c r="AN4" s="1149" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
@@ -8081,7 +8093,7 @@
           <t>February</t>
         </is>
       </c>
-      <c r="B18" s="1277" t="n"/>
+      <c r="B18" s="1285" t="n"/>
       <c r="I18" s="1149" t="n"/>
       <c r="J18" s="1238" t="n">
         <v>1</v>
@@ -8167,7 +8179,7 @@
       <c r="AK18" s="1239" t="n">
         <v>28</v>
       </c>
-      <c r="AL18" s="1278" t="n"/>
+      <c r="AL18" s="1286" t="n"/>
       <c r="AN18" s="1149" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1" thickBot="1">
@@ -8695,7 +8707,7 @@
           <t>March</t>
         </is>
       </c>
-      <c r="B32" s="1278" t="n"/>
+      <c r="B32" s="1286" t="n"/>
       <c r="I32" s="1149" t="n"/>
       <c r="J32" s="1238" t="n">
         <v>1</v>
@@ -9311,7 +9323,7 @@
           <t>April</t>
         </is>
       </c>
-      <c r="B45" s="1278" t="n"/>
+      <c r="B45" s="1286" t="n"/>
       <c r="E45" s="1149" t="n"/>
       <c r="F45" s="1238" t="n">
         <v>1</v>
@@ -9403,7 +9415,7 @@
       <c r="AI45" s="1238" t="n">
         <v>30</v>
       </c>
-      <c r="AJ45" s="1266" t="n"/>
+      <c r="AJ45" s="1283" t="n"/>
       <c r="AN45" s="1149" t="n"/>
     </row>
     <row r="46" ht="15" customHeight="1">
@@ -9906,7 +9918,7 @@
           <t>May</t>
         </is>
       </c>
-      <c r="B58" s="1278" t="n"/>
+      <c r="B58" s="1286" t="n"/>
       <c r="G58" s="1149" t="n"/>
       <c r="H58" s="1239" t="n">
         <v>1</v>
@@ -10001,7 +10013,7 @@
       <c r="AL58" s="1238" t="n">
         <v>31</v>
       </c>
-      <c r="AM58" s="1278" t="n"/>
+      <c r="AM58" s="1286" t="n"/>
       <c r="AN58" s="1149" t="n"/>
     </row>
     <row r="59" ht="15" customHeight="1" thickBot="1">
@@ -10522,7 +10534,7 @@
           <t>June</t>
         </is>
       </c>
-      <c r="B71" s="1266" t="n"/>
+      <c r="B71" s="1283" t="n"/>
       <c r="C71" s="1149" t="n"/>
       <c r="D71" s="1238" t="n">
         <v>1</v>
@@ -10614,7 +10626,7 @@
       <c r="AG71" s="1238" t="n">
         <v>30</v>
       </c>
-      <c r="AH71" s="1266" t="n"/>
+      <c r="AH71" s="1283" t="n"/>
       <c r="AN71" s="1149" t="n"/>
     </row>
     <row r="72" ht="15" customHeight="1" thickBot="1">
@@ -11121,7 +11133,7 @@
           <t>July</t>
         </is>
       </c>
-      <c r="B84" s="1278" t="n"/>
+      <c r="B84" s="1286" t="n"/>
       <c r="E84" s="1149" t="n"/>
       <c r="F84" s="1238" t="n">
         <v>1</v>
@@ -11216,7 +11228,7 @@
       <c r="AJ84" s="1239" t="n">
         <v>31</v>
       </c>
-      <c r="AK84" s="1266" t="n"/>
+      <c r="AK84" s="1283" t="n"/>
       <c r="AN84" s="1149" t="n"/>
     </row>
     <row r="85" ht="15" customHeight="1" thickBot="1">
@@ -11725,7 +11737,7 @@
           <t>August</t>
         </is>
       </c>
-      <c r="B97" s="1278" t="n"/>
+      <c r="B97" s="1286" t="n"/>
       <c r="H97" s="1149" t="n"/>
       <c r="I97" s="1239" t="n">
         <v>1</v>
@@ -11820,7 +11832,7 @@
       <c r="AM97" s="1238" t="n">
         <v>31</v>
       </c>
-      <c r="AN97" s="1266" t="n"/>
+      <c r="AN97" s="1283" t="n"/>
     </row>
     <row r="98" ht="15" customHeight="1">
       <c r="A98" s="1241" t="inlineStr">
@@ -12368,7 +12380,7 @@
           <t>September</t>
         </is>
       </c>
-      <c r="B111" s="1278" t="n"/>
+      <c r="B111" s="1286" t="n"/>
       <c r="D111" s="1149" t="n"/>
       <c r="E111" s="1238" t="n">
         <v>1</v>
@@ -12460,7 +12472,7 @@
       <c r="AH111" s="1238" t="n">
         <v>30</v>
       </c>
-      <c r="AI111" s="1266" t="n"/>
+      <c r="AI111" s="1283" t="n"/>
       <c r="AN111" s="1149" t="n"/>
     </row>
     <row r="112" ht="15" customHeight="1">
@@ -12975,7 +12987,7 @@
           <t>October</t>
         </is>
       </c>
-      <c r="B124" s="1266" t="n"/>
+      <c r="B124" s="1283" t="n"/>
       <c r="F124" s="1149" t="n"/>
       <c r="G124" s="1238" t="n">
         <v>1</v>
@@ -13070,7 +13082,7 @@
       <c r="AK124" s="1239" t="n">
         <v>31</v>
       </c>
-      <c r="AL124" s="1278" t="n"/>
+      <c r="AL124" s="1286" t="n"/>
       <c r="AN124" s="1149" t="n"/>
     </row>
     <row r="125" ht="15" customHeight="1">
@@ -13583,7 +13595,7 @@
           <t>November</t>
         </is>
       </c>
-      <c r="B137" s="1278" t="n"/>
+      <c r="B137" s="1286" t="n"/>
       <c r="I137" s="1149" t="n"/>
       <c r="J137" s="1238" t="n">
         <v>1</v>
@@ -13675,7 +13687,7 @@
       <c r="AM137" s="1238" t="n">
         <v>30</v>
       </c>
-      <c r="AN137" s="1278" t="n"/>
+      <c r="AN137" s="1286" t="n"/>
     </row>
     <row r="138" ht="15" customHeight="1" thickBot="1">
       <c r="A138" s="1241" t="inlineStr">
@@ -14181,7 +14193,7 @@
           <t>December</t>
         </is>
       </c>
-      <c r="B150" s="1266" t="n"/>
+      <c r="B150" s="1283" t="n"/>
       <c r="D150" s="1149" t="n"/>
       <c r="E150" s="1238" t="n">
         <v>1</v>
@@ -14276,7 +14288,7 @@
       <c r="AI150" s="1238" t="n">
         <v>31</v>
       </c>
-      <c r="AJ150" s="1266" t="n"/>
+      <c r="AJ150" s="1283" t="n"/>
       <c r="AN150" s="1149" t="n"/>
     </row>
     <row r="151" ht="15" customHeight="1" thickBot="1">
@@ -15068,8 +15080,8 @@
     <mergeCell ref="D81:U81"/>
     <mergeCell ref="P131:U131"/>
     <mergeCell ref="J42:W42"/>
+    <mergeCell ref="J147:AB147"/>
     <mergeCell ref="G131:H131"/>
-    <mergeCell ref="J147:AB147"/>
     <mergeCell ref="AN97:AN109"/>
     <mergeCell ref="V41:AB41"/>
     <mergeCell ref="AE13:AK13"/>

--- a/output/acs-activity-calendar-2027.xlsx
+++ b/output/acs-activity-calendar-2027.xlsx
@@ -828,7 +828,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="153">
+  <borders count="155">
     <border>
       <left/>
       <right/>
@@ -2554,6 +2554,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color rgb="00C8C6BD"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="00C8C6BD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color rgb="00C8C6BD"/>
+      </right>
+      <top style="hair">
+        <color rgb="00C8C6BD"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="00C8C6BD"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2574,7 +2598,7 @@
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1287">
+  <cellXfs count="1294">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6472,6 +6496,25 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="103" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="53" borderId="146" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="146" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="103" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="54" borderId="146" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="54" borderId="146" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="146" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7789,7 +7832,7 @@
       <c r="K11" s="1013" t="n"/>
       <c r="L11" s="1273" t="inlineStr">
         <is>
-          <t>TtT TFCC</t>
+          <t>LD TtT TFCC</t>
         </is>
       </c>
       <c r="M11" s="1155" t="n"/>
@@ -7805,7 +7848,7 @@
       <c r="W11" s="1012" t="n"/>
       <c r="X11" s="1273" t="inlineStr">
         <is>
-          <t>LEAD TEAMS BMC</t>
+          <t>LD LEAD TEAMS BMC</t>
         </is>
       </c>
       <c r="Y11" s="1155" t="n"/>
@@ -7842,7 +7885,7 @@
       <c r="P12" s="1012" t="n"/>
       <c r="Q12" s="1274" t="inlineStr">
         <is>
-          <t>LEAD TEAMS BMC</t>
+          <t>ELDA LEAD TEAMS BMC</t>
         </is>
       </c>
       <c r="R12" s="1155" t="n"/>
@@ -7860,7 +7903,7 @@
       <c r="AD12" s="1012" t="n"/>
       <c r="AE12" s="1274" t="inlineStr">
         <is>
-          <t>LEAD TEAMS LMC</t>
+          <t>ELDA LEAD TEAMS LMC</t>
         </is>
       </c>
       <c r="AF12" s="1155" t="n"/>
@@ -8370,15 +8413,11 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="1268" t="n"/>
       <c r="I24" s="1149" t="n"/>
-      <c r="J24" s="1273" t="inlineStr">
-        <is>
-          <t>LEAD TEAMS LMC</t>
-        </is>
-      </c>
-      <c r="K24" s="1155" t="n"/>
-      <c r="L24" s="1155" t="n"/>
-      <c r="M24" s="1155" t="n"/>
-      <c r="N24" s="1156" t="n"/>
+      <c r="J24" s="1287" t="n"/>
+      <c r="K24" s="1003" t="n"/>
+      <c r="L24" s="1003" t="n"/>
+      <c r="M24" s="1003" t="n"/>
+      <c r="N24" s="1003" t="n"/>
       <c r="O24" s="1015" t="n"/>
       <c r="P24" s="1015" t="n"/>
       <c r="Q24" s="1043" t="n"/>
@@ -8388,15 +8427,11 @@
       <c r="U24" s="1024" t="n"/>
       <c r="V24" s="1012" t="n"/>
       <c r="W24" s="1012" t="n"/>
-      <c r="X24" s="1273" t="inlineStr">
-        <is>
-          <t>LEAD LEADERS BMC</t>
-        </is>
-      </c>
-      <c r="Y24" s="1155" t="n"/>
-      <c r="Z24" s="1155" t="n"/>
-      <c r="AA24" s="1155" t="n"/>
-      <c r="AB24" s="1156" t="n"/>
+      <c r="X24" s="1287" t="n"/>
+      <c r="Y24" s="1003" t="n"/>
+      <c r="Z24" s="1003" t="n"/>
+      <c r="AA24" s="1003" t="n"/>
+      <c r="AB24" s="1003" t="n"/>
       <c r="AC24" s="1012" t="n"/>
       <c r="AD24" s="1012" t="n"/>
       <c r="AE24" s="1024" t="n"/>
@@ -8415,41 +8450,41 @@
         </is>
       </c>
       <c r="I25" s="1149" t="n"/>
-      <c r="J25" s="1024" t="n"/>
-      <c r="K25" s="1024" t="n"/>
-      <c r="L25" s="1024" t="n"/>
-      <c r="M25" s="1024" t="n"/>
-      <c r="N25" s="1008" t="n"/>
+      <c r="J25" s="1288" t="inlineStr">
+        <is>
+          <t>LD LEAD TEAMS LMC</t>
+        </is>
+      </c>
+      <c r="K25" s="1289" t="n"/>
+      <c r="L25" s="1289" t="n"/>
+      <c r="M25" s="1289" t="n"/>
+      <c r="N25" s="1289" t="n"/>
       <c r="O25" s="1012" t="n"/>
       <c r="P25" s="1012" t="n"/>
-      <c r="Q25" s="1274" t="inlineStr">
-        <is>
-          <t>LEAD LEADERS BMC</t>
-        </is>
-      </c>
-      <c r="R25" s="1155" t="n"/>
-      <c r="S25" s="1155" t="n"/>
-      <c r="T25" s="1155" t="n"/>
-      <c r="U25" s="1155" t="n"/>
-      <c r="V25" s="1156" t="n"/>
+      <c r="Q25" s="1287" t="n"/>
+      <c r="R25" s="1003" t="n"/>
+      <c r="S25" s="1003" t="n"/>
+      <c r="T25" s="1003" t="n"/>
+      <c r="U25" s="1003" t="n"/>
+      <c r="V25" s="1290" t="n"/>
       <c r="W25" s="1012" t="n"/>
-      <c r="X25" s="1024" t="n"/>
-      <c r="Y25" s="1024" t="n"/>
-      <c r="Z25" s="1024" t="n"/>
-      <c r="AA25" s="1024" t="n"/>
-      <c r="AB25" s="1024" t="n"/>
+      <c r="X25" s="1288" t="inlineStr">
+        <is>
+          <t>LD LEAD LEADERS BMC</t>
+        </is>
+      </c>
+      <c r="Y25" s="1289" t="n"/>
+      <c r="Z25" s="1289" t="n"/>
+      <c r="AA25" s="1289" t="n"/>
+      <c r="AB25" s="1289" t="n"/>
       <c r="AC25" s="1012" t="n"/>
       <c r="AD25" s="1012" t="n"/>
-      <c r="AE25" s="1274" t="inlineStr">
-        <is>
-          <t>LEAD LEADERS OFFICER</t>
-        </is>
-      </c>
-      <c r="AF25" s="1155" t="n"/>
-      <c r="AG25" s="1155" t="n"/>
-      <c r="AH25" s="1155" t="n"/>
-      <c r="AI25" s="1155" t="n"/>
-      <c r="AJ25" s="1156" t="n"/>
+      <c r="AE25" s="1287" t="n"/>
+      <c r="AF25" s="1003" t="n"/>
+      <c r="AG25" s="1003" t="n"/>
+      <c r="AH25" s="1003" t="n"/>
+      <c r="AI25" s="1003" t="n"/>
+      <c r="AJ25" s="1290" t="n"/>
       <c r="AK25" s="1045" t="n"/>
       <c r="AN25" s="1149" t="n"/>
     </row>
@@ -8467,12 +8502,16 @@
       <c r="N26" s="1008" t="n"/>
       <c r="O26" s="1012" t="n"/>
       <c r="P26" s="1012" t="n"/>
-      <c r="Q26" s="1043" t="n"/>
-      <c r="R26" s="1024" t="n"/>
-      <c r="S26" s="1024" t="n"/>
-      <c r="T26" s="1024" t="n"/>
-      <c r="U26" s="1024" t="n"/>
-      <c r="V26" s="1012" t="n"/>
+      <c r="Q26" s="1291" t="inlineStr">
+        <is>
+          <t>ELDA LEAD LEADERS BMC</t>
+        </is>
+      </c>
+      <c r="R26" s="1292" t="n"/>
+      <c r="S26" s="1292" t="n"/>
+      <c r="T26" s="1292" t="n"/>
+      <c r="U26" s="1292" t="n"/>
+      <c r="V26" s="1292" t="n"/>
       <c r="W26" s="1012" t="n"/>
       <c r="X26" s="1024" t="n"/>
       <c r="Y26" s="1024" t="n"/>
@@ -8481,12 +8520,16 @@
       <c r="AB26" s="1024" t="n"/>
       <c r="AC26" s="1043" t="n"/>
       <c r="AD26" s="1012" t="n"/>
-      <c r="AE26" s="1024" t="n"/>
-      <c r="AF26" s="1024" t="n"/>
-      <c r="AG26" s="1024" t="n"/>
-      <c r="AH26" s="1024" t="n"/>
-      <c r="AI26" s="1024" t="n"/>
-      <c r="AJ26" s="1045" t="n"/>
+      <c r="AE26" s="1291" t="inlineStr">
+        <is>
+          <t>ELDA LEAD LEADERS OFFICER</t>
+        </is>
+      </c>
+      <c r="AF26" s="1292" t="n"/>
+      <c r="AG26" s="1292" t="n"/>
+      <c r="AH26" s="1292" t="n"/>
+      <c r="AI26" s="1292" t="n"/>
+      <c r="AJ26" s="1292" t="n"/>
       <c r="AK26" s="1045" t="n"/>
       <c r="AN26" s="1149" t="n"/>
     </row>
@@ -8817,21 +8860,13 @@
       <c r="N33" s="1008" t="n"/>
       <c r="O33" s="1012" t="n"/>
       <c r="P33" s="1012" t="n"/>
-      <c r="Q33" s="1273" t="inlineStr">
-        <is>
-          <t>TTT WAI</t>
-        </is>
-      </c>
-      <c r="R33" s="1155" t="n"/>
-      <c r="S33" s="1156" t="n"/>
+      <c r="Q33" s="1287" t="n"/>
+      <c r="R33" s="1003" t="n"/>
+      <c r="S33" s="1003" t="n"/>
       <c r="T33" s="1008" t="n"/>
-      <c r="U33" s="1273" t="inlineStr">
-        <is>
-          <t>LEAD TEAMS</t>
-        </is>
-      </c>
-      <c r="V33" s="1155" t="n"/>
-      <c r="W33" s="1156" t="n"/>
+      <c r="U33" s="1287" t="n"/>
+      <c r="V33" s="1290" t="n"/>
+      <c r="W33" s="1290" t="n"/>
       <c r="X33" s="1008" t="n"/>
       <c r="Y33" s="1009" t="n"/>
       <c r="Z33" s="1009" t="n"/>
@@ -8868,18 +8903,14 @@
       <c r="V34" s="1012" t="n"/>
       <c r="W34" s="1012" t="n"/>
       <c r="X34" s="1008" t="n"/>
-      <c r="Y34" s="1274" t="inlineStr">
-        <is>
-          <t>LEAD SYS OFFICER</t>
-        </is>
-      </c>
-      <c r="Z34" s="1155" t="n"/>
-      <c r="AA34" s="1155" t="n"/>
-      <c r="AB34" s="1155" t="n"/>
-      <c r="AC34" s="1155" t="n"/>
-      <c r="AD34" s="1155" t="n"/>
-      <c r="AE34" s="1155" t="n"/>
-      <c r="AF34" s="1156" t="n"/>
+      <c r="Y34" s="1287" t="n"/>
+      <c r="Z34" s="1003" t="n"/>
+      <c r="AA34" s="1003" t="n"/>
+      <c r="AB34" s="1003" t="n"/>
+      <c r="AC34" s="1290" t="n"/>
+      <c r="AD34" s="1290" t="n"/>
+      <c r="AE34" s="1003" t="n"/>
+      <c r="AF34" s="1003" t="n"/>
       <c r="AG34" s="1022" t="n"/>
       <c r="AH34" s="1022" t="n"/>
       <c r="AI34" s="1012" t="n"/>
@@ -9020,13 +9051,21 @@
       <c r="N38" s="1013" t="n"/>
       <c r="O38" s="1012" t="n"/>
       <c r="P38" s="1015" t="n"/>
-      <c r="Q38" s="1064" t="n"/>
-      <c r="R38" s="1022" t="n"/>
-      <c r="S38" s="1022" t="n"/>
+      <c r="Q38" s="1245" t="inlineStr">
+        <is>
+          <t>LD TTT WAI</t>
+        </is>
+      </c>
+      <c r="R38" s="1293" t="n"/>
+      <c r="S38" s="1293" t="n"/>
       <c r="T38" s="1024" t="n"/>
-      <c r="U38" s="1022" t="n"/>
-      <c r="V38" s="1044" t="n"/>
-      <c r="W38" s="1044" t="n"/>
+      <c r="U38" s="1288" t="inlineStr">
+        <is>
+          <t>LD LEAD TEAMS</t>
+        </is>
+      </c>
+      <c r="V38" s="1289" t="n"/>
+      <c r="W38" s="1289" t="n"/>
       <c r="X38" s="1008" t="n"/>
       <c r="Y38" s="1008" t="n"/>
       <c r="Z38" s="1022" t="n"/>
@@ -9067,14 +9106,18 @@
       <c r="V39" s="1012" t="n"/>
       <c r="W39" s="1012" t="n"/>
       <c r="X39" s="1008" t="n"/>
-      <c r="Y39" s="1022" t="n"/>
-      <c r="Z39" s="1022" t="n"/>
-      <c r="AA39" s="1022" t="n"/>
-      <c r="AB39" s="1022" t="n"/>
-      <c r="AC39" s="1044" t="n"/>
-      <c r="AD39" s="1044" t="n"/>
-      <c r="AE39" s="1022" t="n"/>
-      <c r="AF39" s="1022" t="n"/>
+      <c r="Y39" s="1291" t="inlineStr">
+        <is>
+          <t>ELDA LEAD SYS OFFICER</t>
+        </is>
+      </c>
+      <c r="Z39" s="1292" t="n"/>
+      <c r="AA39" s="1292" t="n"/>
+      <c r="AB39" s="1292" t="n"/>
+      <c r="AC39" s="1292" t="n"/>
+      <c r="AD39" s="1292" t="n"/>
+      <c r="AE39" s="1292" t="n"/>
+      <c r="AF39" s="1292" t="n"/>
       <c r="AG39" s="1022" t="n"/>
       <c r="AH39" s="1022" t="n"/>
       <c r="AI39" s="1012" t="n"/>
@@ -9682,7 +9725,7 @@
       <c r="AD52" s="1012" t="n"/>
       <c r="AE52" s="1274" t="inlineStr">
         <is>
-          <t>LEAD LEADERS BMC</t>
+          <t>ELDA LEAD LEADERS BMC</t>
         </is>
       </c>
       <c r="AF52" s="1155" t="n"/>
@@ -10219,7 +10262,7 @@
       <c r="I64" s="1090" t="n"/>
       <c r="J64" s="1273" t="inlineStr">
         <is>
-          <t>LEAD LEADERS 27_03 BMC</t>
+          <t>LD LEAD LEADERS 27_03 BMC</t>
         </is>
       </c>
       <c r="K64" s="1155" t="n"/>
@@ -10237,7 +10280,7 @@
       <c r="W64" s="1091" t="n"/>
       <c r="X64" s="1273" t="inlineStr">
         <is>
-          <t>LEAD TEAMS BMC</t>
+          <t>LD LEAD TEAMS BMC</t>
         </is>
       </c>
       <c r="Y64" s="1155" t="n"/>
@@ -10274,7 +10317,7 @@
       <c r="P65" s="1012" t="n"/>
       <c r="Q65" s="1274" t="inlineStr">
         <is>
-          <t>LEAD TEAMS BMC</t>
+          <t>ELDA LEAD TEAMS BMC</t>
         </is>
       </c>
       <c r="R65" s="1155" t="n"/>
@@ -10292,7 +10335,7 @@
       <c r="AD65" s="1012" t="n"/>
       <c r="AE65" s="1274" t="inlineStr">
         <is>
-          <t>LEAD TEAMS LTN</t>
+          <t>ELDA LEAD TEAMS LTN</t>
         </is>
       </c>
       <c r="AF65" s="1155" t="n"/>
@@ -10825,7 +10868,7 @@
       <c r="C77" s="1149" t="n"/>
       <c r="D77" s="1273" t="inlineStr">
         <is>
-          <t>LEAD TEAMS LTN</t>
+          <t>LD LEAD TEAMS LTN</t>
         </is>
       </c>
       <c r="E77" s="1155" t="n"/>
@@ -10882,7 +10925,7 @@
       <c r="Q78" s="1008" t="n"/>
       <c r="R78" s="1274" t="inlineStr">
         <is>
-          <t>LEAD SYS</t>
+          <t>ELDA LEAD SYS</t>
         </is>
       </c>
       <c r="S78" s="1155" t="n"/>
@@ -12084,7 +12127,7 @@
       <c r="M104" s="1008" t="n"/>
       <c r="N104" s="1274" t="inlineStr">
         <is>
-          <t>LEAD SYS (ADV RACE)</t>
+          <t>ELDA LEAD SYS (ADV RACE)</t>
         </is>
       </c>
       <c r="O104" s="1155" t="n"/>
@@ -12105,7 +12148,7 @@
       <c r="AD104" s="1012" t="n"/>
       <c r="AE104" s="1274" t="inlineStr">
         <is>
-          <t>LEAD SYS (ALPINE TOUR)</t>
+          <t>ELDA LEAD SYS (ALPINE TOUR)</t>
         </is>
       </c>
       <c r="AF104" s="1155" t="n"/>
@@ -12116,7 +12159,7 @@
       <c r="AK104" s="1156" t="n"/>
       <c r="AL104" s="1274" t="inlineStr">
         <is>
-          <t>LEAD TEAMS</t>
+          <t>ELDA LEAD TEAMS</t>
         </is>
       </c>
       <c r="AM104" s="1156" t="n"/>
@@ -12676,7 +12719,7 @@
       <c r="I117" s="1044" t="n"/>
       <c r="J117" s="1273" t="inlineStr">
         <is>
-          <t>LEAD TEAMS BMC</t>
+          <t>LD LEAD TEAMS BMC</t>
         </is>
       </c>
       <c r="K117" s="1155" t="n"/>
@@ -12694,7 +12737,7 @@
       <c r="W117" s="1108" t="n"/>
       <c r="X117" s="1273" t="inlineStr">
         <is>
-          <t>LEAD TEAMS LTN</t>
+          <t>LD LEAD TEAMS LTN</t>
         </is>
       </c>
       <c r="Y117" s="1155" t="n"/>
@@ -12718,7 +12761,7 @@
       <c r="D118" s="1149" t="n"/>
       <c r="E118" s="1274" t="inlineStr">
         <is>
-          <t>LEAD TEAMS BMC</t>
+          <t>ELDA LEAD TEAMS BMC</t>
         </is>
       </c>
       <c r="F118" s="1155" t="n"/>
@@ -12734,7 +12777,7 @@
       <c r="P118" s="1044" t="n"/>
       <c r="Q118" s="1274" t="inlineStr">
         <is>
-          <t>LEAD TEAMS LTN</t>
+          <t>ELDA LEAD TEAMS LTN</t>
         </is>
       </c>
       <c r="R118" s="1155" t="n"/>
@@ -12751,7 +12794,7 @@
       <c r="AC118" s="1044" t="n"/>
       <c r="AD118" s="1274" t="inlineStr">
         <is>
-          <t>LEAD LEADERS</t>
+          <t>ELDA LEAD LEADERS</t>
         </is>
       </c>
       <c r="AE118" s="1155" t="n"/>
@@ -13289,7 +13332,7 @@
       <c r="I130" s="1091" t="n"/>
       <c r="J130" s="1273" t="inlineStr">
         <is>
-          <t>LEAD LEADERS</t>
+          <t>LD LEAD LEADERS</t>
         </is>
       </c>
       <c r="K130" s="1155" t="n"/>
@@ -13339,7 +13382,7 @@
       <c r="O131" s="1043" t="n"/>
       <c r="P131" s="1274" t="inlineStr">
         <is>
-          <t>LEAD LEADERS (OFFICERS)</t>
+          <t>ELDA LEAD LEADERS (OFFICERS)</t>
         </is>
       </c>
       <c r="Q131" s="1155" t="n"/>
@@ -13926,7 +13969,7 @@
       <c r="O144" s="1043" t="n"/>
       <c r="P144" s="1274" t="inlineStr">
         <is>
-          <t>LEAD INTEGRATED CAP</t>
+          <t>ELDA LEAD INTEGRATED CAP</t>
         </is>
       </c>
       <c r="Q144" s="1155" t="n"/>
@@ -15039,6 +15082,7 @@
     <mergeCell ref="AK105:AM105"/>
     <mergeCell ref="AH71:AN82"/>
     <mergeCell ref="L11:N11"/>
+    <mergeCell ref="J25:N25"/>
     <mergeCell ref="A33:A34"/>
     <mergeCell ref="D77:G77"/>
     <mergeCell ref="B137:I148"/>
@@ -15046,7 +15090,6 @@
     <mergeCell ref="AJ45:AN56"/>
     <mergeCell ref="F87:Q87"/>
     <mergeCell ref="D79:AG79"/>
-    <mergeCell ref="Q33:S33"/>
     <mergeCell ref="J130:N130"/>
     <mergeCell ref="A59:A60"/>
     <mergeCell ref="B97:H109"/>
@@ -15058,12 +15101,12 @@
     <mergeCell ref="J145:P145"/>
     <mergeCell ref="AL104:AM104"/>
     <mergeCell ref="J151:N160"/>
-    <mergeCell ref="J24:N24"/>
     <mergeCell ref="A114:A116"/>
     <mergeCell ref="A46:A47"/>
     <mergeCell ref="A21:A24"/>
     <mergeCell ref="AM58:AN69"/>
     <mergeCell ref="AE52:AI52"/>
+    <mergeCell ref="U38:W38"/>
     <mergeCell ref="J120:AH120"/>
     <mergeCell ref="P107:AC107"/>
     <mergeCell ref="AE80:AG80"/>
@@ -15077,16 +15120,18 @@
     <mergeCell ref="B18:I30"/>
     <mergeCell ref="B150:D161"/>
     <mergeCell ref="A74:A76"/>
+    <mergeCell ref="X25:AB25"/>
     <mergeCell ref="D81:U81"/>
     <mergeCell ref="P131:U131"/>
     <mergeCell ref="J42:W42"/>
+    <mergeCell ref="G131:H131"/>
     <mergeCell ref="J147:AB147"/>
-    <mergeCell ref="G131:H131"/>
     <mergeCell ref="AN97:AN109"/>
     <mergeCell ref="V41:AB41"/>
     <mergeCell ref="AE13:AK13"/>
     <mergeCell ref="X11:AB11"/>
     <mergeCell ref="A100:A102"/>
+    <mergeCell ref="Q26:V26"/>
     <mergeCell ref="AE104:AK104"/>
     <mergeCell ref="Q114:AH114"/>
     <mergeCell ref="Q65:V65"/>
@@ -15094,8 +15139,6 @@
     <mergeCell ref="F93:N93"/>
     <mergeCell ref="AE65:AJ65"/>
     <mergeCell ref="A127:A129"/>
-    <mergeCell ref="X24:AB24"/>
-    <mergeCell ref="Y34:AF34"/>
     <mergeCell ref="A87:A89"/>
     <mergeCell ref="V81:AB81"/>
     <mergeCell ref="J28:AK28"/>
@@ -15117,6 +15160,7 @@
     <mergeCell ref="AE12:AJ12"/>
     <mergeCell ref="AE55:AI55"/>
     <mergeCell ref="B111:D122"/>
+    <mergeCell ref="Q38:S38"/>
     <mergeCell ref="O7:AK7"/>
     <mergeCell ref="J36:U36"/>
     <mergeCell ref="AL4:AN16"/>
@@ -15124,10 +15168,10 @@
     <mergeCell ref="X119:AH119"/>
     <mergeCell ref="AE133:AK133"/>
     <mergeCell ref="A140:A142"/>
+    <mergeCell ref="Y39:AF39"/>
     <mergeCell ref="F55:G55"/>
     <mergeCell ref="A35:A37"/>
     <mergeCell ref="M23:AB23"/>
-    <mergeCell ref="U33:W33"/>
     <mergeCell ref="AC92:AJ92"/>
     <mergeCell ref="A108:A109"/>
     <mergeCell ref="AJ150:AN161"/>
@@ -15141,14 +15185,13 @@
     <mergeCell ref="AC145:AI145"/>
     <mergeCell ref="A72:A73"/>
     <mergeCell ref="AE121:AH121"/>
+    <mergeCell ref="AE26:AJ26"/>
     <mergeCell ref="X117:AB117"/>
     <mergeCell ref="S100:AD100"/>
-    <mergeCell ref="Q25:V25"/>
     <mergeCell ref="AC147:AI147"/>
     <mergeCell ref="Q67:AL67"/>
     <mergeCell ref="X40:AI40"/>
     <mergeCell ref="O146:U146"/>
-    <mergeCell ref="AE25:AJ25"/>
     <mergeCell ref="O93:U93"/>
     <mergeCell ref="AL18:AN30"/>
     <mergeCell ref="X74:AG74"/>

--- a/output/acs-activity-calendar-2027.xlsx
+++ b/output/acs-activity-calendar-2027.xlsx
@@ -2598,7 +2598,7 @@
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1294">
+  <cellXfs count="1295">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6515,6 +6515,10 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="53" borderId="146" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="103" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8455,10 +8459,10 @@
           <t>LD LEAD TEAMS LMC</t>
         </is>
       </c>
-      <c r="K25" s="1289" t="n"/>
-      <c r="L25" s="1289" t="n"/>
-      <c r="M25" s="1289" t="n"/>
-      <c r="N25" s="1289" t="n"/>
+      <c r="K25" s="844" t="n"/>
+      <c r="L25" s="844" t="n"/>
+      <c r="M25" s="844" t="n"/>
+      <c r="N25" s="844" t="n"/>
       <c r="O25" s="1012" t="n"/>
       <c r="P25" s="1012" t="n"/>
       <c r="Q25" s="1287" t="n"/>
@@ -8473,10 +8477,10 @@
           <t>LD LEAD LEADERS BMC</t>
         </is>
       </c>
-      <c r="Y25" s="1289" t="n"/>
-      <c r="Z25" s="1289" t="n"/>
-      <c r="AA25" s="1289" t="n"/>
-      <c r="AB25" s="1289" t="n"/>
+      <c r="Y25" s="844" t="n"/>
+      <c r="Z25" s="844" t="n"/>
+      <c r="AA25" s="844" t="n"/>
+      <c r="AB25" s="844" t="n"/>
       <c r="AC25" s="1012" t="n"/>
       <c r="AD25" s="1012" t="n"/>
       <c r="AE25" s="1287" t="n"/>
@@ -8507,11 +8511,11 @@
           <t>ELDA LEAD LEADERS BMC</t>
         </is>
       </c>
-      <c r="R26" s="1292" t="n"/>
-      <c r="S26" s="1292" t="n"/>
-      <c r="T26" s="1292" t="n"/>
-      <c r="U26" s="1292" t="n"/>
-      <c r="V26" s="1292" t="n"/>
+      <c r="R26" s="844" t="n"/>
+      <c r="S26" s="844" t="n"/>
+      <c r="T26" s="844" t="n"/>
+      <c r="U26" s="844" t="n"/>
+      <c r="V26" s="844" t="n"/>
       <c r="W26" s="1012" t="n"/>
       <c r="X26" s="1024" t="n"/>
       <c r="Y26" s="1024" t="n"/>
@@ -8525,11 +8529,11 @@
           <t>ELDA LEAD LEADERS OFFICER</t>
         </is>
       </c>
-      <c r="AF26" s="1292" t="n"/>
-      <c r="AG26" s="1292" t="n"/>
-      <c r="AH26" s="1292" t="n"/>
-      <c r="AI26" s="1292" t="n"/>
-      <c r="AJ26" s="1292" t="n"/>
+      <c r="AF26" s="844" t="n"/>
+      <c r="AG26" s="844" t="n"/>
+      <c r="AH26" s="844" t="n"/>
+      <c r="AI26" s="844" t="n"/>
+      <c r="AJ26" s="844" t="n"/>
       <c r="AK26" s="1045" t="n"/>
       <c r="AN26" s="1149" t="n"/>
     </row>
@@ -9051,28 +9055,24 @@
       <c r="N38" s="1013" t="n"/>
       <c r="O38" s="1012" t="n"/>
       <c r="P38" s="1015" t="n"/>
-      <c r="Q38" s="1245" t="inlineStr">
-        <is>
-          <t>LD TTT WAI</t>
-        </is>
-      </c>
-      <c r="R38" s="1293" t="n"/>
-      <c r="S38" s="1293" t="n"/>
+      <c r="Q38" s="1287" t="n"/>
+      <c r="R38" s="1003" t="n"/>
+      <c r="S38" s="1003" t="n"/>
       <c r="T38" s="1024" t="n"/>
-      <c r="U38" s="1288" t="inlineStr">
-        <is>
-          <t>LD LEAD TEAMS</t>
-        </is>
-      </c>
-      <c r="V38" s="1289" t="n"/>
-      <c r="W38" s="1289" t="n"/>
+      <c r="U38" s="1294" t="n"/>
+      <c r="V38" s="1290" t="n"/>
+      <c r="W38" s="1290" t="n"/>
       <c r="X38" s="1008" t="n"/>
       <c r="Y38" s="1008" t="n"/>
       <c r="Z38" s="1022" t="n"/>
       <c r="AA38" s="1022" t="n"/>
-      <c r="AB38" s="1022" t="n"/>
-      <c r="AC38" s="1044" t="n"/>
-      <c r="AD38" s="1044" t="n"/>
+      <c r="AB38" s="1288" t="inlineStr">
+        <is>
+          <t>LD LEAD TEAMS</t>
+        </is>
+      </c>
+      <c r="AC38" s="1289" t="n"/>
+      <c r="AD38" s="1289" t="n"/>
       <c r="AE38" s="1022" t="n"/>
       <c r="AF38" s="1022" t="n"/>
       <c r="AG38" s="1022" t="n"/>
@@ -9111,13 +9111,13 @@
           <t>ELDA LEAD SYS OFFICER</t>
         </is>
       </c>
-      <c r="Z39" s="1292" t="n"/>
-      <c r="AA39" s="1292" t="n"/>
-      <c r="AB39" s="1292" t="n"/>
-      <c r="AC39" s="1292" t="n"/>
-      <c r="AD39" s="1292" t="n"/>
-      <c r="AE39" s="1292" t="n"/>
-      <c r="AF39" s="1292" t="n"/>
+      <c r="Z39" s="844" t="n"/>
+      <c r="AA39" s="844" t="n"/>
+      <c r="AB39" s="844" t="n"/>
+      <c r="AC39" s="844" t="n"/>
+      <c r="AD39" s="844" t="n"/>
+      <c r="AE39" s="844" t="n"/>
+      <c r="AF39" s="844" t="n"/>
       <c r="AG39" s="1022" t="n"/>
       <c r="AH39" s="1022" t="n"/>
       <c r="AI39" s="1012" t="n"/>
@@ -15057,7 +15057,7 @@
       <c r="AN164" s="1225" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="141">
+  <mergeCells count="140">
     <mergeCell ref="AK84:AN95"/>
     <mergeCell ref="Q118:V118"/>
     <mergeCell ref="J64:N64"/>
@@ -15106,7 +15106,6 @@
     <mergeCell ref="A21:A24"/>
     <mergeCell ref="AM58:AN69"/>
     <mergeCell ref="AE52:AI52"/>
-    <mergeCell ref="U38:W38"/>
     <mergeCell ref="J120:AH120"/>
     <mergeCell ref="P107:AC107"/>
     <mergeCell ref="AE80:AG80"/>
@@ -15124,8 +15123,8 @@
     <mergeCell ref="D81:U81"/>
     <mergeCell ref="P131:U131"/>
     <mergeCell ref="J42:W42"/>
+    <mergeCell ref="J147:AB147"/>
     <mergeCell ref="G131:H131"/>
-    <mergeCell ref="J147:AB147"/>
     <mergeCell ref="AN97:AN109"/>
     <mergeCell ref="V41:AB41"/>
     <mergeCell ref="AE13:AK13"/>
@@ -15134,6 +15133,7 @@
     <mergeCell ref="Q26:V26"/>
     <mergeCell ref="AE104:AK104"/>
     <mergeCell ref="Q114:AH114"/>
+    <mergeCell ref="AB38:AD38"/>
     <mergeCell ref="Q65:V65"/>
     <mergeCell ref="J41:U41"/>
     <mergeCell ref="F93:N93"/>
@@ -15160,7 +15160,6 @@
     <mergeCell ref="AE12:AJ12"/>
     <mergeCell ref="AE55:AI55"/>
     <mergeCell ref="B111:D122"/>
-    <mergeCell ref="Q38:S38"/>
     <mergeCell ref="O7:AK7"/>
     <mergeCell ref="J36:U36"/>
     <mergeCell ref="AL4:AN16"/>

--- a/output/acs-activity-calendar-2027.xlsx
+++ b/output/acs-activity-calendar-2027.xlsx
@@ -828,7 +828,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="155">
+  <borders count="156">
     <border>
       <left/>
       <right/>
@@ -2578,6 +2578,10 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <right/>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2598,7 +2602,7 @@
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1295">
+  <cellXfs count="1297">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6516,6 +6520,14 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="53" borderId="146" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="103" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="53" borderId="155" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="54" borderId="155" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -8454,7 +8466,7 @@
         </is>
       </c>
       <c r="I25" s="1149" t="n"/>
-      <c r="J25" s="1288" t="inlineStr">
+      <c r="J25" s="1295" t="inlineStr">
         <is>
           <t>LD LEAD TEAMS LMC</t>
         </is>
@@ -8472,7 +8484,7 @@
       <c r="U25" s="1003" t="n"/>
       <c r="V25" s="1290" t="n"/>
       <c r="W25" s="1012" t="n"/>
-      <c r="X25" s="1288" t="inlineStr">
+      <c r="X25" s="1295" t="inlineStr">
         <is>
           <t>LD LEAD LEADERS BMC</t>
         </is>
@@ -8506,7 +8518,7 @@
       <c r="N26" s="1008" t="n"/>
       <c r="O26" s="1012" t="n"/>
       <c r="P26" s="1012" t="n"/>
-      <c r="Q26" s="1291" t="inlineStr">
+      <c r="Q26" s="1296" t="inlineStr">
         <is>
           <t>ELDA LEAD LEADERS BMC</t>
         </is>
@@ -8524,7 +8536,7 @@
       <c r="AB26" s="1024" t="n"/>
       <c r="AC26" s="1043" t="n"/>
       <c r="AD26" s="1012" t="n"/>
-      <c r="AE26" s="1291" t="inlineStr">
+      <c r="AE26" s="1296" t="inlineStr">
         <is>
           <t>ELDA LEAD LEADERS OFFICER</t>
         </is>
@@ -9066,13 +9078,13 @@
       <c r="Y38" s="1008" t="n"/>
       <c r="Z38" s="1022" t="n"/>
       <c r="AA38" s="1022" t="n"/>
-      <c r="AB38" s="1288" t="inlineStr">
+      <c r="AB38" s="1295" t="inlineStr">
         <is>
           <t>LD LEAD TEAMS</t>
         </is>
       </c>
-      <c r="AC38" s="1289" t="n"/>
-      <c r="AD38" s="1289" t="n"/>
+      <c r="AC38" s="844" t="n"/>
+      <c r="AD38" s="844" t="n"/>
       <c r="AE38" s="1022" t="n"/>
       <c r="AF38" s="1022" t="n"/>
       <c r="AG38" s="1022" t="n"/>
@@ -9106,7 +9118,7 @@
       <c r="V39" s="1012" t="n"/>
       <c r="W39" s="1012" t="n"/>
       <c r="X39" s="1008" t="n"/>
-      <c r="Y39" s="1291" t="inlineStr">
+      <c r="Y39" s="1296" t="inlineStr">
         <is>
           <t>ELDA LEAD SYS OFFICER</t>
         </is>
@@ -9725,7 +9737,7 @@
       <c r="AD52" s="1012" t="n"/>
       <c r="AE52" s="1274" t="inlineStr">
         <is>
-          <t>ELDA LEAD LEADERS BMC</t>
+          <t>ELDA LEAD LEADERS</t>
         </is>
       </c>
       <c r="AF52" s="1155" t="n"/>
@@ -10306,7 +10318,11 @@
         </is>
       </c>
       <c r="G65" s="1149" t="n"/>
-      <c r="H65" s="1012" t="n"/>
+      <c r="H65" s="1291" t="inlineStr">
+        <is>
+          <t>ELDA</t>
+        </is>
+      </c>
       <c r="I65" s="1012" t="n"/>
       <c r="J65" s="1008" t="n"/>
       <c r="K65" s="1008" t="n"/>
